--- a/Sistemas ternarios_MF_filled.xlsx
+++ b/Sistemas ternarios_MF_filled.xlsx
@@ -1073,13 +1073,13 @@
         <v>2</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>157.651809</v>
+        <v>154.574631</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>156.413729</v>
+        <v>155.54848</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>141.744175</v>
+        <v>139.868341</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1087,13 +1087,13 @@
         <v>3</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>1.05643576</v>
+        <v>1.05174512</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.03759299</v>
+        <v>1.046301</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.06384666</v>
+        <v>1.06554432</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>4</v>
@@ -1262,27 +1262,27 @@
       </c>
       <c r="O5" s="24" t="n">
         <f aca="false">(L5/$F$2)^(1/$F$3)</f>
-        <v>0.916561356599235</v>
+        <v>0.93353874253343</v>
       </c>
       <c r="P5" s="24" t="n">
         <f aca="false">(M5/$G$2)^(1/$G$3)</f>
-        <v>10.6755947451344</v>
+        <v>10.5229040374223</v>
       </c>
       <c r="Q5" s="24" t="n">
         <f aca="false">(N5/$H$2)^(1/$H$3)</f>
-        <v>10.4831289808958</v>
+        <v>10.57535482243</v>
       </c>
       <c r="R5" s="25" t="n">
         <f aca="false">O5*$K5/$I5</f>
-        <v>3.76011014363903</v>
+        <v>3.82975833533293</v>
       </c>
       <c r="S5" s="25" t="n">
         <f aca="false">P5*$K5/$I5</f>
-        <v>43.7956627797382</v>
+        <v>43.1692629487025</v>
       </c>
       <c r="T5" s="26" t="n">
         <f aca="false">Q5*$K5/$I5</f>
-        <v>43.0060893734339</v>
+        <v>43.3844375546678</v>
       </c>
       <c r="U5" s="27" t="n">
         <v>1.9303</v>
@@ -1290,15 +1290,15 @@
       <c r="V5" s="27"/>
       <c r="W5" s="28" t="n">
         <f aca="false">AVERAGE(R5:R6)/100</f>
-        <v>0.0381237964556902</v>
+        <v>0.0388367967251444</v>
       </c>
       <c r="X5" s="27" t="n">
         <f aca="false">AVERAGE(S5:S6)/100</f>
-        <v>0.443712304556594</v>
+        <v>0.437225184224645</v>
       </c>
       <c r="Y5" s="27" t="n">
         <f aca="false">AVERAGE(T5:T6)/100</f>
-        <v>0.435501224799513</v>
+        <v>0.439305838971171</v>
       </c>
       <c r="Z5" s="29" t="n">
         <f aca="false">AVERAGE(U5:V6)/100</f>
@@ -1306,20 +1306,20 @@
       </c>
       <c r="AA5" s="2" t="n">
         <f aca="false">SUM(W5:Z5)</f>
-        <v>0.936828825811797</v>
+        <v>0.93485931992096</v>
       </c>
       <c r="AB5" s="2"/>
       <c r="AC5" s="30" t="n">
         <v>1</v>
       </c>
       <c r="AD5" s="31" t="n">
-        <v>0.0407491393027032</v>
+        <v>0.0416005549605888</v>
       </c>
       <c r="AE5" s="31" t="n">
-        <v>0.474267942588426</v>
+        <v>0.468339611920537</v>
       </c>
       <c r="AF5" s="31" t="n">
-        <v>0.465491418108871</v>
+        <v>0.470568333118875</v>
       </c>
       <c r="AG5" s="31" t="n">
         <v>0.0194915</v>
@@ -1372,27 +1372,27 @@
       </c>
       <c r="O6" s="24" t="n">
         <f aca="false">(L6/$F$2)^(1/$F$3)</f>
-        <v>0.990789444710306</v>
+        <v>1.00949228998242</v>
       </c>
       <c r="P6" s="24" t="n">
         <f aca="false">(M6/$G$2)^(1/$G$3)</f>
-        <v>11.5231192956065</v>
+        <v>11.3510871901917</v>
       </c>
       <c r="Q6" s="24" t="n">
         <f aca="false">(N6/$H$2)^(1/$H$3)</f>
-        <v>11.3045252650579</v>
+        <v>11.4026068537445</v>
       </c>
       <c r="R6" s="25" t="n">
         <f aca="false">O6*$K6/$I6</f>
-        <v>3.86464914749902</v>
+        <v>3.93760100969595</v>
       </c>
       <c r="S6" s="25" t="n">
         <f aca="false">P6*$K6/$I6</f>
-        <v>44.9467981315807</v>
+        <v>44.2757738962264</v>
       </c>
       <c r="T6" s="26" t="n">
         <f aca="false">Q6*$K6/$I6</f>
-        <v>44.0941555864687</v>
+        <v>44.4767302395664</v>
       </c>
       <c r="U6" s="27" t="n">
         <v>1.968</v>
@@ -1407,19 +1407,19 @@
       <c r="AC6" s="30"/>
       <c r="AD6" s="31" t="n">
         <f aca="false">W7/$AA7</f>
-        <v>0.00126359967502694</v>
+        <v>0.00126790536818949</v>
       </c>
       <c r="AE6" s="31" t="n">
         <f aca="false">X7/$AA7</f>
-        <v>0.00062736199948897</v>
+        <v>0.000651971535977927</v>
       </c>
       <c r="AF6" s="31" t="n">
         <f aca="false">Y7/$AA7</f>
-        <v>0.000747865045461097</v>
+        <v>0.00076189343968978</v>
       </c>
       <c r="AG6" s="31" t="n">
         <f aca="false">Z7/$AA7</f>
-        <v>0.997361173280023</v>
+        <v>0.997318229656143</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1469,27 +1469,27 @@
       </c>
       <c r="O7" s="37" t="n">
         <f aca="false">(L7/$F$2)^(1/$F$3)</f>
-        <v>0.0320343712741526</v>
+        <v>0.0321433408909263</v>
       </c>
       <c r="P7" s="37" t="n">
         <f aca="false">(M7/$G$2)^(1/$G$3)</f>
-        <v>0.00775306626617127</v>
+        <v>0.00811598407714054</v>
       </c>
       <c r="Q7" s="37" t="n">
         <f aca="false">(N7/$H$2)^(1/$H$3)</f>
-        <v>0.0102919528987929</v>
+        <v>0.0104977020258997</v>
       </c>
       <c r="R7" s="38" t="n">
         <f aca="false">O7*$K7/$I7</f>
-        <v>0.122291331810875</v>
+        <v>0.12270732372931</v>
       </c>
       <c r="S7" s="38" t="n">
         <f aca="false">P7*$K7/$I7</f>
-        <v>0.029597359386075</v>
+        <v>0.0309827994829478</v>
       </c>
       <c r="T7" s="39" t="n">
         <f aca="false">Q7*$K7/$I7</f>
-        <v>0.0392895685748549</v>
+        <v>0.0400750166349241</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>97.9104</v>
@@ -1497,15 +1497,15 @@
       <c r="V7" s="2"/>
       <c r="W7" s="32" t="n">
         <f aca="false">AVERAGE(R7:R8)/100</f>
-        <v>0.00124101049673721</v>
+        <v>0.0012452928365592</v>
       </c>
       <c r="X7" s="2" t="n">
         <f aca="false">AVERAGE(S7:S8)/100</f>
-        <v>0.000616146744896289</v>
+        <v>0.000640343911906584</v>
       </c>
       <c r="Y7" s="2" t="n">
         <f aca="false">AVERAGE(T7:T8)/100</f>
-        <v>0.000734495576330602</v>
+        <v>0.000748305407068313</v>
       </c>
       <c r="Z7" s="33" t="n">
         <f aca="false">AVERAGE(U7:V8)/100</f>
@@ -1513,23 +1513,23 @@
       </c>
       <c r="AA7" s="2" t="n">
         <f aca="false">SUM(W7:Z7)</f>
-        <v>0.982123152817964</v>
+        <v>0.982165442155534</v>
       </c>
       <c r="AB7" s="2"/>
       <c r="AC7" s="30" t="n">
         <v>2</v>
       </c>
       <c r="AD7" s="31" t="n">
-        <v>0.00124101049673721</v>
+        <v>0.0012452928365592</v>
       </c>
       <c r="AE7" s="31" t="n">
-        <v>0.000616146744896289</v>
+        <v>0.000640343911906584</v>
       </c>
       <c r="AF7" s="31" t="n">
-        <v>0.000734495576330602</v>
+        <v>0.000748305407068313</v>
       </c>
       <c r="AG7" s="31" t="n">
-        <v>0.997408347182036</v>
+        <v>0.997366057844466</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1579,27 +1579,27 @@
       </c>
       <c r="O8" s="37" t="n">
         <f aca="false">(L8/$F$2)^(1/$F$3)</f>
-        <v>0.0327338913164489</v>
+        <v>0.032848404914437</v>
       </c>
       <c r="P8" s="37" t="n">
         <f aca="false">(M8/$G$2)^(1/$G$3)</f>
-        <v>0.0243421546151403</v>
+        <v>0.0252401130953542</v>
       </c>
       <c r="Q8" s="37" t="n">
         <f aca="false">(N8/$H$2)^(1/$H$3)</f>
-        <v>0.0279759966118958</v>
+        <v>0.0284898456617123</v>
       </c>
       <c r="R8" s="38" t="n">
         <f aca="false">O8*$K8/$I8</f>
-        <v>0.125910767536568</v>
+        <v>0.126351243582531</v>
       </c>
       <c r="S8" s="38" t="n">
         <f aca="false">P8*$K8/$I8</f>
-        <v>0.0936319895931828</v>
+        <v>0.097085982898369</v>
       </c>
       <c r="T8" s="39" t="n">
         <f aca="false">Q8*$K8/$I8</f>
-        <v>0.107609546691266</v>
+        <v>0.109586064778739</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>97.9959</v>
@@ -1614,19 +1614,19 @@
       <c r="AC8" s="30"/>
       <c r="AD8" s="31" t="n">
         <f aca="false">W11/$AA11</f>
-        <v>0.858101779084878</v>
+        <v>0.861496673499354</v>
       </c>
       <c r="AE8" s="31" t="n">
         <f aca="false">X11/$AA11</f>
-        <v>0.0236659242403977</v>
+        <v>0.0232405720730087</v>
       </c>
       <c r="AF8" s="31" t="n">
         <f aca="false">Y11/$AA11</f>
-        <v>0.024650934085898</v>
+        <v>0.0242868426774779</v>
       </c>
       <c r="AG8" s="31" t="n">
         <f aca="false">Z11/$AA11</f>
-        <v>0.0935813625888259</v>
+        <v>0.0909759117501596</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1678,27 +1678,27 @@
       </c>
       <c r="O9" s="24" t="n">
         <f aca="false">(L9/$F$2)^(1/$F$3)</f>
-        <v>0.58660428753313</v>
+        <v>0.596281920970589</v>
       </c>
       <c r="P9" s="24" t="n">
         <f aca="false">(M9/$G$2)^(1/$G$3)</f>
-        <v>0.000487948162450284</v>
+        <v>0.000522682218105157</v>
       </c>
       <c r="Q9" s="24" t="n">
         <f aca="false">(N9/$H$2)^(1/$H$3)</f>
-        <v>0.00105562775377233</v>
+        <v>0.00108064472410342</v>
       </c>
       <c r="R9" s="25" t="n">
         <f aca="false">O9*$K9/$I9</f>
-        <v>2.22374213112484</v>
+        <v>2.26042880672853</v>
       </c>
       <c r="S9" s="25" t="n">
         <f aca="false">P9*$K9/$I9</f>
-        <v>0.00184974932796475</v>
+        <v>0.0019814217084538</v>
       </c>
       <c r="T9" s="26" t="n">
         <f aca="false">Q9*$K9/$I9</f>
-        <v>0.00400175034642179</v>
+        <v>0.00409658649423157</v>
       </c>
       <c r="U9" s="27" t="n">
         <v>98.9515</v>
@@ -1706,15 +1706,15 @@
       <c r="V9" s="27"/>
       <c r="W9" s="28" t="n">
         <f aca="false">AVERAGE(R9:R10)/100</f>
-        <v>0.0220657097909616</v>
+        <v>0.022429496434778</v>
       </c>
       <c r="X9" s="27" t="n">
         <f aca="false">AVERAGE(S9:S10)/100</f>
-        <v>2.26011858724942E-005</v>
+        <v>2.41651253614074E-005</v>
       </c>
       <c r="Y9" s="27" t="n">
         <f aca="false">AVERAGE(T9:T10)/100</f>
-        <v>4.5253218079143E-005</v>
+        <v>4.63156550236011E-005</v>
       </c>
       <c r="Z9" s="29" t="n">
         <f aca="false">AVERAGE(U9:V10)/100</f>
@@ -1722,23 +1722,23 @@
       </c>
       <c r="AA9" s="2" t="n">
         <f aca="false">SUM(W9:Z9)</f>
-        <v>1.00694406419491</v>
+        <v>1.00731047721516</v>
       </c>
       <c r="AB9" s="2"/>
       <c r="AC9" s="30" t="n">
         <v>3</v>
       </c>
       <c r="AD9" s="31" t="n">
-        <v>0.0220657097909616</v>
+        <v>0.022429496434778</v>
       </c>
       <c r="AE9" s="31" t="n">
-        <v>2.26011858724942E-005</v>
+        <v>2.41651253614074E-005</v>
       </c>
       <c r="AF9" s="31" t="n">
-        <v>4.5253218079143E-005</v>
+        <v>4.63156550236011E-005</v>
       </c>
       <c r="AG9" s="31" t="n">
-        <v>0.977866435805087</v>
+        <v>0.977500022784837</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1788,27 +1788,27 @@
       </c>
       <c r="O10" s="24" t="n">
         <f aca="false">(L10/$F$2)^(1/$F$3)</f>
-        <v>0.583688837033651</v>
+        <v>0.593305188205999</v>
       </c>
       <c r="P10" s="24" t="n">
         <f aca="false">(M10/$G$2)^(1/$G$3)</f>
-        <v>0.000711945769879673</v>
+        <v>0.000760230740194773</v>
       </c>
       <c r="Q10" s="24" t="n">
         <f aca="false">(N10/$H$2)^(1/$H$3)</f>
-        <v>0.00134602305357552</v>
+        <v>0.00137738859733488</v>
       </c>
       <c r="R10" s="25" t="n">
         <f aca="false">O10*$K10/$I10</f>
-        <v>2.18939982706748</v>
+        <v>2.22547048022707</v>
       </c>
       <c r="S10" s="25" t="n">
         <f aca="false">P10*$K10/$I10</f>
-        <v>0.00267048784653409</v>
+        <v>0.00285160336382767</v>
       </c>
       <c r="T10" s="26" t="n">
         <f aca="false">Q10*$K10/$I10</f>
-        <v>0.00504889326940681</v>
+        <v>0.00516654451048865</v>
       </c>
       <c r="U10" s="27" t="n">
         <v>98.0106</v>
@@ -1823,19 +1823,19 @@
       <c r="AC10" s="30"/>
       <c r="AD10" s="31" t="n">
         <f aca="false">W15/$AA15</f>
-        <v>0.0132140972740956</v>
+        <v>0.0134022231763033</v>
       </c>
       <c r="AE10" s="31" t="n">
         <f aca="false">X15/$AA15</f>
-        <v>0.000137542316783192</v>
+        <v>0.000144783302783293</v>
       </c>
       <c r="AF10" s="31" t="n">
         <f aca="false">Y15/$AA15</f>
-        <v>0.000271833088461651</v>
+        <v>0.000277340987718069</v>
       </c>
       <c r="AG10" s="31" t="n">
         <f aca="false">Z15/$AA15</f>
-        <v>0.98637652732066</v>
+        <v>0.986175652533195</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1885,27 +1885,27 @@
       </c>
       <c r="O11" s="37" t="n">
         <f aca="false">(L11/$F$2)^(1/$F$3)</f>
-        <v>19.6513351224358</v>
+        <v>20.2908374640603</v>
       </c>
       <c r="P11" s="37" t="n">
         <f aca="false">(M11/$G$2)^(1/$G$3)</f>
-        <v>0.542318133173569</v>
+        <v>0.547984569988561</v>
       </c>
       <c r="Q11" s="37" t="n">
         <f aca="false">(N11/$H$2)^(1/$H$3)</f>
-        <v>0.565842800705721</v>
+        <v>0.573481887142643</v>
       </c>
       <c r="R11" s="38" t="n">
         <f aca="false">O11*$K11/$I11</f>
-        <v>77.410730451905</v>
+        <v>79.929864296116</v>
       </c>
       <c r="S11" s="38" t="n">
         <f aca="false">P11*$K11/$I11</f>
-        <v>2.13630486502415</v>
+        <v>2.15862614804004</v>
       </c>
       <c r="T11" s="39" t="n">
         <f aca="false">Q11*$K11/$I11</f>
-        <v>2.22897346417816</v>
+        <v>2.25906542777163</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>8.5693</v>
@@ -1915,15 +1915,15 @@
       </c>
       <c r="W11" s="32" t="n">
         <f aca="false">AVERAGE(R11:R12)/100</f>
-        <v>0.782538059599706</v>
+        <v>0.808133703012013</v>
       </c>
       <c r="X11" s="2" t="n">
         <f aca="false">AVERAGE(S11:S12)/100</f>
-        <v>0.0215819228966807</v>
+        <v>0.0218010006854568</v>
       </c>
       <c r="Y11" s="2" t="n">
         <f aca="false">AVERAGE(T11:T12)/100</f>
-        <v>0.0224801936053215</v>
+        <v>0.0227824630218205</v>
       </c>
       <c r="Z11" s="33" t="n">
         <f aca="false">AVERAGE(U11:V12)/100</f>
@@ -1931,20 +1931,20 @@
       </c>
       <c r="AA11" s="2" t="n">
         <f aca="false">SUM(W11:Z11)</f>
-        <v>0.911940842768374</v>
+        <v>0.938057833385957</v>
       </c>
       <c r="AB11" s="2"/>
       <c r="AC11" s="30" t="n">
         <v>4</v>
       </c>
       <c r="AD11" s="31" t="n">
-        <v>0.865903202775701</v>
+        <v>0.866837285433114</v>
       </c>
       <c r="AE11" s="31" t="n">
-        <v>0.0238810827525163</v>
+        <v>0.0233846456142987</v>
       </c>
       <c r="AF11" s="31" t="n">
-        <v>0.0248750478051164</v>
+        <v>0.0244374022859205</v>
       </c>
       <c r="AG11" s="31" t="n">
         <v>0.0853406666666667</v>
@@ -1997,27 +1997,27 @@
       </c>
       <c r="O12" s="37" t="n">
         <f aca="false">(L12/$F$2)^(1/$F$3)</f>
-        <v>21.1045042864891</v>
+        <v>21.7982307797502</v>
       </c>
       <c r="P12" s="37" t="n">
         <f aca="false">(M12/$G$2)^(1/$G$3)</f>
-        <v>0.581685406828315</v>
+        <v>0.587420475075652</v>
       </c>
       <c r="Q12" s="37" t="n">
         <f aca="false">(N12/$H$2)^(1/$H$3)</f>
-        <v>0.604894751141849</v>
+        <v>0.612995870335117</v>
       </c>
       <c r="R12" s="38" t="n">
         <f aca="false">O12*$K12/$I12</f>
-        <v>79.0968814680361</v>
+        <v>81.6968763062865</v>
       </c>
       <c r="S12" s="38" t="n">
         <f aca="false">P12*$K12/$I12</f>
-        <v>2.180079714312</v>
+        <v>2.20157398905131</v>
       </c>
       <c r="T12" s="39" t="n">
         <f aca="false">Q12*$K12/$I12</f>
-        <v>2.26706525688613</v>
+        <v>2.29742717659247</v>
       </c>
       <c r="U12" s="2"/>
       <c r="V12" s="2" t="n">
@@ -2032,19 +2032,19 @@
       <c r="AC12" s="30"/>
       <c r="AD12" s="31" t="n">
         <f aca="false">W19/$AA19</f>
-        <v>0.0079429689638234</v>
+        <v>0.00803597300954261</v>
       </c>
       <c r="AE12" s="31" t="n">
         <f aca="false">X19/$AA19</f>
-        <v>0.000714196572706856</v>
+        <v>0.000740924878946511</v>
       </c>
       <c r="AF12" s="31" t="n">
         <f aca="false">Y19/$AA19</f>
-        <v>0.000889639918618229</v>
+        <v>0.000905924409562502</v>
       </c>
       <c r="AG12" s="31" t="n">
         <f aca="false">Z19/$AA19</f>
-        <v>0.990453194544852</v>
+        <v>0.990317177701948</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2096,27 +2096,27 @@
       </c>
       <c r="O13" s="24" t="n">
         <f aca="false">(L13/$F$2)^(1/$F$3)</f>
-        <v>11.3471022209968</v>
+        <v>11.6877030308204</v>
       </c>
       <c r="P13" s="24" t="n">
         <f aca="false">(M13/$G$2)^(1/$G$3)</f>
-        <v>5.72561830133955</v>
+        <v>5.67306530877131</v>
       </c>
       <c r="Q13" s="24" t="n">
         <f aca="false">(N13/$H$2)^(1/$H$3)</f>
-        <v>5.72380830219254</v>
+        <v>5.77973344269852</v>
       </c>
       <c r="R13" s="25" t="n">
         <f aca="false">O13*$K13/$I13</f>
-        <v>44.6339002687728</v>
+        <v>45.9736557659074</v>
       </c>
       <c r="S13" s="25" t="n">
         <f aca="false">P13*$K13/$I13</f>
-        <v>22.5217567676587</v>
+        <v>22.3150392301383</v>
       </c>
       <c r="T13" s="26" t="n">
         <f aca="false">Q13*$K13/$I13</f>
-        <v>22.5146371242607</v>
+        <v>22.7346190275912</v>
       </c>
       <c r="U13" s="27" t="n">
         <v>4.0063</v>
@@ -2124,15 +2124,15 @@
       <c r="V13" s="27"/>
       <c r="W13" s="28" t="n">
         <f aca="false">AVERAGE(R13:R14)/100</f>
-        <v>0.4468745628246</v>
+        <v>0.460384567450759</v>
       </c>
       <c r="X13" s="27" t="n">
         <f aca="false">AVERAGE(S13:S14)/100</f>
-        <v>0.225447000422808</v>
+        <v>0.223290844227201</v>
       </c>
       <c r="Y13" s="27" t="n">
         <f aca="false">AVERAGE(T13:T14)/100</f>
-        <v>0.224996142778877</v>
+        <v>0.227178211822202</v>
       </c>
       <c r="Z13" s="29" t="n">
         <f aca="false">AVERAGE(U13:V14)/100</f>
@@ -2140,20 +2140,20 @@
       </c>
       <c r="AA13" s="2" t="n">
         <f aca="false">SUM(W13:Z13)</f>
-        <v>0.937594206026285</v>
+        <v>0.951130123500162</v>
       </c>
       <c r="AB13" s="2"/>
       <c r="AC13" s="30" t="n">
         <v>5</v>
       </c>
       <c r="AD13" s="31" t="n">
-        <v>0.477953367703224</v>
+        <v>0.485085503334719</v>
       </c>
       <c r="AE13" s="31" t="n">
-        <v>0.241126172878551</v>
+        <v>0.23527103039476</v>
       </c>
       <c r="AF13" s="31" t="n">
-        <v>0.240643959418225</v>
+        <v>0.239366966270521</v>
       </c>
       <c r="AG13" s="31" t="n">
         <v>0.0402765</v>
@@ -2206,27 +2206,27 @@
       </c>
       <c r="O14" s="24" t="n">
         <f aca="false">(L14/$F$2)^(1/$F$3)</f>
-        <v>12.4625048108725</v>
+        <v>12.8419551033441</v>
       </c>
       <c r="P14" s="24" t="n">
         <f aca="false">(M14/$G$2)^(1/$G$3)</f>
-        <v>6.28616450484686</v>
+        <v>6.22362673596959</v>
       </c>
       <c r="Q14" s="24" t="n">
         <f aca="false">(N14/$H$2)^(1/$H$3)</f>
-        <v>6.26303059553002</v>
+        <v>6.3233171988729</v>
       </c>
       <c r="R14" s="25" t="n">
         <f aca="false">O14*$K14/$I14</f>
-        <v>44.7410122961471</v>
+        <v>46.1032577242443</v>
       </c>
       <c r="S14" s="25" t="n">
         <f aca="false">P14*$K14/$I14</f>
-        <v>22.5676433169029</v>
+        <v>22.3431296153018</v>
       </c>
       <c r="T14" s="26" t="n">
         <f aca="false">Q14*$K14/$I14</f>
-        <v>22.4845914315147</v>
+        <v>22.7010233368492</v>
       </c>
       <c r="U14" s="27" t="n">
         <v>4.049</v>
@@ -2241,19 +2241,19 @@
       <c r="AC14" s="30"/>
       <c r="AD14" s="31" t="n">
         <f aca="false">W23/$AA23</f>
-        <v>0.702275392920899</v>
+        <v>0.708116557937581</v>
       </c>
       <c r="AE14" s="31" t="n">
         <f aca="false">X23/$AA23</f>
-        <v>0.110505733476083</v>
+        <v>0.107709047768124</v>
       </c>
       <c r="AF14" s="31" t="n">
         <f aca="false">Y23/$AA23</f>
-        <v>0.112169422112053</v>
+        <v>0.110829411404902</v>
       </c>
       <c r="AG14" s="31" t="n">
         <f aca="false">Z23/$AA23</f>
-        <v>0.075049451490966</v>
+        <v>0.0733449828893929</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2303,27 +2303,27 @@
       </c>
       <c r="O15" s="37" t="n">
         <f aca="false">(L15/$F$2)^(1/$F$3)</f>
-        <v>0.369243194359218</v>
+        <v>0.374560805047172</v>
       </c>
       <c r="P15" s="37" t="n">
         <f aca="false">(M15/$G$2)^(1/$G$3)</f>
-        <v>0.00384381882825816</v>
+        <v>0.00404731124339593</v>
       </c>
       <c r="Q15" s="37" t="n">
         <f aca="false">(N15/$H$2)^(1/$H$3)</f>
-        <v>0.00757202487940087</v>
+        <v>0.0077271766155872</v>
       </c>
       <c r="R15" s="38" t="n">
         <f aca="false">O15*$K15/$I15</f>
-        <v>1.2430261251312</v>
+        <v>1.26092741379238</v>
       </c>
       <c r="S15" s="38" t="n">
         <f aca="false">P15*$K15/$I15</f>
-        <v>0.0129398924524194</v>
+        <v>0.0136249325347999</v>
       </c>
       <c r="T15" s="39" t="n">
         <f aca="false">Q15*$K15/$I15</f>
-        <v>0.0254905842247752</v>
+        <v>0.0260128894815416</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>97.5173</v>
@@ -2331,15 +2331,15 @@
       <c r="V15" s="2"/>
       <c r="W15" s="32" t="n">
         <f aca="false">AVERAGE(R15:R16)/100</f>
-        <v>0.0130996162152444</v>
+        <v>0.0132888185355668</v>
       </c>
       <c r="X15" s="2" t="n">
         <f aca="false">AVERAGE(S15:S16)/100</f>
-        <v>0.000136350711353356</v>
+        <v>0.000143558200184956</v>
       </c>
       <c r="Y15" s="2" t="n">
         <f aca="false">AVERAGE(T15:T16)/100</f>
-        <v>0.000269478047541914</v>
+        <v>0.00027499423116433</v>
       </c>
       <c r="Z15" s="33" t="n">
         <f aca="false">AVERAGE(U15:V16)/100</f>
@@ -2347,20 +2347,20 @@
       </c>
       <c r="AA15" s="2" t="n">
         <f aca="false">SUM(W15:Z15)</f>
-        <v>0.99133644497414</v>
+        <v>0.991538370966916</v>
       </c>
       <c r="AB15" s="2"/>
       <c r="AD15" s="0" t="n">
-        <v>0.0130996162152444</v>
+        <v>0.0132888185355668</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>0.000136350711353356</v>
+        <v>0.000143558200184956</v>
       </c>
       <c r="AF15" s="0" t="n">
-        <v>0.000269478047541914</v>
+        <v>0.00027499423116433</v>
       </c>
       <c r="AG15" s="0" t="n">
-        <v>0.98649455502586</v>
+        <v>0.986292629033084</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2410,27 +2410,27 @@
       </c>
       <c r="O16" s="37" t="n">
         <f aca="false">(L16/$F$2)^(1/$F$3)</f>
-        <v>0.375818802581781</v>
+        <v>0.381261124253474</v>
       </c>
       <c r="P16" s="37" t="n">
         <f aca="false">(M16/$G$2)^(1/$G$3)</f>
-        <v>0.00391138688382031</v>
+        <v>0.00411785911568307</v>
       </c>
       <c r="Q16" s="37" t="n">
         <f aca="false">(N16/$H$2)^(1/$H$3)</f>
-        <v>0.00775304302004417</v>
+        <v>0.00791160604246488</v>
       </c>
       <c r="R16" s="38" t="n">
         <f aca="false">O16*$K16/$I16</f>
-        <v>1.37689711791768</v>
+        <v>1.39683629332098</v>
       </c>
       <c r="S16" s="38" t="n">
         <f aca="false">P16*$K16/$I16</f>
-        <v>0.0143302498182519</v>
+        <v>0.0150867075021912</v>
       </c>
       <c r="T16" s="39" t="n">
         <f aca="false">Q16*$K16/$I16</f>
-        <v>0.0284050252836075</v>
+        <v>0.0289859567513243</v>
       </c>
       <c r="U16" s="2" t="n">
         <v>97.0495</v>
@@ -2494,27 +2494,27 @@
       </c>
       <c r="O17" s="24" t="n">
         <f aca="false">(L17/$F$2)^(1/$F$3)</f>
-        <v>5.60798801811875</v>
+        <v>5.7581929348405</v>
       </c>
       <c r="P17" s="24" t="n">
         <f aca="false">(M17/$G$2)^(1/$G$3)</f>
-        <v>8.31298360513033</v>
+        <v>8.21116139259152</v>
       </c>
       <c r="Q17" s="24" t="n">
         <f aca="false">(N17/$H$2)^(1/$H$3)</f>
-        <v>8.23417107939367</v>
+        <v>8.30980797991203</v>
       </c>
       <c r="R17" s="25" t="n">
         <f aca="false">O17*$K17/$I17</f>
-        <v>22.8561110797882</v>
+        <v>23.4682914643094</v>
       </c>
       <c r="S17" s="25" t="n">
         <f aca="false">P17*$K17/$I17</f>
-        <v>33.8806852064307</v>
+        <v>33.4656950544087</v>
       </c>
       <c r="T17" s="26" t="n">
         <f aca="false">Q17*$K17/$I17</f>
-        <v>33.5594741344926</v>
+        <v>33.8677425178047</v>
       </c>
       <c r="U17" s="27" t="n">
         <v>2.6416</v>
@@ -2522,15 +2522,15 @@
       <c r="V17" s="27"/>
       <c r="W17" s="32" t="n">
         <f aca="false">AVERAGE(R17:R18)/100</f>
-        <v>0.229272787325909</v>
+        <v>0.235473327844142</v>
       </c>
       <c r="X17" s="2" t="n">
         <f aca="false">AVERAGE(S17:S18)/100</f>
-        <v>0.340653946395026</v>
+        <v>0.336315476779463</v>
       </c>
       <c r="Y17" s="2" t="n">
         <f aca="false">AVERAGE(T17:T18)/100</f>
-        <v>0.336568684638486</v>
+        <v>0.339629687581382</v>
       </c>
       <c r="Z17" s="33" t="n">
         <f aca="false">AVERAGE(U17:V18)/100</f>
@@ -2538,17 +2538,17 @@
       </c>
       <c r="AA17" s="2" t="n">
         <f aca="false">SUM(W17:Z17)</f>
-        <v>0.933115918359422</v>
+        <v>0.938038992204987</v>
       </c>
       <c r="AB17" s="2"/>
       <c r="AD17" s="0" t="n">
-        <v>0.246189254320548</v>
+        <v>0.251481522572307</v>
       </c>
       <c r="AE17" s="0" t="n">
-        <v>0.365788465445443</v>
+        <v>0.359179228235616</v>
       </c>
       <c r="AF17" s="0" t="n">
-        <v>0.361401780234009</v>
+        <v>0.362718749192077</v>
       </c>
       <c r="AG17" s="0" t="n">
         <v>0.0266205</v>
@@ -2601,27 +2601,27 @@
       </c>
       <c r="O18" s="24" t="n">
         <f aca="false">(L18/$F$2)^(1/$F$3)</f>
-        <v>6.28074014992374</v>
+        <v>6.45222350887206</v>
       </c>
       <c r="P18" s="24" t="n">
         <f aca="false">(M18/$G$2)^(1/$G$3)</f>
-        <v>9.35350154453505</v>
+        <v>9.22987081298632</v>
       </c>
       <c r="Q18" s="24" t="n">
         <f aca="false">(N18/$H$2)^(1/$H$3)</f>
-        <v>9.21809021373725</v>
+        <v>9.30109230755209</v>
       </c>
       <c r="R18" s="25" t="n">
         <f aca="false">O18*$K18/$I18</f>
-        <v>22.9984463853936</v>
+        <v>23.6263741045189</v>
       </c>
       <c r="S18" s="25" t="n">
         <f aca="false">P18*$K18/$I18</f>
-        <v>34.2501040725746</v>
+        <v>33.797400301484</v>
       </c>
       <c r="T18" s="26" t="n">
         <f aca="false">Q18*$K18/$I18</f>
-        <v>33.7542627932046</v>
+        <v>34.0581949984718</v>
       </c>
       <c r="U18" s="27" t="n">
         <v>2.6825</v>
@@ -2681,27 +2681,27 @@
       </c>
       <c r="O19" s="37" t="n">
         <f aca="false">(L19/$F$2)^(1/$F$3)</f>
-        <v>0.225348163891774</v>
+        <v>0.228090605760248</v>
       </c>
       <c r="P19" s="37" t="n">
         <f aca="false">(M19/$G$2)^(1/$G$3)</f>
-        <v>0.0299389436645101</v>
+        <v>0.0309899398482363</v>
       </c>
       <c r="Q19" s="37" t="n">
         <f aca="false">(N19/$H$2)^(1/$H$3)</f>
-        <v>0.0352994756937982</v>
+        <v>0.0359345239429189</v>
       </c>
       <c r="R19" s="38" t="n">
         <f aca="false">O19*$K19/$I19</f>
-        <v>0.822603444230853</v>
+        <v>0.832614362836308</v>
       </c>
       <c r="S19" s="38" t="n">
         <f aca="false">P19*$K19/$I19</f>
-        <v>0.109288124428151</v>
+        <v>0.113124645949674</v>
       </c>
       <c r="T19" s="39" t="n">
         <f aca="false">Q19*$K19/$I19</f>
-        <v>0.128856032300344</v>
+        <v>0.131174191312416</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>96.7978</v>
@@ -2709,15 +2709,15 @@
       <c r="V19" s="2"/>
       <c r="W19" s="32" t="n">
         <f aca="false">AVERAGE(R19:R20)/100</f>
-        <v>0.00774200065867064</v>
+        <v>0.00783372736021942</v>
       </c>
       <c r="X19" s="2" t="n">
         <f aca="false">AVERAGE(S19:S20)/100</f>
-        <v>0.000696126393229066</v>
+        <v>0.000722277624523893</v>
       </c>
       <c r="Y19" s="2" t="n">
         <f aca="false">AVERAGE(T19:T20)/100</f>
-        <v>0.000867130775317375</v>
+        <v>0.000883124523321954</v>
       </c>
       <c r="Z19" s="33" t="n">
         <f aca="false">AVERAGE(U19:V20)/100</f>
@@ -2725,20 +2725,20 @@
       </c>
       <c r="AA19" s="2" t="n">
         <f aca="false">SUM(W19:Z19)</f>
-        <v>0.97469859116055</v>
+        <v>0.974832462841399</v>
       </c>
       <c r="AB19" s="2"/>
       <c r="AD19" s="0" t="n">
-        <v>0.00774200065867064</v>
+        <v>0.00783372736021942</v>
       </c>
       <c r="AE19" s="0" t="n">
-        <v>0.000696126393229066</v>
+        <v>0.000722277624523893</v>
       </c>
       <c r="AF19" s="0" t="n">
-        <v>0.000867130775317375</v>
+        <v>0.000883124523321954</v>
       </c>
       <c r="AG19" s="0" t="n">
-        <v>0.990694742172783</v>
+        <v>0.990560870491935</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2788,27 +2788,27 @@
       </c>
       <c r="O20" s="37" t="n">
         <f aca="false">(L20/$F$2)^(1/$F$3)</f>
-        <v>0.193539386395308</v>
+        <v>0.195761825392872</v>
       </c>
       <c r="P20" s="37" t="n">
         <f aca="false">(M20/$G$2)^(1/$G$3)</f>
-        <v>0.00798297726824772</v>
+        <v>0.00835462491438987</v>
       </c>
       <c r="Q20" s="37" t="n">
         <f aca="false">(N20/$H$2)^(1/$H$3)</f>
-        <v>0.0118849732434208</v>
+        <v>0.0121197896392033</v>
       </c>
       <c r="R20" s="38" t="n">
         <f aca="false">O20*$K20/$I20</f>
-        <v>0.725796687503275</v>
+        <v>0.734131109207576</v>
       </c>
       <c r="S20" s="38" t="n">
         <f aca="false">P20*$K20/$I20</f>
-        <v>0.0299371542176627</v>
+        <v>0.0313308789551041</v>
       </c>
       <c r="T20" s="39" t="n">
         <f aca="false">Q20*$K20/$I20</f>
-        <v>0.0445701227631308</v>
+        <v>0.0454507133519752</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>96.7891</v>
@@ -2872,27 +2872,27 @@
       </c>
       <c r="O21" s="24" t="n">
         <f aca="false">(L21/$F$2)^(1/$F$3)</f>
-        <v>0.551864112900037</v>
+        <v>0.560815899340119</v>
       </c>
       <c r="P21" s="24" t="n">
         <f aca="false">(M21/$G$2)^(1/$G$3)</f>
-        <v>0.0107857547112622</v>
+        <v>0.0112596515581288</v>
       </c>
       <c r="Q21" s="24" t="n">
         <f aca="false">(N21/$H$2)^(1/$H$3)</f>
-        <v>0.0138883341245924</v>
+        <v>0.0141592172219458</v>
       </c>
       <c r="R21" s="25" t="n">
         <f aca="false">O21*$K21/$I21</f>
-        <v>2.08402759931137</v>
+        <v>2.11783260595737</v>
       </c>
       <c r="S21" s="25" t="n">
         <f aca="false">P21*$K21/$I21</f>
-        <v>0.0407306979603232</v>
+        <v>0.0425202945023175</v>
       </c>
       <c r="T21" s="26" t="n">
         <f aca="false">Q21*$K21/$I21</f>
-        <v>0.0524470987468455</v>
+        <v>0.0534700459504692</v>
       </c>
       <c r="U21" s="27" t="n">
         <v>98.8196</v>
@@ -2900,15 +2900,15 @@
       <c r="V21" s="27"/>
       <c r="W21" s="28" t="n">
         <f aca="false">AVERAGE(R21:R22)/100</f>
-        <v>0.0242410750881541</v>
+        <v>0.0246546748774306</v>
       </c>
       <c r="X21" s="27" t="n">
         <f aca="false">AVERAGE(S21:S22)/100</f>
-        <v>0.000954064836618211</v>
+        <v>0.000987250945559395</v>
       </c>
       <c r="Y21" s="27" t="n">
         <f aca="false">AVERAGE(T21:T22)/100</f>
-        <v>0.00112086662179403</v>
+        <v>0.0011410162239653</v>
       </c>
       <c r="Z21" s="29" t="n">
         <f aca="false">AVERAGE(U21:V22)/100</f>
@@ -2916,20 +2916,20 @@
       </c>
       <c r="AA21" s="2" t="n">
         <f aca="false">SUM(W21:Z21)</f>
-        <v>1.01451200654657</v>
+        <v>1.01497894204696</v>
       </c>
       <c r="AB21" s="2"/>
       <c r="AD21" s="0" t="n">
-        <v>0.0242410750881541</v>
+        <v>0.0211783260595737</v>
       </c>
       <c r="AE21" s="0" t="n">
-        <v>0.000954064836618211</v>
+        <v>0.000425202945023175</v>
       </c>
       <c r="AF21" s="0" t="n">
-        <v>0.00112086662179403</v>
+        <v>0.000534700459504692</v>
       </c>
       <c r="AG21" s="0" t="n">
-        <v>0.973683993453434</v>
+        <v>0.977861770535899</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2979,27 +2979,27 @@
       </c>
       <c r="O22" s="24" t="n">
         <f aca="false">(L22/$F$2)^(1/$F$3)</f>
-        <v>0.763952940486906</v>
+        <v>0.777471821501433</v>
       </c>
       <c r="P22" s="24" t="n">
         <f aca="false">(M22/$G$2)^(1/$G$3)</f>
-        <v>0.0414790220935029</v>
+        <v>0.0428187856481381</v>
       </c>
       <c r="Q22" s="24" t="n">
         <f aca="false">(N22/$H$2)^(1/$H$3)</f>
-        <v>0.0474608755345304</v>
+        <v>0.0482919284603492</v>
       </c>
       <c r="R22" s="25" t="n">
         <f aca="false">O22*$K22/$I22</f>
-        <v>2.76418741831945</v>
+        <v>2.81310236952875</v>
       </c>
       <c r="S22" s="25" t="n">
         <f aca="false">P22*$K22/$I22</f>
-        <v>0.150082269363319</v>
+        <v>0.154929894609561</v>
       </c>
       <c r="T22" s="26" t="n">
         <f aca="false">Q22*$K22/$I22</f>
-        <v>0.17172622561196</v>
+        <v>0.174733198842591</v>
       </c>
       <c r="U22" s="27" t="n">
         <v>98.8196</v>
@@ -3059,27 +3059,27 @@
       </c>
       <c r="O23" s="37" t="n">
         <f aca="false">(L23/$F$2)^(1/$F$3)</f>
-        <v>15.748940364729</v>
+        <v>16.2454024284824</v>
       </c>
       <c r="P23" s="37" t="n">
         <f aca="false">(M23/$G$2)^(1/$G$3)</f>
-        <v>2.47718876703807</v>
+        <v>2.47162627941431</v>
       </c>
       <c r="Q23" s="37" t="n">
         <f aca="false">(N23/$H$2)^(1/$H$3)</f>
-        <v>2.52071916280301</v>
+        <v>2.54867605629299</v>
       </c>
       <c r="R23" s="38" t="n">
         <f aca="false">O23*$K23/$I23</f>
-        <v>60.5980862431319</v>
+        <v>62.5083513313882</v>
       </c>
       <c r="S23" s="38" t="n">
         <f aca="false">P23*$K23/$I23</f>
-        <v>9.5316189577859</v>
+        <v>9.5102158603746</v>
       </c>
       <c r="T23" s="39" t="n">
         <f aca="false">Q23*$K23/$I23</f>
-        <v>9.69911331713146</v>
+        <v>9.80668463326835</v>
       </c>
       <c r="U23" s="2" t="n">
         <v>6.6554</v>
@@ -3087,15 +3087,15 @@
       <c r="V23" s="2"/>
       <c r="W23" s="32" t="n">
         <f aca="false">AVERAGE(R23:R24)/100</f>
-        <v>0.621230521965124</v>
+        <v>0.640954490064211</v>
       </c>
       <c r="X23" s="2" t="n">
         <f aca="false">AVERAGE(S23:S24)/100</f>
-        <v>0.0977530113962259</v>
+        <v>0.0974932686062186</v>
       </c>
       <c r="Y23" s="2" t="n">
         <f aca="false">AVERAGE(T23:T24)/100</f>
-        <v>0.0992247049371495</v>
+        <v>0.100317678036004</v>
       </c>
       <c r="Z23" s="33" t="n">
         <f aca="false">AVERAGE(U23:V24)/100</f>
@@ -3103,17 +3103,17 @@
       </c>
       <c r="AA23" s="2" t="n">
         <f aca="false">SUM(W23:Z23)</f>
-        <v>0.8845967382985</v>
+        <v>0.905153936706434</v>
       </c>
       <c r="AB23" s="2"/>
       <c r="AD23" s="0" t="n">
-        <v>0.708851282973822</v>
+        <v>0.713432452880176</v>
       </c>
       <c r="AE23" s="0" t="n">
-        <v>0.111540475061622</v>
+        <v>0.108517629315729</v>
       </c>
       <c r="AF23" s="0" t="n">
-        <v>0.113219741964555</v>
+        <v>0.111661417804094</v>
       </c>
       <c r="AG23" s="0" t="n">
         <v>0.0663885</v>
@@ -3166,27 +3166,27 @@
       </c>
       <c r="O24" s="37" t="n">
         <f aca="false">(L24/$F$2)^(1/$F$3)</f>
-        <v>17.335971644885</v>
+        <v>17.8901213255677</v>
       </c>
       <c r="P24" s="37" t="n">
         <f aca="false">(M24/$G$2)^(1/$G$3)</f>
-        <v>2.72889582142765</v>
+        <v>2.72057607708896</v>
       </c>
       <c r="Q24" s="37" t="n">
         <f aca="false">(N24/$H$2)^(1/$H$3)</f>
-        <v>2.76344473746162</v>
+        <v>2.79368443540772</v>
       </c>
       <c r="R24" s="38" t="n">
         <f aca="false">O24*$K24/$I24</f>
-        <v>63.648018149893</v>
+        <v>65.6825466814541</v>
       </c>
       <c r="S24" s="38" t="n">
         <f aca="false">P24*$K24/$I24</f>
-        <v>10.0189833214593</v>
+        <v>9.98843786086912</v>
       </c>
       <c r="T24" s="39" t="n">
         <f aca="false">Q24*$K24/$I24</f>
-        <v>10.1458276702984</v>
+        <v>10.2568509739325</v>
       </c>
       <c r="U24" s="42" t="n">
         <v>6.6223</v>
@@ -3242,19 +3242,19 @@
       </c>
       <c r="P25" s="1" t="n">
         <f aca="false">(M25/$G$2)^(1/$G$3)</f>
-        <v>17.4784601417738</v>
+        <v>17.1579234092013</v>
       </c>
       <c r="Q25" s="1" t="n">
         <f aca="false">(N25/$H$2)^(1/$H$3)</f>
-        <v>16.7004399378438</v>
+        <v>16.8348681641731</v>
       </c>
       <c r="S25" s="1" t="n">
         <f aca="false">P25*$K25/$I25</f>
-        <v>48.065765389878</v>
+        <v>47.1842893753037</v>
       </c>
       <c r="T25" s="1" t="n">
         <f aca="false">Q25*$K25/$I25</f>
-        <v>45.9262098290704</v>
+        <v>46.2958874514761</v>
       </c>
       <c r="U25" s="1" t="n">
         <v>1.5599</v>
@@ -3264,11 +3264,11 @@
       </c>
       <c r="X25" s="1" t="n">
         <f aca="false">AVERAGE(S25:S26)/100</f>
-        <v>0.489257680377166</v>
+        <v>0.480280741522099</v>
       </c>
       <c r="Y25" s="1" t="n">
         <f aca="false">AVERAGE(T25:T26)/100</f>
-        <v>0.467275983173164</v>
+        <v>0.471036755031365</v>
       </c>
       <c r="Z25" s="1" t="n">
         <f aca="false">AVERAGE(U25:V26)/100</f>
@@ -3276,19 +3276,19 @@
       </c>
       <c r="AA25" s="1" t="n">
         <f aca="false">SUM(W25:Z25)</f>
-        <v>0.97198566355033</v>
+        <v>0.966769496553464</v>
       </c>
       <c r="AE25" s="1" t="n">
         <f aca="false">IFERROR(X25/$AA25,"")</f>
-        <v>0.503358947281255</v>
+        <v>0.496789300070287</v>
       </c>
       <c r="AF25" s="1" t="n">
         <f aca="false">IFERROR(Y25/$AA25,"")</f>
-        <v>0.480743698900213</v>
+        <v>0.487227572560587</v>
       </c>
       <c r="AG25" s="1" t="n">
         <f aca="false">IFERROR(Z25/$AA25,"")</f>
-        <v>0.0158973538185318</v>
+        <v>0.0159831273691262</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3332,19 +3332,19 @@
       </c>
       <c r="P26" s="1" t="n">
         <f aca="false">(M26/$G$2)^(1/$G$3)</f>
-        <v>17.5168600548097</v>
+        <v>17.1953050377929</v>
       </c>
       <c r="Q26" s="1" t="n">
         <f aca="false">(N26/$H$2)^(1/$H$3)</f>
-        <v>16.7228225847569</v>
+        <v>16.8573950057178</v>
       </c>
       <c r="S26" s="1" t="n">
         <f aca="false">P26*$K26/$I26</f>
-        <v>49.7857706855552</v>
+        <v>48.8718589291161</v>
       </c>
       <c r="T26" s="1" t="n">
         <f aca="false">Q26*$K26/$I26</f>
-        <v>47.5289868055624</v>
+        <v>47.9114635547969</v>
       </c>
       <c r="U26" s="1" t="n">
         <v>1.4736</v>
@@ -3391,27 +3391,27 @@
       </c>
       <c r="P27" s="1" t="n">
         <f aca="false">(M27/$G$2)^(1/$G$3)</f>
-        <v>0.513304144005008</v>
+        <v>0.518904831257438</v>
       </c>
       <c r="Q27" s="1" t="n">
         <f aca="false">(N27/$H$2)^(1/$H$3)</f>
-        <v>0.496852242962129</v>
+        <v>0.503664258643063</v>
       </c>
       <c r="S27" s="1" t="n">
         <f aca="false">P27*$K27/$I27</f>
-        <v>1.35052837628599</v>
+        <v>1.36526405911546</v>
       </c>
       <c r="T27" s="1" t="n">
         <f aca="false">Q27*$K27/$I27</f>
-        <v>1.30724261780975</v>
+        <v>1.32516536514045</v>
       </c>
       <c r="X27" s="1" t="n">
         <f aca="false">AVERAGE(S27:S28)/100</f>
-        <v>0.0121341150229621</v>
+        <v>0.0122767622715784</v>
       </c>
       <c r="Y27" s="1" t="n">
         <f aca="false">AVERAGE(T27:T28)/100</f>
-        <v>0.0117317632669767</v>
+        <v>0.0118945299187236</v>
       </c>
       <c r="Z27" s="1" t="e">
         <f aca="false">AVERAGE(U27:V28)/100</f>
@@ -3475,19 +3475,19 @@
       </c>
       <c r="P28" s="1" t="n">
         <f aca="false">(M28/$G$2)^(1/$G$3)</f>
-        <v>0.409389789937736</v>
+        <v>0.414636519952529</v>
       </c>
       <c r="Q28" s="1" t="n">
         <f aca="false">(N28/$H$2)^(1/$H$3)</f>
-        <v>0.395245900149066</v>
+        <v>0.400810929603969</v>
       </c>
       <c r="S28" s="1" t="n">
         <f aca="false">P28*$K28/$I28</f>
-        <v>1.07629462830643</v>
+        <v>1.09008839520021</v>
       </c>
       <c r="T28" s="1" t="n">
         <f aca="false">Q28*$K28/$I28</f>
-        <v>1.03911003558559</v>
+        <v>1.05374061860426</v>
       </c>
     </row>
   </sheetData>
@@ -3553,13 +3553,13 @@
         <v>2</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>157.651809</v>
+        <v>154.574631</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>156.413729</v>
+        <v>155.54848</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>147.968358</v>
+        <v>145.969512</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3567,13 +3567,13 @@
         <v>3</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>1.05643576</v>
+        <v>1.05174512</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.03759299</v>
+        <v>1.046301</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.04568333</v>
+        <v>1.04716839</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>4</v>
@@ -3725,27 +3725,27 @@
       </c>
       <c r="O5" s="24" t="n">
         <f aca="false">(L5/$F$2)^(1/$F$3)</f>
-        <v>0.505739900934416</v>
+        <v>0.513743491032854</v>
       </c>
       <c r="P5" s="24" t="n">
         <f aca="false">(M5/$G$2)^(1/$G$3)</f>
-        <v>0.000448492283418835</v>
+        <v>0.000480754965897079</v>
       </c>
       <c r="Q5" s="24" t="n">
         <f aca="false">(N5/$H$2)^(1/$H$3)</f>
-        <v>0.000628441903340449</v>
+        <v>0.000643348613900439</v>
       </c>
       <c r="R5" s="25" t="n">
         <f aca="false">O5*$K5/$I5</f>
-        <v>2.26835623487349</v>
+        <v>2.30425412125268</v>
       </c>
       <c r="S5" s="25" t="n">
         <f aca="false">P5*$K5/$I5</f>
-        <v>0.00201158790418969</v>
+        <v>0.0021562932296308</v>
       </c>
       <c r="T5" s="26" t="n">
         <f aca="false">Q5*$K5/$I5</f>
-        <v>0.00281870207801329</v>
+        <v>0.00288556199904727</v>
       </c>
       <c r="U5" s="27" t="n">
         <v>93.8865</v>
@@ -3753,15 +3753,15 @@
       <c r="V5" s="27"/>
       <c r="W5" s="28" t="n">
         <f aca="false">AVERAGE(R5:R6)/100</f>
-        <v>0.0245295765826063</v>
+        <v>0.0249246213698665</v>
       </c>
       <c r="X5" s="27" t="n">
         <f aca="false">AVERAGE(S5:S6)/100</f>
-        <v>5.33078108341684E-005</v>
+        <v>5.65969280179736E-005</v>
       </c>
       <c r="Y5" s="27" t="n">
         <f aca="false">AVERAGE(T5:T6)/100</f>
-        <v>6.44235988922182E-005</v>
+        <v>6.58614447060957E-005</v>
       </c>
       <c r="Z5" s="29" t="n">
         <f aca="false">AVERAGE(U5:V6)/100</f>
@@ -3769,19 +3769,19 @@
       </c>
       <c r="AA5" s="2" t="n">
         <f aca="false">SUM(W5:Z5)</f>
-        <v>0.962492807992333</v>
+        <v>0.962892579742591</v>
       </c>
       <c r="AD5" s="0" t="n">
-        <v>0.0245295765826063</v>
+        <v>0.0249246213698665</v>
       </c>
       <c r="AE5" s="0" t="n">
-        <v>5.33078108341684E-005</v>
+        <v>5.65969280179736E-005</v>
       </c>
       <c r="AF5" s="0" t="n">
-        <v>6.44235988922182E-005</v>
+        <v>6.58614447060957E-005</v>
       </c>
       <c r="AG5" s="0" t="n">
-        <v>0.975352692007667</v>
+        <v>0.974952920257409</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3831,27 +3831,27 @@
       </c>
       <c r="O6" s="24" t="n">
         <f aca="false">(L6/$F$2)^(1/$F$3)</f>
-        <v>0.567178737748837</v>
+        <v>0.576449310318848</v>
       </c>
       <c r="P6" s="24" t="n">
         <f aca="false">(M6/$G$2)^(1/$G$3)</f>
-        <v>0.00186008401403519</v>
+        <v>0.00197042454999494</v>
       </c>
       <c r="Q6" s="24" t="n">
         <f aca="false">(N6/$H$2)^(1/$H$3)</f>
-        <v>0.00216458893877017</v>
+        <v>0.00221205008950286</v>
       </c>
       <c r="R6" s="25" t="n">
         <f aca="false">O6*$K6/$I6</f>
-        <v>2.63755908164776</v>
+        <v>2.68067015272062</v>
       </c>
       <c r="S6" s="25" t="n">
         <f aca="false">P6*$K6/$I6</f>
-        <v>0.00864997426264398</v>
+        <v>0.00916309237396392</v>
       </c>
       <c r="T6" s="26" t="n">
         <f aca="false">Q6*$K6/$I6</f>
-        <v>0.0100660177004304</v>
+        <v>0.0102867269421719</v>
       </c>
       <c r="U6" s="27" t="n">
         <v>93.6826</v>
@@ -3910,27 +3910,27 @@
       </c>
       <c r="O7" s="37" t="n">
         <f aca="false">(L7/$F$2)^(1/$F$3)</f>
-        <v>18.3540048831083</v>
+        <v>18.9455173012586</v>
       </c>
       <c r="P7" s="37" t="n">
         <f aca="false">(M7/$G$2)^(1/$G$3)</f>
-        <v>0.375135628008707</v>
+        <v>0.380219766107627</v>
       </c>
       <c r="Q7" s="37" t="n">
         <f aca="false">(N7/$H$2)^(1/$H$3)</f>
-        <v>0.403838866876564</v>
+        <v>0.409644582719245</v>
       </c>
       <c r="R7" s="38" t="n">
         <f aca="false">O7*$K7/$I7</f>
-        <v>75.9322178221505</v>
+        <v>78.3793594713734</v>
       </c>
       <c r="S7" s="38" t="n">
         <f aca="false">P7*$K7/$I7</f>
-        <v>1.55197083144626</v>
+        <v>1.57300438156373</v>
       </c>
       <c r="T7" s="39" t="n">
         <f aca="false">Q7*$K7/$I7</f>
-        <v>1.67071878862487</v>
+        <v>1.69473757268794</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>8.9269</v>
@@ -3938,15 +3938,15 @@
       <c r="V7" s="2"/>
       <c r="W7" s="32" t="n">
         <f aca="false">AVERAGE(R7:R8)/100</f>
-        <v>0.766710988614479</v>
+        <v>0.791429054587144</v>
       </c>
       <c r="X7" s="2" t="n">
         <f aca="false">AVERAGE(S7:S8)/100</f>
-        <v>0.0156877801381957</v>
+        <v>0.015899929607843</v>
       </c>
       <c r="Y7" s="2" t="n">
         <f aca="false">AVERAGE(T7:T8)/100</f>
-        <v>0.0168653695993729</v>
+        <v>0.0171077792581102</v>
       </c>
       <c r="Z7" s="33" t="n">
         <f aca="false">AVERAGE(U7:V8)/100</f>
@@ -3954,16 +3954,16 @@
       </c>
       <c r="AA7" s="2" t="n">
         <f aca="false">SUM(W7:Z7)</f>
-        <v>0.887785138352048</v>
+        <v>0.912957763453097</v>
       </c>
       <c r="AD7" s="0" t="n">
-        <v>0.874355462303404</v>
+        <v>0.874986409175426</v>
       </c>
       <c r="AE7" s="0" t="n">
-        <v>0.0178903086807633</v>
+        <v>0.0175786095204275</v>
       </c>
       <c r="AF7" s="0" t="n">
-        <v>0.0192332290158323</v>
+        <v>0.0189139813041467</v>
       </c>
       <c r="AG7" s="0" t="n">
         <v>0.088521</v>
@@ -4016,27 +4016,27 @@
       </c>
       <c r="O8" s="37" t="n">
         <f aca="false">(L8/$F$2)^(1/$F$3)</f>
-        <v>18.4420079336269</v>
+        <v>19.036762616469</v>
       </c>
       <c r="P8" s="37" t="n">
         <f aca="false">(M8/$G$2)^(1/$G$3)</f>
-        <v>0.377746833226459</v>
+        <v>0.382844257910423</v>
       </c>
       <c r="Q8" s="37" t="n">
         <f aca="false">(N8/$H$2)^(1/$H$3)</f>
-        <v>0.405565882804929</v>
+        <v>0.411393937072035</v>
       </c>
       <c r="R8" s="38" t="n">
         <f aca="false">O8*$K8/$I8</f>
-        <v>77.4099799007454</v>
+        <v>79.9064514460554</v>
       </c>
       <c r="S8" s="38" t="n">
         <f aca="false">P8*$K8/$I8</f>
-        <v>1.58558519619287</v>
+        <v>1.60698154000486</v>
       </c>
       <c r="T8" s="39" t="n">
         <f aca="false">Q8*$K8/$I8</f>
-        <v>1.70235513124971</v>
+        <v>1.7268182789341</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>8.7773</v>
@@ -4097,27 +4097,27 @@
       </c>
       <c r="O9" s="24" t="n">
         <f aca="false">(L9/$F$2)^(1/$F$3)</f>
-        <v>0.986128904402904</v>
+        <v>1.00472264638047</v>
       </c>
       <c r="P9" s="24" t="n">
         <f aca="false">(M9/$G$2)^(1/$G$3)</f>
-        <v>8.84665565062901</v>
+        <v>8.73377281537794</v>
       </c>
       <c r="Q9" s="24" t="n">
         <f aca="false">(N9/$H$2)^(1/$H$3)</f>
-        <v>9.05988432862505</v>
+        <v>9.14968054753829</v>
       </c>
       <c r="R9" s="25" t="n">
         <f aca="false">O9*$K9/$I9</f>
-        <v>4.65807015935386</v>
+        <v>4.74589940182886</v>
       </c>
       <c r="S9" s="25" t="n">
         <f aca="false">P9*$K9/$I9</f>
-        <v>41.7879878708409</v>
+        <v>41.2547754641884</v>
       </c>
       <c r="T9" s="26" t="n">
         <f aca="false">Q9*$K9/$I9</f>
-        <v>42.7951930522905</v>
+        <v>43.2193537131078</v>
       </c>
       <c r="U9" s="27" t="n">
         <v>2.3903</v>
@@ -4125,15 +4125,15 @@
       <c r="V9" s="27"/>
       <c r="W9" s="28" t="n">
         <f aca="false">AVERAGE(R9:R10)/100</f>
-        <v>0.0467030659416649</v>
+        <v>0.0475937981394202</v>
       </c>
       <c r="X9" s="27" t="n">
         <f aca="false">AVERAGE(S9:S10)/100</f>
-        <v>0.419330315121381</v>
+        <v>0.413812242388233</v>
       </c>
       <c r="Y9" s="27" t="n">
         <f aca="false">AVERAGE(T9:T10)/100</f>
-        <v>0.429313037792397</v>
+        <v>0.433538429687698</v>
       </c>
       <c r="Z9" s="29" t="n">
         <f aca="false">AVERAGE(U9:V10)/100</f>
@@ -4141,16 +4141,16 @@
       </c>
       <c r="AA9" s="2" t="n">
         <f aca="false">SUM(W9:Z9)</f>
-        <v>0.919652918855444</v>
+        <v>0.919250970215351</v>
       </c>
       <c r="AD9" s="0" t="n">
-        <v>0.0508941309304672</v>
+        <v>0.0518880903010331</v>
       </c>
       <c r="AE9" s="0" t="n">
-        <v>0.456960405716371</v>
+        <v>0.451149684204952</v>
       </c>
       <c r="AF9" s="0" t="n">
-        <v>0.467838963353162</v>
+        <v>0.472655725494015</v>
       </c>
       <c r="AG9" s="0" t="n">
         <v>0.0243065</v>
@@ -4203,27 +4203,27 @@
       </c>
       <c r="O10" s="24" t="n">
         <f aca="false">(L10/$F$2)^(1/$F$3)</f>
-        <v>1.08464702888529</v>
+        <v>1.10556777192161</v>
       </c>
       <c r="P10" s="24" t="n">
         <f aca="false">(M10/$G$2)^(1/$G$3)</f>
-        <v>9.74681042201461</v>
+        <v>9.61468457019284</v>
       </c>
       <c r="Q10" s="24" t="n">
         <f aca="false">(N10/$H$2)^(1/$H$3)</f>
-        <v>9.97597734752549</v>
+        <v>10.0734771782097</v>
       </c>
       <c r="R10" s="25" t="n">
         <f aca="false">O10*$K10/$I10</f>
-        <v>4.68254302897912</v>
+        <v>4.77286022605518</v>
       </c>
       <c r="S10" s="25" t="n">
         <f aca="false">P10*$K10/$I10</f>
-        <v>42.0780751534353</v>
+        <v>41.5076730134582</v>
       </c>
       <c r="T10" s="26" t="n">
         <f aca="false">Q10*$K10/$I10</f>
-        <v>43.067414506189</v>
+        <v>43.4883322244317</v>
       </c>
       <c r="U10" s="27" t="n">
         <v>2.471</v>
@@ -4282,27 +4282,27 @@
       </c>
       <c r="O11" s="37" t="n">
         <f aca="false">(L11/$F$2)^(1/$F$3)</f>
-        <v>0.0308958006498731</v>
+        <v>0.0309958941506313</v>
       </c>
       <c r="P11" s="37" t="n">
         <f aca="false">(M11/$G$2)^(1/$G$3)</f>
-        <v>0.011340444101167</v>
+        <v>0.0118337723469224</v>
       </c>
       <c r="Q11" s="37" t="n">
         <f aca="false">(N11/$H$2)^(1/$H$3)</f>
-        <v>0.00593320666848319</v>
+        <v>0.0060546349405248</v>
       </c>
       <c r="R11" s="38" t="n">
         <f aca="false">O11*$K11/$I11</f>
-        <v>0.127239877099678</v>
+        <v>0.127652097675519</v>
       </c>
       <c r="S11" s="38" t="n">
         <f aca="false">P11*$K11/$I11</f>
-        <v>0.0467039754056084</v>
+        <v>0.0487356762853195</v>
       </c>
       <c r="T11" s="39" t="n">
         <f aca="false">Q11*$K11/$I11</f>
-        <v>0.024435051736</v>
+        <v>0.0249351364752205</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>97.4397</v>
@@ -4310,15 +4310,15 @@
       <c r="V11" s="2"/>
       <c r="W11" s="32" t="n">
         <f aca="false">AVERAGE(R11:R12)/100</f>
-        <v>0.00127334957867731</v>
+        <v>0.00127757433988938</v>
       </c>
       <c r="X11" s="2" t="n">
         <f aca="false">AVERAGE(S11:S12)/100</f>
-        <v>0.000462548994379192</v>
+        <v>0.000482642843348461</v>
       </c>
       <c r="Y11" s="2" t="n">
         <f aca="false">AVERAGE(T11:T12)/100</f>
-        <v>0.000237586722399035</v>
+        <v>0.000242453077139348</v>
       </c>
       <c r="Z11" s="33" t="n">
         <f aca="false">AVERAGE(U11:V12)/100</f>
@@ -4326,19 +4326,19 @@
       </c>
       <c r="AA11" s="2" t="n">
         <f aca="false">SUM(W11:Z11)</f>
-        <v>0.983872485295456</v>
+        <v>0.983901670260377</v>
       </c>
       <c r="AD11" s="0" t="n">
-        <v>0.00127334957867731</v>
+        <v>0.00127757433988938</v>
       </c>
       <c r="AE11" s="0" t="n">
-        <v>0.000462548994379192</v>
+        <v>0.000482642843348461</v>
       </c>
       <c r="AF11" s="0" t="n">
-        <v>0.000237586722399035</v>
+        <v>0.000242453077139349</v>
       </c>
       <c r="AG11" s="0" t="n">
-        <v>0.998026514704545</v>
+        <v>0.997997329739623</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4388,27 +4388,27 @@
       </c>
       <c r="O12" s="37" t="n">
         <f aca="false">(L12/$F$2)^(1/$F$3)</f>
-        <v>0.0319928103309594</v>
+        <v>0.0321014527066592</v>
       </c>
       <c r="P12" s="37" t="n">
         <f aca="false">(M12/$G$2)^(1/$G$3)</f>
-        <v>0.0115000908578942</v>
+        <v>0.0119989678853619</v>
       </c>
       <c r="Q12" s="37" t="n">
         <f aca="false">(N12/$H$2)^(1/$H$3)</f>
-        <v>0.00579508114148001</v>
+        <v>0.00591388010593754</v>
       </c>
       <c r="R12" s="38" t="n">
         <f aca="false">O12*$K12/$I12</f>
-        <v>0.127430038635783</v>
+        <v>0.127862770302358</v>
       </c>
       <c r="S12" s="38" t="n">
         <f aca="false">P12*$K12/$I12</f>
-        <v>0.0458058234702301</v>
+        <v>0.0477928923843727</v>
       </c>
       <c r="T12" s="39" t="n">
         <f aca="false">Q12*$K12/$I12</f>
-        <v>0.023082292743807</v>
+        <v>0.0235554789526492</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>98.9401</v>
@@ -4469,27 +4469,27 @@
       </c>
       <c r="O13" s="24" t="n">
         <f aca="false">(L13/$F$2)^(1/$F$3)</f>
-        <v>10.3349485228905</v>
+        <v>10.6407331602098</v>
       </c>
       <c r="P13" s="24" t="n">
         <f aca="false">(M13/$G$2)^(1/$G$3)</f>
-        <v>4.77169234756343</v>
+        <v>4.73507174996775</v>
       </c>
       <c r="Q13" s="24" t="n">
         <f aca="false">(N13/$H$2)^(1/$H$3)</f>
-        <v>4.92546532816537</v>
+        <v>4.97858468406881</v>
       </c>
       <c r="R13" s="25" t="n">
         <f aca="false">O13*$K13/$I13</f>
-        <v>45.1833699885048</v>
+        <v>46.5202300971157</v>
       </c>
       <c r="S13" s="25" t="n">
         <f aca="false">P13*$K13/$I13</f>
-        <v>20.86136571786</v>
+        <v>20.7012640969665</v>
       </c>
       <c r="T13" s="26" t="n">
         <f aca="false">Q13*$K13/$I13</f>
-        <v>21.5336459388387</v>
+        <v>21.7658784948132</v>
       </c>
       <c r="U13" s="27" t="n">
         <v>4.4629</v>
@@ -4497,15 +4497,15 @@
       <c r="V13" s="27"/>
       <c r="W13" s="28" t="n">
         <f aca="false">AVERAGE(R13:R14)/100</f>
-        <v>0.451376662918962</v>
+        <v>0.46475215736729</v>
       </c>
       <c r="X13" s="27" t="n">
         <f aca="false">AVERAGE(S13:S14)/100</f>
-        <v>0.208428171601451</v>
+        <v>0.206811412346901</v>
       </c>
       <c r="Y13" s="27" t="n">
         <f aca="false">AVERAGE(T13:T14)/100</f>
-        <v>0.215177791899499</v>
+        <v>0.217495282534139</v>
       </c>
       <c r="Z13" s="29" t="n">
         <f aca="false">AVERAGE(U13:V14)/100</f>
@@ -4513,16 +4513,16 @@
       </c>
       <c r="AA13" s="2" t="n">
         <f aca="false">SUM(W13:Z13)</f>
-        <v>0.919087626419912</v>
+        <v>0.933163852248331</v>
       </c>
       <c r="AD13" s="0" t="n">
-        <v>0.493116871321574</v>
+        <v>0.499690501189135</v>
       </c>
       <c r="AE13" s="0" t="n">
-        <v>0.227702174965648</v>
+        <v>0.222358727440152</v>
       </c>
       <c r="AF13" s="0" t="n">
-        <v>0.235075953712777</v>
+        <v>0.233845771370712</v>
       </c>
       <c r="AG13" s="0" t="n">
         <v>0.044105</v>
@@ -4575,27 +4575,27 @@
       </c>
       <c r="O14" s="24" t="n">
         <f aca="false">(L14/$F$2)^(1/$F$3)</f>
-        <v>10.5407711689798</v>
+        <v>10.8536000623938</v>
       </c>
       <c r="P14" s="24" t="n">
         <f aca="false">(M14/$G$2)^(1/$G$3)</f>
-        <v>4.86791519964862</v>
+        <v>4.82975355799796</v>
       </c>
       <c r="Q14" s="24" t="n">
         <f aca="false">(N14/$H$2)^(1/$H$3)</f>
-        <v>5.02632233533233</v>
+        <v>5.08038335468879</v>
       </c>
       <c r="R14" s="25" t="n">
         <f aca="false">O14*$K14/$I14</f>
-        <v>45.0919625952876</v>
+        <v>46.4302013763423</v>
       </c>
       <c r="S14" s="25" t="n">
         <f aca="false">P14*$K14/$I14</f>
-        <v>20.8242686024303</v>
+        <v>20.6610183724138</v>
       </c>
       <c r="T14" s="26" t="n">
         <f aca="false">Q14*$K14/$I14</f>
-        <v>21.5019124410611</v>
+        <v>21.7331780120146</v>
       </c>
       <c r="U14" s="27" t="n">
         <v>4.3581</v>
@@ -4654,27 +4654,27 @@
       </c>
       <c r="O15" s="37" t="n">
         <f aca="false">(L15/$F$2)^(1/$F$3)</f>
-        <v>0.322592018903776</v>
+        <v>0.327040726022503</v>
       </c>
       <c r="P15" s="37" t="n">
         <f aca="false">(M15/$G$2)^(1/$G$3)</f>
-        <v>0.00415851482801292</v>
+        <v>0.00437580054708265</v>
       </c>
       <c r="Q15" s="37" t="n">
         <f aca="false">(N15/$H$2)^(1/$H$3)</f>
-        <v>0.00383082306898614</v>
+        <v>0.00391165036026433</v>
       </c>
       <c r="R15" s="38" t="n">
         <f aca="false">O15*$K15/$I15</f>
-        <v>1.32797758416047</v>
+        <v>1.34629106678239</v>
       </c>
       <c r="S15" s="38" t="n">
         <f aca="false">P15*$K15/$I15</f>
-        <v>0.0171188812846834</v>
+        <v>0.0180133564960149</v>
       </c>
       <c r="T15" s="39" t="n">
         <f aca="false">Q15*$K15/$I15</f>
-        <v>0.015769910184963</v>
+        <v>0.0161026426294003</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>99.7309</v>
@@ -4682,15 +4682,15 @@
       <c r="V15" s="2"/>
       <c r="W15" s="32" t="n">
         <f aca="false">AVERAGE(R15:R16)/100</f>
-        <v>0.0133929691462078</v>
+        <v>0.0135775328502213</v>
       </c>
       <c r="X15" s="2" t="n">
         <f aca="false">AVERAGE(S15:S16)/100</f>
-        <v>0.000176970281941239</v>
+        <v>0.000186181812273992</v>
       </c>
       <c r="Y15" s="2" t="n">
         <f aca="false">AVERAGE(T15:T16)/100</f>
-        <v>0.000163486295835889</v>
+        <v>0.000166929647062546</v>
       </c>
       <c r="Z15" s="33" t="n">
         <f aca="false">AVERAGE(U15:V16)/100</f>
@@ -4698,19 +4698,19 @@
       </c>
       <c r="AA15" s="2" t="n">
         <f aca="false">SUM(W15:Z15)</f>
-        <v>1.00766992572399</v>
+        <v>1.00786714430956</v>
       </c>
       <c r="AD15" s="0" t="n">
-        <v>0.0133929691462078</v>
+        <v>0.0135775328502213</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>0.000176970281941239</v>
+        <v>0.000186181812273992</v>
       </c>
       <c r="AF15" s="0" t="n">
-        <v>0.000163486295835889</v>
+        <v>0.000166929647062546</v>
       </c>
       <c r="AG15" s="0" t="n">
-        <v>0.986266574276015</v>
+        <v>0.986069355690442</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4760,27 +4760,27 @@
       </c>
       <c r="O16" s="37" t="n">
         <f aca="false">(L16/$F$2)^(1/$F$3)</f>
-        <v>0.321199184990046</v>
+        <v>0.325622400385863</v>
       </c>
       <c r="P16" s="37" t="n">
         <f aca="false">(M16/$G$2)^(1/$G$3)</f>
-        <v>0.00434614300708547</v>
+        <v>0.00457155307401869</v>
       </c>
       <c r="Q16" s="37" t="n">
         <f aca="false">(N16/$H$2)^(1/$H$3)</f>
-        <v>0.00402560736029281</v>
+        <v>0.0041102553363339</v>
       </c>
       <c r="R16" s="38" t="n">
         <f aca="false">O16*$K16/$I16</f>
-        <v>1.3506162450811</v>
+        <v>1.36921550326186</v>
       </c>
       <c r="S16" s="38" t="n">
         <f aca="false">P16*$K16/$I16</f>
-        <v>0.0182751751035643</v>
+        <v>0.0192230059587835</v>
       </c>
       <c r="T16" s="39" t="n">
         <f aca="false">Q16*$K16/$I16</f>
-        <v>0.0169273489822149</v>
+        <v>0.0172832867831089</v>
       </c>
       <c r="U16" s="2" t="n">
         <v>99.0564</v>
@@ -4841,27 +4841,27 @@
       </c>
       <c r="O17" s="24" t="n">
         <f aca="false">(L17/$F$2)^(1/$F$3)</f>
-        <v>6.62937681901853</v>
+        <v>6.81202007926486</v>
       </c>
       <c r="P17" s="24" t="n">
         <f aca="false">(M17/$G$2)^(1/$G$3)</f>
-        <v>7.97993638578231</v>
+        <v>7.88487628023512</v>
       </c>
       <c r="Q17" s="24" t="n">
         <f aca="false">(N17/$H$2)^(1/$H$3)</f>
-        <v>8.21969593388061</v>
+        <v>8.3023105118904</v>
       </c>
       <c r="R17" s="25" t="n">
         <f aca="false">O17*$K17/$I17</f>
-        <v>26.185860130206</v>
+        <v>26.9072960957729</v>
       </c>
       <c r="S17" s="25" t="n">
         <f aca="false">P17*$K17/$I17</f>
-        <v>31.5205340940288</v>
+        <v>31.1450492338712</v>
       </c>
       <c r="T17" s="26" t="n">
         <f aca="false">Q17*$K17/$I17</f>
-        <v>32.4675778604009</v>
+        <v>32.7939032215229</v>
       </c>
       <c r="U17" s="27" t="n">
         <v>3.3914</v>
@@ -4869,15 +4869,15 @@
       <c r="V17" s="27"/>
       <c r="W17" s="32" t="n">
         <f aca="false">AVERAGE(R17:R18)/100</f>
-        <v>0.265342856726465</v>
+        <v>0.272676553884793</v>
       </c>
       <c r="X17" s="2" t="n">
         <f aca="false">AVERAGE(S17:S18)/100</f>
-        <v>0.319428671211128</v>
+        <v>0.315572851109972</v>
       </c>
       <c r="Y17" s="2" t="n">
         <f aca="false">AVERAGE(T17:T18)/100</f>
-        <v>0.328949143173593</v>
+        <v>0.332246370942616</v>
       </c>
       <c r="Z17" s="33" t="n">
         <f aca="false">AVERAGE(U17:V18)/100</f>
@@ -4885,16 +4885,16 @@
       </c>
       <c r="AA17" s="2" t="n">
         <f aca="false">SUM(W17:Z17)</f>
-        <v>0.947132171111186</v>
+        <v>0.95390727593738</v>
       </c>
       <c r="AD17" s="0" t="n">
-        <v>0.280695580146002</v>
+        <v>0.286330505901855</v>
       </c>
       <c r="AE17" s="0" t="n">
-        <v>0.337910796947907</v>
+        <v>0.331374783859803</v>
       </c>
       <c r="AF17" s="0" t="n">
-        <v>0.347982122906091</v>
+        <v>0.348883210238342</v>
       </c>
       <c r="AG17" s="0" t="n">
         <v>0.0334115</v>
@@ -4947,27 +4947,27 @@
       </c>
       <c r="O18" s="24" t="n">
         <f aca="false">(L18/$F$2)^(1/$F$3)</f>
-        <v>6.88541325393628</v>
+        <v>7.07630629008214</v>
       </c>
       <c r="P18" s="24" t="n">
         <f aca="false">(M18/$G$2)^(1/$G$3)</f>
-        <v>8.28963181145322</v>
+        <v>8.18828732609682</v>
       </c>
       <c r="Q18" s="24" t="n">
         <f aca="false">(N18/$H$2)^(1/$H$3)</f>
-        <v>8.53475920999041</v>
+        <v>8.62008059634533</v>
       </c>
       <c r="R18" s="25" t="n">
         <f aca="false">O18*$K18/$I18</f>
-        <v>26.882711215087</v>
+        <v>27.6280146811856</v>
       </c>
       <c r="S18" s="25" t="n">
         <f aca="false">P18*$K18/$I18</f>
-        <v>32.3652001481969</v>
+        <v>31.9695209881232</v>
       </c>
       <c r="T18" s="26" t="n">
         <f aca="false">Q18*$K18/$I18</f>
-        <v>33.3222507743178</v>
+        <v>33.6553709670003</v>
       </c>
       <c r="U18" s="27" t="n">
         <v>3.2909</v>
@@ -5026,27 +5026,27 @@
       </c>
       <c r="O19" s="37" t="n">
         <f aca="false">(L19/$F$2)^(1/$F$3)</f>
-        <v>0.208651158950355</v>
+        <v>0.211117905439826</v>
       </c>
       <c r="P19" s="37" t="n">
         <f aca="false">(M19/$G$2)^(1/$G$3)</f>
-        <v>0.00895906729416209</v>
+        <v>0.00936715949233744</v>
       </c>
       <c r="Q19" s="37" t="n">
         <f aca="false">(N19/$H$2)^(1/$H$3)</f>
-        <v>0.00674438228713089</v>
+        <v>0.00688116134365743</v>
       </c>
       <c r="R19" s="38" t="n">
         <f aca="false">O19*$K19/$I19</f>
-        <v>0.802354824678084</v>
+        <v>0.811840542164828</v>
       </c>
       <c r="S19" s="38" t="n">
         <f aca="false">P19*$K19/$I19</f>
-        <v>0.0344515261944791</v>
+        <v>0.0360208189114075</v>
       </c>
       <c r="T19" s="39" t="n">
         <f aca="false">Q19*$K19/$I19</f>
-        <v>0.0259350951836334</v>
+        <v>0.0264610703877543</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>98.2495</v>
@@ -5054,15 +5054,15 @@
       <c r="V19" s="2"/>
       <c r="W19" s="32" t="n">
         <f aca="false">AVERAGE(R19:R20)/100</f>
-        <v>0.00825535359714553</v>
+        <v>0.00835405281883261</v>
       </c>
       <c r="X19" s="2" t="n">
         <f aca="false">AVERAGE(S19:S20)/100</f>
-        <v>0.00078494631571017</v>
+        <v>0.000813964789591377</v>
       </c>
       <c r="Y19" s="2" t="n">
         <f aca="false">AVERAGE(T19:T20)/100</f>
-        <v>0.000729409742336783</v>
+        <v>0.00074287382179994</v>
       </c>
       <c r="Z19" s="33" t="n">
         <f aca="false">AVERAGE(U19:V20)/100</f>
@@ -5070,19 +5070,19 @@
       </c>
       <c r="AA19" s="2" t="n">
         <f aca="false">SUM(W19:Z19)</f>
-        <v>0.997962209655192</v>
+        <v>0.998103391430224</v>
       </c>
       <c r="AD19" s="0" t="n">
-        <v>0.00825535359714553</v>
+        <v>0.00835405281883261</v>
       </c>
       <c r="AE19" s="0" t="n">
-        <v>0.00078494631571017</v>
+        <v>0.000813964789591377</v>
       </c>
       <c r="AF19" s="0" t="n">
-        <v>0.000729409742336783</v>
+        <v>0.00074287382179994</v>
       </c>
       <c r="AG19" s="0" t="n">
-        <v>0.990230290344808</v>
+        <v>0.990089108569776</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5132,27 +5132,27 @@
       </c>
       <c r="O20" s="37" t="n">
         <f aca="false">(L20/$F$2)^(1/$F$3)</f>
-        <v>0.221003973103705</v>
+        <v>0.223674127850097</v>
       </c>
       <c r="P20" s="37" t="n">
         <f aca="false">(M20/$G$2)^(1/$G$3)</f>
-        <v>0.031908589067359</v>
+        <v>0.0330112191519542</v>
       </c>
       <c r="Q20" s="37" t="n">
         <f aca="false">(N20/$H$2)^(1/$H$3)</f>
-        <v>0.0312339279857207</v>
+        <v>0.0317981690989192</v>
       </c>
       <c r="R20" s="38" t="n">
         <f aca="false">O20*$K20/$I20</f>
-        <v>0.848715894751023</v>
+        <v>0.858970021601694</v>
       </c>
       <c r="S20" s="38" t="n">
         <f aca="false">P20*$K20/$I20</f>
-        <v>0.122537736947555</v>
+        <v>0.126772139006868</v>
       </c>
       <c r="T20" s="39" t="n">
         <f aca="false">Q20*$K20/$I20</f>
-        <v>0.119946853283723</v>
+        <v>0.122113693972234</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>99.389</v>
@@ -5213,27 +5213,27 @@
       </c>
       <c r="O21" s="24" t="n">
         <f aca="false">(L21/$F$2)^(1/$F$3)</f>
-        <v>14.9827672067849</v>
+        <v>15.4516395951095</v>
       </c>
       <c r="P21" s="24" t="n">
         <f aca="false">(M21/$G$2)^(1/$G$3)</f>
-        <v>2.91283159486088</v>
+        <v>2.90237501841678</v>
       </c>
       <c r="Q21" s="24" t="n">
         <f aca="false">(N21/$H$2)^(1/$H$3)</f>
-        <v>2.98504892019895</v>
+        <v>3.01938526164188</v>
       </c>
       <c r="R21" s="25" t="n">
         <f aca="false">O21*$K21/$I21</f>
-        <v>60.52260046916</v>
+        <v>62.41660147965</v>
       </c>
       <c r="S21" s="25" t="n">
         <f aca="false">P21*$K21/$I21</f>
-        <v>11.7663273023342</v>
+        <v>11.72408816255</v>
       </c>
       <c r="T21" s="26" t="n">
         <f aca="false">Q21*$K21/$I21</f>
-        <v>12.0580478014959</v>
+        <v>12.1967487935118</v>
       </c>
       <c r="U21" s="27" t="n">
         <v>5.883</v>
@@ -5241,15 +5241,15 @@
       <c r="V21" s="27"/>
       <c r="W21" s="28" t="n">
         <f aca="false">AVERAGE(R21:R22)/100</f>
-        <v>0.610501671467566</v>
+        <v>0.629603891857857</v>
       </c>
       <c r="X21" s="27" t="n">
         <f aca="false">AVERAGE(S21:S22)/100</f>
-        <v>0.118980912136057</v>
+        <v>0.118552380297014</v>
       </c>
       <c r="Y21" s="27" t="n">
         <f aca="false">AVERAGE(T21:T22)/100</f>
-        <v>0.121720499722465</v>
+        <v>0.123120675031439</v>
       </c>
       <c r="Z21" s="29" t="n">
         <f aca="false">AVERAGE(U21:V22)/100</f>
@@ -5257,16 +5257,16 @@
       </c>
       <c r="AA21" s="2" t="n">
         <f aca="false">SUM(W21:Z21)</f>
-        <v>0.909303083326088</v>
+        <v>0.92937694718631</v>
       </c>
       <c r="AD21" s="0" t="n">
-        <v>0.675551505415555</v>
+        <v>0.680637663668273</v>
       </c>
       <c r="AE21" s="0" t="n">
-        <v>0.131658499993966</v>
+        <v>0.128161874777434</v>
       </c>
       <c r="AF21" s="0" t="n">
-        <v>0.134689994590479</v>
+        <v>0.133100461554292</v>
       </c>
       <c r="AG21" s="0" t="n">
         <v>0.0581</v>
@@ -5319,27 +5319,27 @@
       </c>
       <c r="O22" s="24" t="n">
         <f aca="false">(L22/$F$2)^(1/$F$3)</f>
-        <v>14.9522529206475</v>
+        <v>15.4200301867884</v>
       </c>
       <c r="P22" s="24" t="n">
         <f aca="false">(M22/$G$2)^(1/$G$3)</f>
-        <v>2.92107918324809</v>
+        <v>2.9105245079326</v>
       </c>
       <c r="Q22" s="24" t="n">
         <f aca="false">(N22/$H$2)^(1/$H$3)</f>
-        <v>2.98328872514795</v>
+        <v>3.01760734368739</v>
       </c>
       <c r="R22" s="25" t="n">
         <f aca="false">O22*$K22/$I22</f>
-        <v>61.5777338243533</v>
+        <v>63.5041768919214</v>
       </c>
       <c r="S22" s="25" t="n">
         <f aca="false">P22*$K22/$I22</f>
-        <v>12.0298551248771</v>
+        <v>11.9863878968527</v>
       </c>
       <c r="T22" s="26" t="n">
         <f aca="false">Q22*$K22/$I22</f>
-        <v>12.286052142997</v>
+        <v>12.4273862127761</v>
       </c>
       <c r="U22" s="27" t="n">
         <v>5.737</v>
@@ -5398,27 +5398,27 @@
       </c>
       <c r="O23" s="37" t="n">
         <f aca="false">(L23/$F$2)^(1/$F$3)</f>
-        <v>0.503555722644206</v>
+        <v>0.511514873212641</v>
       </c>
       <c r="P23" s="37" t="n">
         <f aca="false">(M23/$G$2)^(1/$G$3)</f>
-        <v>0.00909733194754559</v>
+        <v>0.00951050989779457</v>
       </c>
       <c r="Q23" s="37" t="n">
         <f aca="false">(N23/$H$2)^(1/$H$3)</f>
-        <v>0.00972342265882325</v>
+        <v>0.00991547244067781</v>
       </c>
       <c r="R23" s="38" t="n">
         <f aca="false">O23*$K23/$I23</f>
-        <v>1.9549958661417</v>
+        <v>1.98589633208732</v>
       </c>
       <c r="S23" s="38" t="n">
         <f aca="false">P23*$K23/$I23</f>
-        <v>0.0353193212798355</v>
+        <v>0.0369234360746709</v>
       </c>
       <c r="T23" s="39" t="n">
         <f aca="false">Q23*$K23/$I23</f>
-        <v>0.0377500448270731</v>
+        <v>0.0384956555166856</v>
       </c>
       <c r="U23" s="2" t="n">
         <v>98.2209</v>
@@ -5426,15 +5426,15 @@
       <c r="V23" s="2"/>
       <c r="W23" s="32" t="n">
         <f aca="false">AVERAGE(R23:R24)/100</f>
-        <v>0.0190419585548697</v>
+        <v>0.0193409846827522</v>
       </c>
       <c r="X23" s="2" t="n">
         <f aca="false">AVERAGE(S23:S24)/100</f>
-        <v>0.000267103120469415</v>
+        <v>0.000279756625784368</v>
       </c>
       <c r="Y23" s="2" t="n">
         <f aca="false">AVERAGE(T23:T24)/100</f>
-        <v>0.000286948741310364</v>
+        <v>0.000292708191267029</v>
       </c>
       <c r="Z23" s="33" t="n">
         <f aca="false">AVERAGE(U23:V24)/100</f>
@@ -5442,19 +5442,19 @@
       </c>
       <c r="AA23" s="2" t="n">
         <f aca="false">SUM(W23:Z23)</f>
-        <v>0.998305510416649</v>
+        <v>0.998622949499804</v>
       </c>
       <c r="AD23" s="0" t="n">
-        <v>0.0190419585548697</v>
+        <v>0.0193409846827522</v>
       </c>
       <c r="AE23" s="0" t="n">
-        <v>0.000267103120469416</v>
+        <v>0.000279756625784368</v>
       </c>
       <c r="AF23" s="0" t="n">
-        <v>0.000286948741310364</v>
+        <v>0.000292708191267029</v>
       </c>
       <c r="AG23" s="0" t="n">
-        <v>0.980403989583351</v>
+        <v>0.980086550500196</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5504,27 +5504,27 @@
       </c>
       <c r="O24" s="37" t="n">
         <f aca="false">(L24/$F$2)^(1/$F$3)</f>
-        <v>0.480709203604781</v>
+        <v>0.488206136341134</v>
       </c>
       <c r="P24" s="37" t="n">
         <f aca="false">(M24/$G$2)^(1/$G$3)</f>
-        <v>0.00469487556272006</v>
+        <v>0.00493520120512283</v>
       </c>
       <c r="Q24" s="37" t="n">
         <f aca="false">(N24/$H$2)^(1/$H$3)</f>
-        <v>0.00509388548787176</v>
+        <v>0.00519926081830414</v>
       </c>
       <c r="R24" s="38" t="n">
         <f aca="false">O24*$K24/$I24</f>
-        <v>1.85339584483225</v>
+        <v>1.88230060446312</v>
       </c>
       <c r="S24" s="38" t="n">
         <f aca="false">P24*$K24/$I24</f>
-        <v>0.0181013028140476</v>
+        <v>0.0190278890822027</v>
       </c>
       <c r="T24" s="39" t="n">
         <f aca="false">Q24*$K24/$I24</f>
-        <v>0.0196397034349997</v>
+        <v>0.0200459827367203</v>
       </c>
       <c r="U24" s="42" t="n">
         <v>97.521</v>
@@ -5579,30 +5579,30 @@
       </c>
       <c r="P25" s="1" t="n">
         <f aca="false">(M25/$G$2)^(1/$G$3)</f>
-        <v>16.0631389440853</v>
+        <v>15.7796435014962</v>
       </c>
       <c r="Q25" s="1" t="n">
         <f aca="false">(N25/$H$2)^(1/$H$3)</f>
-        <v>16.6454516520611</v>
+        <v>16.7959363703835</v>
       </c>
       <c r="S25" s="1" t="n">
         <f aca="false">P25*$K25/$I25</f>
-        <v>47.0093939329019</v>
+        <v>46.1797336164941</v>
       </c>
       <c r="T25" s="1" t="n">
         <f aca="false">Q25*$K25/$I25</f>
-        <v>48.7135544694357</v>
+        <v>49.1539537854801</v>
       </c>
       <c r="U25" s="1" t="n">
         <v>2.1978</v>
       </c>
       <c r="X25" s="1" t="n">
         <f aca="false">AVERAGE(S25:S26)/100</f>
-        <v>0.473015233292863</v>
+        <v>0.464445317991907</v>
       </c>
       <c r="Y25" s="1" t="n">
         <f aca="false">AVERAGE(T25:T26)/100</f>
-        <v>0.48992493893955</v>
+        <v>0.494314292623636</v>
       </c>
       <c r="Z25" s="1" t="n">
         <f aca="false">AVERAGE(U25:V26)/100</f>
@@ -5610,19 +5610,19 @@
       </c>
       <c r="AA25" s="1" t="n">
         <f aca="false">SUM(W25:Z25)</f>
-        <v>0.985058172232412</v>
+        <v>0.980877610615543</v>
       </c>
       <c r="AE25" s="1" t="n">
         <f aca="false">IFERROR(X25/$AA25,"")</f>
-        <v>0.480190151837307</v>
+        <v>0.473499764869185</v>
       </c>
       <c r="AF25" s="1" t="n">
         <f aca="false">IFERROR(Y25/$AA25,"")</f>
-        <v>0.497356351888585</v>
+        <v>0.503951040653719</v>
       </c>
       <c r="AG25" s="1" t="n">
         <f aca="false">IFERROR(Z25/$AA25,"")</f>
-        <v>0.0224534962741079</v>
+        <v>0.0225491944770969</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5666,19 +5666,19 @@
       </c>
       <c r="P26" s="1" t="n">
         <f aca="false">(M26/$G$2)^(1/$G$3)</f>
-        <v>18.0033928694877</v>
+        <v>17.6688774694716</v>
       </c>
       <c r="Q26" s="1" t="n">
         <f aca="false">(N26/$H$2)^(1/$H$3)</f>
-        <v>18.6380519349549</v>
+        <v>18.8035355531748</v>
       </c>
       <c r="S26" s="1" t="n">
         <f aca="false">P26*$K26/$I26</f>
-        <v>47.5936527256707</v>
+        <v>46.7093299818873</v>
       </c>
       <c r="T26" s="1" t="n">
         <f aca="false">Q26*$K26/$I26</f>
-        <v>49.2714333184743</v>
+        <v>49.7089047392471</v>
       </c>
       <c r="U26" s="1" t="n">
         <v>2.2258</v>
@@ -5725,27 +5725,27 @@
       </c>
       <c r="P27" s="1" t="n">
         <f aca="false">(M27/$G$2)^(1/$G$3)</f>
-        <v>0.0455254879098827</v>
+        <v>0.0469595572572974</v>
       </c>
       <c r="Q27" s="1" t="n">
         <f aca="false">(N27/$H$2)^(1/$H$3)</f>
-        <v>0.023962424894358</v>
+        <v>0.0244044767074111</v>
       </c>
       <c r="S27" s="1" t="n">
         <f aca="false">P27*$K27/$I27</f>
-        <v>0.0975900130089038</v>
+        <v>0.100664133742039</v>
       </c>
       <c r="T27" s="1" t="n">
         <f aca="false">Q27*$K27/$I27</f>
-        <v>0.0513666841263581</v>
+        <v>0.0523142817066818</v>
       </c>
       <c r="X27" s="1" t="n">
         <f aca="false">AVERAGE(S27:S28)/100</f>
-        <v>0.00355303269532338</v>
+        <v>0.00362468765950455</v>
       </c>
       <c r="Y27" s="1" t="n">
         <f aca="false">AVERAGE(T27:T28)/100</f>
-        <v>0.00295460225738688</v>
+        <v>0.00300111521001261</v>
       </c>
       <c r="Z27" s="1" t="e">
         <f aca="false">AVERAGE(U27:V28)/100</f>
@@ -5809,19 +5809,19 @@
       </c>
       <c r="P28" s="1" t="n">
         <f aca="false">(M28/$G$2)^(1/$G$3)</f>
-        <v>0.212382977141635</v>
+        <v>0.216282982947256</v>
       </c>
       <c r="Q28" s="1" t="n">
         <f aca="false">(N28/$H$2)^(1/$H$3)</f>
-        <v>0.186931396736226</v>
+        <v>0.189826030404646</v>
       </c>
       <c r="S28" s="1" t="n">
         <f aca="false">P28*$K28/$I28</f>
-        <v>0.613016526055772</v>
+        <v>0.624273398158871</v>
       </c>
       <c r="T28" s="1" t="n">
         <f aca="false">Q28*$K28/$I28</f>
-        <v>0.539553767351019</v>
+        <v>0.547908760295841</v>
       </c>
     </row>
   </sheetData>
@@ -5882,13 +5882,13 @@
         <v>2</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>157.651809</v>
+        <v>154.574631</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>156.413729</v>
+        <v>155.54848</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>164.347912</v>
+        <v>162.845817</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5896,13 +5896,13 @@
         <v>3</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>1.05643576</v>
+        <v>1.05174512</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.03759299</v>
+        <v>1.046301</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.02652889</v>
+        <v>1.02796306</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>4</v>
@@ -6054,27 +6054,27 @@
       </c>
       <c r="O5" s="24" t="n">
         <f aca="false">(L5/$F$2)^(1/$F$3)</f>
-        <v>0.372486743957617</v>
+        <v>0.377865804895652</v>
       </c>
       <c r="P5" s="47" t="n">
         <f aca="false">(M5/$G$2)^(1/$G$3)</f>
-        <v>0.000341765208880952</v>
+        <v>0.000367179946216064</v>
       </c>
       <c r="Q5" s="26" t="n">
         <f aca="false">(N5/$H$2)^(1/$H$3)</f>
-        <v>0.000281179258271366</v>
+        <v>0.000286956864926806</v>
       </c>
       <c r="R5" s="25" t="n">
         <f aca="false">O5*$K5/$I5</f>
-        <v>2.10835034754425</v>
+        <v>2.13879692096501</v>
       </c>
       <c r="S5" s="47" t="n">
         <f aca="false">P5*$K5/$I5</f>
-        <v>0.00193446024217355</v>
+        <v>0.00207831279843882</v>
       </c>
       <c r="T5" s="26" t="n">
         <f aca="false">Q5*$K5/$I5</f>
-        <v>0.00159153150149719</v>
+        <v>0.00162423392432854</v>
       </c>
       <c r="U5" s="27" t="n">
         <v>94.8602</v>
@@ -6082,15 +6082,15 @@
       <c r="V5" s="27"/>
       <c r="W5" s="48" t="n">
         <f aca="false">AVERAGE(R5:R6)/100</f>
-        <v>0.0214107577343211</v>
+        <v>0.0217205401206323</v>
       </c>
       <c r="X5" s="49" t="n">
         <f aca="false">AVERAGE(S5:S6)/100</f>
-        <v>1.96696198251342E-005</v>
+        <v>2.11310192269882E-005</v>
       </c>
       <c r="Y5" s="49" t="n">
         <f aca="false">AVERAGE(T5:T6)/100</f>
-        <v>1.60219079255277E-005</v>
+        <v>1.63511826991334E-005</v>
       </c>
       <c r="Z5" s="50" t="n">
         <f aca="false">AVERAGE(U5:V6)/100</f>
@@ -6098,19 +6098,19 @@
       </c>
       <c r="AA5" s="2" t="n">
         <f aca="false">SUM(W5:Z5)</f>
-        <v>0.996481449262072</v>
+        <v>0.996793022322558</v>
       </c>
       <c r="AD5" s="0" t="n">
-        <v>0.0214107577343211</v>
+        <v>0.0217205401206323</v>
       </c>
       <c r="AE5" s="0" t="n">
-        <v>1.96696198251342E-005</v>
+        <v>2.11310192269882E-005</v>
       </c>
       <c r="AF5" s="0" t="n">
-        <v>1.60219079255277E-005</v>
+        <v>1.63511826991334E-005</v>
       </c>
       <c r="AG5" s="0" t="n">
-        <v>0.978553550737928</v>
+        <v>0.978241977677442</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6160,27 +6160,27 @@
       </c>
       <c r="O6" s="24" t="n">
         <f aca="false">(L6/$F$2)^(1/$F$3)</f>
-        <v>0.376988752212178</v>
+        <v>0.38245331784736</v>
       </c>
       <c r="P6" s="47" t="n">
         <f aca="false">(M6/$G$2)^(1/$G$3)</f>
-        <v>0.000346754493560764</v>
+        <v>0.000372495316468693</v>
       </c>
       <c r="Q6" s="26" t="n">
         <f aca="false">(N6/$H$2)^(1/$H$3)</f>
-        <v>0.000279706507069288</v>
+        <v>0.000285455943417801</v>
       </c>
       <c r="R6" s="25" t="n">
         <f aca="false">O6*$K6/$I6</f>
-        <v>2.17380119931997</v>
+        <v>2.20531110316144</v>
       </c>
       <c r="S6" s="47" t="n">
         <f aca="false">P6*$K6/$I6</f>
-        <v>0.00199946372285329</v>
+        <v>0.00214789104695883</v>
       </c>
       <c r="T6" s="26" t="n">
         <f aca="false">Q6*$K6/$I6</f>
-        <v>0.00161285008360835</v>
+        <v>0.00164600261549815</v>
       </c>
       <c r="U6" s="27" t="n">
         <v>97.836</v>
@@ -6239,27 +6239,27 @@
       </c>
       <c r="O7" s="52" t="n">
         <f aca="false">(L7/$F$2)^(1/$F$3)</f>
-        <v>13.9156050550325</v>
+        <v>14.3463530972446</v>
       </c>
       <c r="P7" s="53" t="n">
         <f aca="false">(M7/$G$2)^(1/$G$3)</f>
-        <v>0.37730773810131</v>
+        <v>0.382402939128063</v>
       </c>
       <c r="Q7" s="54" t="n">
         <f aca="false">(N7/$H$2)^(1/$H$3)</f>
-        <v>0.357124409725781</v>
+        <v>0.360846530718288</v>
       </c>
       <c r="R7" s="55" t="n">
         <f aca="false">O7*$K7/$I7</f>
-        <v>77.6036093786835</v>
+        <v>80.0057760596339</v>
       </c>
       <c r="S7" s="53" t="n">
         <f aca="false">P7*$K7/$I7</f>
-        <v>2.10414439094617</v>
+        <v>2.13255896498893</v>
       </c>
       <c r="T7" s="54" t="n">
         <f aca="false">Q7*$K7/$I7</f>
-        <v>1.99158736413907</v>
+        <v>2.01234463789184</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>8.024</v>
@@ -6267,15 +6267,15 @@
       <c r="V7" s="2"/>
       <c r="W7" s="51" t="n">
         <f aca="false">AVERAGE(R7:R8)/100</f>
-        <v>0.783593498343663</v>
+        <v>0.807803528951634</v>
       </c>
       <c r="X7" s="0" t="n">
         <f aca="false">AVERAGE(S7:S8)/100</f>
-        <v>0.0212708116859395</v>
+        <v>0.0215601205502776</v>
       </c>
       <c r="Y7" s="1" t="n">
         <f aca="false">AVERAGE(T7:T8)/100</f>
-        <v>0.0201387707454584</v>
+        <v>0.0203489853694609</v>
       </c>
       <c r="Z7" s="33" t="n">
         <f aca="false">AVERAGE(U7:V8)/100</f>
@@ -6283,16 +6283,16 @@
       </c>
       <c r="AA7" s="2" t="n">
         <f aca="false">SUM(W7:Z7)</f>
-        <v>0.905077080775061</v>
+        <v>0.929786634871372</v>
       </c>
       <c r="AD7" s="0" t="n">
-        <v>0.873751928150476</v>
+        <v>0.874553865245104</v>
       </c>
       <c r="AE7" s="0" t="n">
-        <v>0.0237181813825671</v>
+        <v>0.0233416741653337</v>
       </c>
       <c r="AF7" s="0" t="n">
-        <v>0.0224558904669567</v>
+        <v>0.022030460589562</v>
       </c>
       <c r="AG7" s="0" t="n">
         <v>0.080074</v>
@@ -6345,27 +6345,27 @@
       </c>
       <c r="O8" s="52" t="n">
         <f aca="false">(L8/$F$2)^(1/$F$3)</f>
-        <v>13.5712629047885</v>
+        <v>13.9897886547188</v>
       </c>
       <c r="P8" s="53" t="n">
         <f aca="false">(M8/$G$2)^(1/$G$3)</f>
-        <v>0.368810282481974</v>
+        <v>0.373861602977176</v>
       </c>
       <c r="Q8" s="54" t="n">
         <f aca="false">(N8/$H$2)^(1/$H$3)</f>
-        <v>0.349280455287119</v>
+        <v>0.352931758286447</v>
       </c>
       <c r="R8" s="55" t="n">
         <f aca="false">O8*$K8/$I8</f>
-        <v>79.1150902900492</v>
+        <v>81.5549297306929</v>
       </c>
       <c r="S8" s="53" t="n">
         <f aca="false">P8*$K8/$I8</f>
-        <v>2.15001794624173</v>
+        <v>2.1794651450666</v>
       </c>
       <c r="T8" s="54" t="n">
         <f aca="false">Q8*$K8/$I8</f>
-        <v>2.03616678495262</v>
+        <v>2.05745243600033</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>7.9908</v>
@@ -6424,27 +6424,27 @@
       </c>
       <c r="O9" s="24" t="n">
         <f aca="false">(L9/$F$2)^(1/$F$3)</f>
-        <v>0.70153706879258</v>
+        <v>0.713680101706344</v>
       </c>
       <c r="P9" s="47" t="n">
         <f aca="false">(M9/$G$2)^(1/$G$3)</f>
-        <v>8.14075855740274</v>
+        <v>8.04244702423472</v>
       </c>
       <c r="Q9" s="26" t="n">
         <f aca="false">(N9/$H$2)^(1/$H$3)</f>
-        <v>6.40597038276665</v>
+        <v>6.44671877405501</v>
       </c>
       <c r="R9" s="25" t="n">
         <f aca="false">O9*$K9/$I9</f>
-        <v>4.07596622336814</v>
+        <v>4.14651786519504</v>
       </c>
       <c r="S9" s="47" t="n">
         <f aca="false">P9*$K9/$I9</f>
-        <v>47.2982232709064</v>
+        <v>46.7270282387607</v>
       </c>
       <c r="T9" s="26" t="n">
         <f aca="false">Q9*$K9/$I9</f>
-        <v>37.219015315887</v>
+        <v>37.4557655518137</v>
       </c>
       <c r="U9" s="27" t="n">
         <v>3.2518</v>
@@ -6452,15 +6452,15 @@
       <c r="V9" s="27"/>
       <c r="W9" s="56" t="n">
         <f aca="false">AVERAGE(R9:R10)/100</f>
-        <v>0.039262203929739</v>
+        <v>0.0399347436548235</v>
       </c>
       <c r="X9" s="57" t="n">
         <f aca="false">AVERAGE(S9:S10)/100</f>
-        <v>0.456031029026115</v>
+        <v>0.450669053077152</v>
       </c>
       <c r="Y9" s="57" t="n">
         <f aca="false">AVERAGE(T9:T10)/100</f>
-        <v>0.368413709255228</v>
+        <v>0.370763991916084</v>
       </c>
       <c r="Z9" s="29" t="n">
         <f aca="false">AVERAGE(U9:V10)/100</f>
@@ -6468,16 +6468,16 @@
       </c>
       <c r="AA9" s="2" t="n">
         <f aca="false">SUM(W9:Z9)</f>
-        <v>0.896147442211083</v>
+        <v>0.89380828864806</v>
       </c>
       <c r="AD9" s="0" t="n">
-        <v>0.0439831111069989</v>
+        <v>0.0448580050386312</v>
       </c>
       <c r="AE9" s="0" t="n">
-        <v>0.510864429663411</v>
+        <v>0.506228732264523</v>
       </c>
       <c r="AF9" s="0" t="n">
-        <v>0.41271195922959</v>
+        <v>0.416472762696846</v>
       </c>
       <c r="AG9" s="0" t="n">
         <v>0.0324405</v>
@@ -6530,27 +6530,27 @@
       </c>
       <c r="O10" s="24" t="n">
         <f aca="false">(L10/$F$2)^(1/$F$3)</f>
-        <v>0.646055765198072</v>
+        <v>0.656997011514432</v>
       </c>
       <c r="P10" s="47" t="n">
         <f aca="false">(M10/$G$2)^(1/$G$3)</f>
-        <v>7.51150438972753</v>
+        <v>7.42576218598691</v>
       </c>
       <c r="Q10" s="26" t="n">
         <f aca="false">(N10/$H$2)^(1/$H$3)</f>
-        <v>6.23798740287375</v>
+        <v>6.27789999204866</v>
       </c>
       <c r="R10" s="25" t="n">
         <f aca="false">O10*$K10/$I10</f>
-        <v>3.77647456257967</v>
+        <v>3.84043086576967</v>
       </c>
       <c r="S10" s="47" t="n">
         <f aca="false">P10*$K10/$I10</f>
-        <v>43.9079825343167</v>
+        <v>43.4067823766698</v>
       </c>
       <c r="T10" s="26" t="n">
         <f aca="false">Q10*$K10/$I10</f>
-        <v>36.4637265351586</v>
+        <v>36.6970328314031</v>
       </c>
       <c r="U10" s="27" t="n">
         <v>3.2363</v>
@@ -6607,27 +6607,27 @@
       </c>
       <c r="O11" s="52" t="n">
         <f aca="false">(L11/$F$2)^(1/$F$3)</f>
-        <v>0.0084590303985429</v>
+        <v>0.00843754836777535</v>
       </c>
       <c r="P11" s="53" t="n">
         <f aca="false">(M11/$G$2)^(1/$G$3)</f>
-        <v>0.0105840519593034</v>
+        <v>0.0110508226422213</v>
       </c>
       <c r="Q11" s="54" t="n">
         <f aca="false">(N11/$H$2)^(1/$H$3)</f>
-        <v>0.00869847161222544</v>
+        <v>0.00883480285778204</v>
       </c>
       <c r="R11" s="55" t="n">
         <f aca="false">O11*$K11/$I11</f>
-        <v>0.0480281825618266</v>
+        <v>0.0479062131579006</v>
       </c>
       <c r="S11" s="53" t="n">
         <f aca="false">P11*$K11/$I11</f>
-        <v>0.0600935043137859</v>
+        <v>0.0627437072942067</v>
       </c>
       <c r="T11" s="54" t="n">
         <f aca="false">Q11*$K11/$I11</f>
-        <v>0.0493876677252268</v>
+        <v>0.0501617212091346</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>85.2153</v>
@@ -6635,15 +6635,15 @@
       <c r="V11" s="2"/>
       <c r="W11" s="51" t="n">
         <f aca="false">AVERAGE(R11:R12)/100</f>
-        <v>0.000477543991152536</v>
+        <v>0.000476326035390112</v>
       </c>
       <c r="X11" s="0" t="n">
         <f aca="false">AVERAGE(S11:S12)/100</f>
-        <v>0.000598299282471471</v>
+        <v>0.000624690978018088</v>
       </c>
       <c r="Y11" s="1" t="n">
         <f aca="false">AVERAGE(T11:T12)/100</f>
-        <v>0.000492421394944429</v>
+        <v>0.000500138906128114</v>
       </c>
       <c r="Z11" s="33" t="n">
         <f aca="false">AVERAGE(U11:V12)/100</f>
@@ -6651,19 +6651,19 @@
       </c>
       <c r="AA11" s="2" t="n">
         <f aca="false">SUM(W11:Z11)</f>
-        <v>0.846425264668569</v>
+        <v>0.846458155919536</v>
       </c>
       <c r="AD11" s="0" t="n">
-        <v>0.000477543991152536</v>
+        <v>0.000476326035390113</v>
       </c>
       <c r="AE11" s="0" t="n">
-        <v>0.000598299282471471</v>
+        <v>0.000624690978018088</v>
       </c>
       <c r="AF11" s="0" t="n">
-        <v>0.000492421394944429</v>
+        <v>0.000500138906128114</v>
       </c>
       <c r="AG11" s="0" t="n">
-        <v>0.998431735331432</v>
+        <v>0.998398844080464</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6713,27 +6713,27 @@
       </c>
       <c r="O12" s="52" t="n">
         <f aca="false">(L12/$F$2)^(1/$F$3)</f>
-        <v>0.0084173657699857</v>
+        <v>0.00839580466070381</v>
       </c>
       <c r="P12" s="53" t="n">
         <f aca="false">(M12/$G$2)^(1/$G$3)</f>
-        <v>0.010559925704962</v>
+        <v>0.0110258418010096</v>
       </c>
       <c r="Q12" s="54" t="n">
         <f aca="false">(N12/$H$2)^(1/$H$3)</f>
-        <v>0.00870384954476522</v>
+        <v>0.0088402574557118</v>
       </c>
       <c r="R12" s="55" t="n">
         <f aca="false">O12*$K12/$I12</f>
-        <v>0.0474806156686806</v>
+        <v>0.0473589939201219</v>
       </c>
       <c r="S12" s="53" t="n">
         <f aca="false">P12*$K12/$I12</f>
-        <v>0.0595663521805083</v>
+        <v>0.0621944883094109</v>
       </c>
       <c r="T12" s="54" t="n">
         <f aca="false">Q12*$K12/$I12</f>
-        <v>0.0490966112636591</v>
+        <v>0.0498660600164882</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>83.7561</v>
@@ -6792,27 +6792,27 @@
       </c>
       <c r="O13" s="24" t="n">
         <f aca="false">(L13/$F$2)^(1/$F$3)</f>
-        <v>9.65994677964558</v>
+        <v>9.94276430650812</v>
       </c>
       <c r="P13" s="47" t="n">
         <f aca="false">(M13/$G$2)^(1/$G$3)</f>
-        <v>5.80486522177361</v>
+        <v>5.75092690000535</v>
       </c>
       <c r="Q13" s="26" t="n">
         <f aca="false">(N13/$H$2)^(1/$H$3)</f>
-        <v>5.41432127235173</v>
+        <v>5.45004043755441</v>
       </c>
       <c r="R13" s="25" t="n">
         <f aca="false">O13*$K13/$I13</f>
-        <v>40.8747914902912</v>
+        <v>42.0714965761478</v>
       </c>
       <c r="S13" s="47" t="n">
         <f aca="false">P13*$K13/$I13</f>
-        <v>24.5625220285059</v>
+        <v>24.3342891297223</v>
       </c>
       <c r="T13" s="26" t="n">
         <f aca="false">Q13*$K13/$I13</f>
-        <v>22.9099867853459</v>
+        <v>23.0611277246462</v>
       </c>
       <c r="U13" s="27" t="n">
         <v>4.6408</v>
@@ -6820,15 +6820,15 @@
       <c r="V13" s="27"/>
       <c r="W13" s="56" t="n">
         <f aca="false">AVERAGE(R13:R14)/100</f>
-        <v>0.442040914660317</v>
+        <v>0.455281368967412</v>
       </c>
       <c r="X13" s="57" t="n">
         <f aca="false">AVERAGE(S13:S14)/100</f>
-        <v>0.264707844251777</v>
+        <v>0.261936042113037</v>
       </c>
       <c r="Y13" s="57" t="n">
         <f aca="false">AVERAGE(T13:T14)/100</f>
-        <v>0.233970113526665</v>
+        <v>0.235486099024823</v>
       </c>
       <c r="Z13" s="29" t="n">
         <f aca="false">AVERAGE(U13:V14)/100</f>
@@ -6836,16 +6836,16 @@
       </c>
       <c r="AA13" s="2" t="n">
         <f aca="false">SUM(W13:Z13)</f>
-        <v>0.983649539105425</v>
+        <v>0.995634176771939</v>
       </c>
       <c r="AD13" s="0" t="n">
-        <v>0.44972394611712</v>
+        <v>0.457367724223647</v>
       </c>
       <c r="AE13" s="0" t="n">
-        <v>0.26930868237965</v>
+        <v>0.263136380355516</v>
       </c>
       <c r="AF13" s="0" t="n">
-        <v>0.238036704836563</v>
+        <v>0.23656522875417</v>
       </c>
       <c r="AG13" s="0" t="n">
         <v>0.0429306666666667</v>
@@ -6898,27 +6898,27 @@
       </c>
       <c r="O14" s="24" t="n">
         <f aca="false">(L14/$F$2)^(1/$F$3)</f>
-        <v>12.6997610722292</v>
+        <v>13.0875358977612</v>
       </c>
       <c r="P14" s="47" t="n">
         <f aca="false">(M14/$G$2)^(1/$G$3)</f>
-        <v>7.58218808217355</v>
+        <v>7.49505477290824</v>
       </c>
       <c r="Q14" s="26" t="n">
         <f aca="false">(N14/$H$2)^(1/$H$3)</f>
-        <v>6.3812309709889</v>
+        <v>6.42185666268047</v>
       </c>
       <c r="R14" s="25" t="n">
         <f aca="false">O14*$K14/$I14</f>
-        <v>47.5333914417722</v>
+        <v>48.9847772173347</v>
       </c>
       <c r="S14" s="47" t="n">
         <f aca="false">P14*$K14/$I14</f>
-        <v>28.3790468218496</v>
+        <v>28.0529192928851</v>
       </c>
       <c r="T14" s="26" t="n">
         <f aca="false">Q14*$K14/$I14</f>
-        <v>23.884035919987</v>
+        <v>24.0360920803183</v>
       </c>
       <c r="U14" s="27" t="n">
         <v>4.1703</v>
@@ -6977,27 +6977,27 @@
       </c>
       <c r="O15" s="52" t="n">
         <f aca="false">(L15/$F$2)^(1/$F$3)</f>
-        <v>0.259043499895929</v>
+        <v>0.262359007280137</v>
       </c>
       <c r="P15" s="53" t="n">
         <f aca="false">(M15/$G$2)^(1/$G$3)</f>
-        <v>0.00787951159493257</v>
+        <v>0.00824723777678869</v>
       </c>
       <c r="Q15" s="54" t="n">
         <f aca="false">(N15/$H$2)^(1/$H$3)</f>
-        <v>0.00384126613440799</v>
+        <v>0.00390592182493379</v>
       </c>
       <c r="R15" s="55" t="n">
         <f aca="false">O15*$K15/$I15</f>
-        <v>0.986802469293174</v>
+        <v>0.9994325907786</v>
       </c>
       <c r="S15" s="53" t="n">
         <f aca="false">P15*$K15/$I15</f>
-        <v>0.030016277196021</v>
+        <v>0.0314170963805408</v>
       </c>
       <c r="T15" s="54" t="n">
         <f aca="false">Q15*$K15/$I15</f>
-        <v>0.014632951254013</v>
+        <v>0.014879251180822</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>99.3191</v>
@@ -7005,15 +7005,15 @@
       <c r="V15" s="2"/>
       <c r="W15" s="51" t="n">
         <f aca="false">AVERAGE(R15:R16)/100</f>
-        <v>0.00493401234646587</v>
+        <v>0.004997162953893</v>
       </c>
       <c r="X15" s="0" t="n">
         <f aca="false">AVERAGE(S15:S16)/100</f>
-        <v>0.000150081385980105</v>
+        <v>0.000157085481902704</v>
       </c>
       <c r="Y15" s="1" t="n">
         <f aca="false">AVERAGE(T15:T16)/100</f>
-        <v>7.31647562700649E-005</v>
+        <v>7.43962559041098E-005</v>
       </c>
       <c r="Z15" s="33" t="n">
         <f aca="false">AVERAGE(U15:V16)/100</f>
@@ -7021,19 +7021,19 @@
       </c>
       <c r="AA15" s="2" t="n">
         <f aca="false">SUM(W15:Z15)</f>
-        <v>1.00173475848872</v>
+        <v>1.0018061446917</v>
       </c>
       <c r="AD15" s="0" t="n">
-        <v>0.00986802469293175</v>
+        <v>0.009994325907786</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>0.00030016277196021</v>
+        <v>0.000314170963805408</v>
       </c>
       <c r="AF15" s="0" t="n">
-        <v>0.00014632951254013</v>
+        <v>0.00014879251180822</v>
       </c>
       <c r="AG15" s="0" t="n">
-        <v>0.989685483022568</v>
+        <v>0.9895427106166</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7794,30 +7794,30 @@
       </c>
       <c r="P25" s="1" t="n">
         <f aca="false">(M25/$G$2)^(1/$G$3)</f>
-        <v>18.7088695586386</v>
+        <v>18.3553730534036</v>
       </c>
       <c r="Q25" s="1" t="n">
         <f aca="false">(N25/$H$2)^(1/$H$3)</f>
-        <v>17.4089706722135</v>
+        <v>17.4952894425709</v>
       </c>
       <c r="S25" s="1" t="n">
         <f aca="false">P25*$K25/$I25</f>
-        <v>50.2381027491326</v>
+        <v>49.2888741655566</v>
       </c>
       <c r="T25" s="1" t="n">
         <f aca="false">Q25*$K25/$I25</f>
-        <v>46.7475415682432</v>
+        <v>46.9793295573999</v>
       </c>
       <c r="U25" s="1" t="n">
         <v>3.2005</v>
       </c>
       <c r="X25" s="1" t="n">
         <f aca="false">AVERAGE(S25:S26)/100</f>
-        <v>0.502380435990308</v>
+        <v>0.492911363582667</v>
       </c>
       <c r="Y25" s="1" t="n">
         <f aca="false">AVERAGE(T25:T26)/100</f>
-        <v>0.467698888400843</v>
+        <v>0.47002127271554</v>
       </c>
       <c r="Z25" s="1" t="n">
         <f aca="false">AVERAGE(U25:V26)/100</f>
@@ -7825,19 +7825,19 @@
       </c>
       <c r="AA25" s="1" t="n">
         <f aca="false">SUM(W25:Z25)</f>
-        <v>1.00206482439115</v>
+        <v>0.994918136298207</v>
       </c>
       <c r="AE25" s="1" t="n">
         <f aca="false">IFERROR(X25/$AA25,"")</f>
-        <v>0.501345246097778</v>
+        <v>0.495429066572897</v>
       </c>
       <c r="AF25" s="1" t="n">
         <f aca="false">IFERROR(Y25/$AA25,"")</f>
-        <v>0.466735162253614</v>
+        <v>0.472422057220053</v>
       </c>
       <c r="AG25" s="1" t="n">
         <f aca="false">IFERROR(Z25/$AA25,"")</f>
-        <v>0.0319195916486084</v>
+        <v>0.0321488762070501</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7881,19 +7881,19 @@
       </c>
       <c r="P26" s="1" t="n">
         <f aca="false">(M26/$G$2)^(1/$G$3)</f>
-        <v>18.4984320822075</v>
+        <v>18.150620396075</v>
       </c>
       <c r="Q26" s="1" t="n">
         <f aca="false">(N26/$H$2)^(1/$H$3)</f>
-        <v>17.2296522479122</v>
+        <v>17.3153320253789</v>
       </c>
       <c r="S26" s="1" t="n">
         <f aca="false">P26*$K26/$I26</f>
-        <v>50.2379844489289</v>
+        <v>49.2933985509767</v>
       </c>
       <c r="T26" s="1" t="n">
         <f aca="false">Q26*$K26/$I26</f>
-        <v>46.7922361119253</v>
+        <v>47.0249249857081</v>
       </c>
       <c r="U26" s="1" t="n">
         <v>3.1966</v>
@@ -7940,27 +7940,27 @@
       </c>
       <c r="P27" s="1" t="n">
         <f aca="false">(M27/$G$2)^(1/$G$3)</f>
-        <v>0.0742353267915583</v>
+        <v>0.0762627816564464</v>
       </c>
       <c r="Q27" s="1" t="n">
         <f aca="false">(N27/$H$2)^(1/$H$3)</f>
-        <v>0.0618406382893861</v>
+        <v>0.0626382243409277</v>
       </c>
       <c r="S27" s="1" t="n">
         <f aca="false">P27*$K27/$I27</f>
-        <v>0.175738199713485</v>
+        <v>0.180537818484697</v>
       </c>
       <c r="T27" s="1" t="n">
         <f aca="false">Q27*$K27/$I27</f>
-        <v>0.14639610158415</v>
+        <v>0.14828423682747</v>
       </c>
       <c r="X27" s="1" t="n">
         <f aca="false">AVERAGE(S27:S28)/100</f>
-        <v>0.00207414316969858</v>
+        <v>0.00212867119015662</v>
       </c>
       <c r="Y27" s="1" t="n">
         <f aca="false">AVERAGE(T27:T28)/100</f>
-        <v>0.00174350577574045</v>
+        <v>0.00176567362735554</v>
       </c>
       <c r="Z27" s="1" t="e">
         <f aca="false">AVERAGE(U27:V28)/100</f>
@@ -8024,19 +8024,19 @@
       </c>
       <c r="P28" s="1" t="n">
         <f aca="false">(M28/$G$2)^(1/$G$3)</f>
-        <v>0.0913560469968065</v>
+        <v>0.0936891335700825</v>
       </c>
       <c r="Q28" s="1" t="n">
         <f aca="false">(N28/$H$2)^(1/$H$3)</f>
-        <v>0.077300415806644</v>
+        <v>0.0782730222077361</v>
       </c>
       <c r="S28" s="1" t="n">
         <f aca="false">P28*$K28/$I28</f>
-        <v>0.239090434226231</v>
+        <v>0.245196419546627</v>
       </c>
       <c r="T28" s="1" t="n">
         <f aca="false">Q28*$K28/$I28</f>
-        <v>0.202305053563939</v>
+        <v>0.204850488643639</v>
       </c>
     </row>
   </sheetData>
@@ -8100,13 +8100,13 @@
         <v>2</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>157.651809</v>
+        <v>154.574631</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>156.413729</v>
+        <v>155.54848</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>129.780531</v>
+        <v>128.508587</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8114,13 +8114,13 @@
         <v>3</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>1.05643576</v>
+        <v>1.05174512</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.03759299</v>
+        <v>1.046301</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.03602508</v>
+        <v>1.0374418</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>4</v>
@@ -8272,27 +8272,27 @@
       </c>
       <c r="O5" s="24" t="n">
         <f aca="false">(L5/$F$2)^(1/$F$3)</f>
-        <v>0.300971627912207</v>
+        <v>0.305027791276203</v>
       </c>
       <c r="P5" s="47" t="n">
         <f aca="false">(M5/$G$2)^(1/$G$3)</f>
-        <v>0.000182046881705432</v>
+        <v>0.000196612428440131</v>
       </c>
       <c r="Q5" s="26" t="n">
         <f aca="false">(N5/$H$2)^(1/$H$3)</f>
-        <v>0.000473108945958362</v>
+        <v>0.000482641680372561</v>
       </c>
       <c r="R5" s="25" t="n">
         <f aca="false">O5*$K5/$I5</f>
-        <v>1.16527655010831</v>
+        <v>1.18098086112347</v>
       </c>
       <c r="S5" s="47" t="n">
         <f aca="false">P5*$K5/$I5</f>
-        <v>0.000704833753743596</v>
+        <v>0.000761227408411944</v>
       </c>
       <c r="T5" s="26" t="n">
         <f aca="false">Q5*$K5/$I5</f>
-        <v>0.00183174329153894</v>
+        <v>0.00186865132818124</v>
       </c>
       <c r="U5" s="27" t="n">
         <v>96.2569</v>
@@ -8300,15 +8300,15 @@
       <c r="V5" s="27"/>
       <c r="W5" s="48" t="n">
         <f aca="false">AVERAGE(R5:R6)/100</f>
-        <v>0.00743720400888518</v>
+        <v>0.00752789377984753</v>
       </c>
       <c r="X5" s="49" t="n">
         <f aca="false">AVERAGE(S5:S6)/100</f>
-        <v>4.96397301176585E-006</v>
+        <v>5.3731402517012E-006</v>
       </c>
       <c r="Y5" s="49" t="n">
         <f aca="false">AVERAGE(T5:T6)/100</f>
-        <v>1.16618192150982E-005</v>
+        <v>1.19014219052806E-005</v>
       </c>
       <c r="Z5" s="50" t="n">
         <f aca="false">AVERAGE(U5:V6)/100</f>
@@ -8316,19 +8316,19 @@
       </c>
       <c r="AA5" s="2" t="n">
         <f aca="false">SUM(W5:Z5)</f>
-        <v>0.979183829801112</v>
+        <v>0.979275168342005</v>
       </c>
       <c r="AD5" s="0" t="n">
-        <v>0.00743720400888518</v>
+        <v>0.00752789377984754</v>
       </c>
       <c r="AE5" s="0" t="n">
-        <v>4.96397301176585E-006</v>
+        <v>5.3731402517012E-006</v>
       </c>
       <c r="AF5" s="0" t="n">
-        <v>1.16618192150982E-005</v>
+        <v>1.19014219052806E-005</v>
       </c>
       <c r="AG5" s="0" t="n">
-        <v>0.992546170198888</v>
+        <v>0.992454831657996</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8378,27 +8378,27 @@
       </c>
       <c r="O6" s="24" t="n">
         <f aca="false">(L6/$F$2)^(1/$F$3)</f>
-        <v>0.0808663419621284</v>
+        <v>0.0814772099289211</v>
       </c>
       <c r="P6" s="47" t="n">
         <f aca="false">(M6/$G$2)^(1/$G$3)</f>
-        <v>7.2280957104178E-005</v>
+        <v>7.86665911877293E-005</v>
       </c>
       <c r="Q6" s="26" t="n">
         <f aca="false">(N6/$H$2)^(1/$H$3)</f>
-        <v>0.000125660598590981</v>
+        <v>0.000128424842913521</v>
       </c>
       <c r="R6" s="25" t="n">
         <f aca="false">O6*$K6/$I6</f>
-        <v>0.322164251668723</v>
+        <v>0.324597894846033</v>
       </c>
       <c r="S6" s="47" t="n">
         <f aca="false">P6*$K6/$I6</f>
-        <v>0.000287960848609575</v>
+        <v>0.000313400641928296</v>
       </c>
       <c r="T6" s="26" t="n">
         <f aca="false">Q6*$K6/$I6</f>
-        <v>0.000500620551480696</v>
+        <v>0.000511633052874878</v>
       </c>
       <c r="U6" s="27" t="n">
         <v>98.0891</v>
@@ -8455,27 +8455,27 @@
       </c>
       <c r="O7" s="52" t="n">
         <f aca="false">(L7/$F$2)^(1/$F$3)</f>
-        <v>2.16244989571547</v>
+        <v>2.21095256480462</v>
       </c>
       <c r="P7" s="53" t="n">
         <f aca="false">(M7/$G$2)^(1/$G$3)</f>
-        <v>0.0457199387500349</v>
+        <v>0.0471584605117064</v>
       </c>
       <c r="Q7" s="54" t="n">
         <f aca="false">(N7/$H$2)^(1/$H$3)</f>
-        <v>0.0485328920811165</v>
+        <v>0.0491986892341035</v>
       </c>
       <c r="R7" s="55" t="n">
         <f aca="false">O7*$K7/$I7</f>
-        <v>9.24391778027856</v>
+        <v>9.45125423051147</v>
       </c>
       <c r="S7" s="53" t="n">
         <f aca="false">P7*$K7/$I7</f>
-        <v>0.195440992904421</v>
+        <v>0.201590303885628</v>
       </c>
       <c r="T7" s="54" t="n">
         <f aca="false">Q7*$K7/$I7</f>
-        <v>0.207465645759407</v>
+        <v>0.210311757548055</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>7.7273</v>
@@ -8483,15 +8483,15 @@
       <c r="V7" s="2"/>
       <c r="W7" s="51" t="n">
         <f aca="false">AVERAGE(R7:R8)/100</f>
-        <v>0.263874390976527</v>
+        <v>0.271507764212663</v>
       </c>
       <c r="X7" s="0" t="n">
         <f aca="false">AVERAGE(S7:S8)/100</f>
-        <v>0.00570232984465359</v>
+        <v>0.00581137134247358</v>
       </c>
       <c r="Y7" s="1" t="n">
         <f aca="false">AVERAGE(T7:T8)/100</f>
-        <v>0.00609042319793964</v>
+        <v>0.0061617126775017</v>
       </c>
       <c r="Z7" s="33" t="n">
         <f aca="false">AVERAGE(U7:V8)/100</f>
@@ -8499,16 +8499,16 @@
       </c>
       <c r="AA7" s="2" t="n">
         <f aca="false">SUM(W7:Z7)</f>
-        <v>0.35442464401912</v>
+        <v>0.362238348232638</v>
       </c>
       <c r="AD7" s="0" t="n">
-        <v>0.881832706230425</v>
+        <v>0.882332944296187</v>
       </c>
       <c r="AE7" s="0" t="n">
-        <v>0.0190564190034519</v>
+        <v>0.0188855165960814</v>
       </c>
       <c r="AF7" s="0" t="n">
-        <v>0.0203533747661228</v>
+        <v>0.0200240391077319</v>
       </c>
       <c r="AG7" s="0" t="n">
         <v>0.0787575</v>
@@ -8561,27 +8561,27 @@
       </c>
       <c r="O8" s="52" t="n">
         <f aca="false">(L8/$F$2)^(1/$F$3)</f>
-        <v>12.0903640867174</v>
+        <v>12.4567993549287</v>
       </c>
       <c r="P8" s="53" t="n">
         <f aca="false">(M8/$G$2)^(1/$G$3)</f>
-        <v>0.262472868098154</v>
+        <v>0.26682202261693</v>
       </c>
       <c r="Q8" s="54" t="n">
         <f aca="false">(N8/$H$2)^(1/$H$3)</f>
-        <v>0.280691063827779</v>
+        <v>0.283860592448785</v>
       </c>
       <c r="R8" s="55" t="n">
         <f aca="false">O8*$K8/$I8</f>
-        <v>43.5309604150268</v>
+        <v>44.8502986120211</v>
       </c>
       <c r="S8" s="53" t="n">
         <f aca="false">P8*$K8/$I8</f>
-        <v>0.945024976026297</v>
+        <v>0.960683964609087</v>
       </c>
       <c r="T8" s="54" t="n">
         <f aca="false">Q8*$K8/$I8</f>
-        <v>1.01061899382852</v>
+        <v>1.02203077795228</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>8.0242</v>
@@ -8640,27 +8640,27 @@
       </c>
       <c r="O9" s="24" t="n">
         <f aca="false">(L9/$F$2)^(1/$F$3)</f>
-        <v>0.0202956139040449</v>
+        <v>0.0203232422730676</v>
       </c>
       <c r="P9" s="47" t="n">
         <f aca="false">(M9/$G$2)^(1/$G$3)</f>
-        <v>0.0281807677510952</v>
+        <v>0.029184740154266</v>
       </c>
       <c r="Q9" s="26" t="n">
         <f aca="false">(N9/$H$2)^(1/$H$3)</f>
-        <v>0.0360193500285744</v>
+        <v>0.0365283517788744</v>
       </c>
       <c r="R9" s="25" t="n">
         <f aca="false">O9*$K9/$I9</f>
-        <v>0.0829833625328898</v>
+        <v>0.0830963275791131</v>
       </c>
       <c r="S9" s="47" t="n">
         <f aca="false">P9*$K9/$I9</f>
-        <v>0.115223657574518</v>
+        <v>0.119328633472228</v>
       </c>
       <c r="T9" s="26" t="n">
         <f aca="false">Q9*$K9/$I9</f>
-        <v>0.147273533865587</v>
+        <v>0.149354706525587</v>
       </c>
       <c r="U9" s="27" t="n">
         <v>98.7791</v>
@@ -8668,15 +8668,15 @@
       <c r="V9" s="27"/>
       <c r="W9" s="56" t="n">
         <f aca="false">AVERAGE(R9:R10)/100</f>
-        <v>0.000870153351752123</v>
+        <v>0.000871601588979647</v>
       </c>
       <c r="X9" s="57" t="n">
         <f aca="false">AVERAGE(S9:S10)/100</f>
-        <v>0.0025674506288186</v>
+        <v>0.0026371141521429</v>
       </c>
       <c r="Y9" s="57" t="n">
         <f aca="false">AVERAGE(T9:T10)/100</f>
-        <v>0.00295007111481544</v>
+        <v>0.00298827464397429</v>
       </c>
       <c r="Z9" s="29" t="n">
         <f aca="false">AVERAGE(U9:V10)/100</f>
@@ -8684,19 +8684,19 @@
       </c>
       <c r="AA9" s="2" t="n">
         <f aca="false">SUM(W9:Z9)</f>
-        <v>0.986705175095386</v>
+        <v>0.986814490385097</v>
       </c>
       <c r="AD9" s="0" t="n">
-        <v>0.000829833625328898</v>
+        <v>0.000830963275791131</v>
       </c>
       <c r="AE9" s="0" t="n">
-        <v>0.00115223657574518</v>
+        <v>0.00119328633472228</v>
       </c>
       <c r="AF9" s="0" t="n">
-        <v>0.00147273533865587</v>
+        <v>0.00149354706525587</v>
       </c>
       <c r="AG9" s="0" t="n">
-        <v>0.99654519446027</v>
+        <v>0.996482203324231</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8746,27 +8746,27 @@
       </c>
       <c r="O10" s="24" t="n">
         <f aca="false">(L10/$F$2)^(1/$F$3)</f>
-        <v>0.0231055598844499</v>
+        <v>0.0231503975172694</v>
       </c>
       <c r="P10" s="47" t="n">
         <f aca="false">(M10/$G$2)^(1/$G$3)</f>
-        <v>0.10107020131947</v>
+        <v>0.103564236354669</v>
       </c>
       <c r="Q10" s="26" t="n">
         <f aca="false">(N10/$H$2)^(1/$H$3)</f>
-        <v>0.112356661063785</v>
+        <v>0.113767533386198</v>
       </c>
       <c r="R10" s="25" t="n">
         <f aca="false">O10*$K10/$I10</f>
-        <v>0.0910473078175348</v>
+        <v>0.0912239902168164</v>
       </c>
       <c r="S10" s="47" t="n">
         <f aca="false">P10*$K10/$I10</f>
-        <v>0.398266468189202</v>
+        <v>0.408094196956351</v>
       </c>
       <c r="T10" s="26" t="n">
         <f aca="false">Q10*$K10/$I10</f>
-        <v>0.4427406890975</v>
+        <v>0.44830022226927</v>
       </c>
       <c r="U10" s="27" t="n">
         <v>97.2844</v>
@@ -8823,27 +8823,27 @@
       </c>
       <c r="O11" s="52" t="n">
         <f aca="false">(L11/$F$2)^(1/$F$3)</f>
-        <v>0.555267964818676</v>
+        <v>0.564290439785625</v>
       </c>
       <c r="P11" s="53" t="n">
         <f aca="false">(M11/$G$2)^(1/$G$3)</f>
-        <v>5.28773116869426</v>
+        <v>5.24266769870039</v>
       </c>
       <c r="Q11" s="54" t="n">
         <f aca="false">(N11/$H$2)^(1/$H$3)</f>
-        <v>5.69180322810508</v>
+        <v>5.73246670489223</v>
       </c>
       <c r="R11" s="55" t="n">
         <f aca="false">O11*$K11/$I11</f>
-        <v>2.40912735590667</v>
+        <v>2.44827294441178</v>
       </c>
       <c r="S11" s="53" t="n">
         <f aca="false">P11*$K11/$I11</f>
-        <v>22.9417481581917</v>
+        <v>22.7462323978871</v>
       </c>
       <c r="T11" s="54" t="n">
         <f aca="false">Q11*$K11/$I11</f>
-        <v>24.6948855868961</v>
+        <v>24.8713112057344</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>2.9293</v>
@@ -8851,15 +8851,15 @@
       <c r="V11" s="2"/>
       <c r="W11" s="51" t="n">
         <f aca="false">AVERAGE(R11:R12)/100</f>
-        <v>0.0346950880777213</v>
+        <v>0.0353347444141482</v>
       </c>
       <c r="X11" s="0" t="n">
         <f aca="false">AVERAGE(S11:S12)/100</f>
-        <v>0.331954801317649</v>
+        <v>0.327793753060823</v>
       </c>
       <c r="Y11" s="1" t="n">
         <f aca="false">AVERAGE(T11:T12)/100</f>
-        <v>0.356988056397143</v>
+        <v>0.359299654922772</v>
       </c>
       <c r="Z11" s="33" t="n">
         <f aca="false">AVERAGE(U11:V12)/100</f>
@@ -8867,16 +8867,16 @@
       </c>
       <c r="AA11" s="2" t="n">
         <f aca="false">SUM(W11:Z11)</f>
-        <v>0.752877945792514</v>
+        <v>0.751668152397743</v>
       </c>
       <c r="AD11" s="0" t="n">
-        <v>0.0465434460674148</v>
+        <v>0.0474809243986844</v>
       </c>
       <c r="AE11" s="0" t="n">
-        <v>0.445317226384806</v>
+        <v>0.440471571692197</v>
       </c>
       <c r="AF11" s="0" t="n">
-        <v>0.478899327547779</v>
+        <v>0.482807503909118</v>
       </c>
       <c r="AG11" s="0" t="n">
         <v>0.02924</v>
@@ -8929,27 +8929,27 @@
       </c>
       <c r="O12" s="52" t="n">
         <f aca="false">(L12/$F$2)^(1/$F$3)</f>
-        <v>1.16166568063906</v>
+        <v>1.18443428430487</v>
       </c>
       <c r="P12" s="53" t="n">
         <f aca="false">(M12/$G$2)^(1/$G$3)</f>
-        <v>11.142313756099</v>
+        <v>10.9790370761079</v>
       </c>
       <c r="Q12" s="54" t="n">
         <f aca="false">(N12/$H$2)^(1/$H$3)</f>
-        <v>11.9766595921147</v>
+        <v>12.0499755731434</v>
       </c>
       <c r="R12" s="55" t="n">
         <f aca="false">O12*$K12/$I12</f>
-        <v>4.52989025963758</v>
+        <v>4.61867593841786</v>
       </c>
       <c r="S12" s="53" t="n">
         <f aca="false">P12*$K12/$I12</f>
-        <v>43.4492121053382</v>
+        <v>42.8125182142774</v>
       </c>
       <c r="T12" s="54" t="n">
         <f aca="false">Q12*$K12/$I12</f>
-        <v>46.7027256925326</v>
+        <v>46.9886197788201</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>2.9187</v>
@@ -9008,27 +9008,27 @@
       </c>
       <c r="O13" s="24" t="n">
         <f aca="false">(L13/$F$2)^(1/$F$3)</f>
-        <v>0.450213157020532</v>
+        <v>0.457100853951892</v>
       </c>
       <c r="P13" s="47" t="n">
         <f aca="false">(M13/$G$2)^(1/$G$3)</f>
-        <v>0.0957268409996605</v>
+        <v>0.0981333738908238</v>
       </c>
       <c r="Q13" s="26" t="n">
         <f aca="false">(N13/$H$2)^(1/$H$3)</f>
-        <v>0.112907012727136</v>
+        <v>0.11432403301287</v>
       </c>
       <c r="R13" s="25" t="n">
         <f aca="false">O13*$K13/$I13</f>
-        <v>1.85469721671071</v>
+        <v>1.88307175914453</v>
       </c>
       <c r="S13" s="47" t="n">
         <f aca="false">P13*$K13/$I13</f>
-        <v>0.394356101766441</v>
+        <v>0.404270049827625</v>
       </c>
       <c r="T13" s="26" t="n">
         <f aca="false">Q13*$K13/$I13</f>
-        <v>0.465131502681941</v>
+        <v>0.470969056602769</v>
       </c>
       <c r="U13" s="27" t="n">
         <v>97.4976</v>
@@ -9036,15 +9036,15 @@
       <c r="V13" s="27"/>
       <c r="W13" s="56" t="n">
         <f aca="false">AVERAGE(R13:R14)/100</f>
-        <v>0.0174422380068271</v>
+        <v>0.0177055813738214</v>
       </c>
       <c r="X13" s="57" t="n">
         <f aca="false">AVERAGE(S13:S14)/100</f>
-        <v>0.00358967991276696</v>
+        <v>0.00368221093439793</v>
       </c>
       <c r="Y13" s="57" t="n">
         <f aca="false">AVERAGE(T13:T14)/100</f>
-        <v>0.00420661462210444</v>
+        <v>0.00425987736330177</v>
       </c>
       <c r="Z13" s="29" t="n">
         <f aca="false">AVERAGE(U13:V14)/100</f>
@@ -9052,19 +9052,19 @@
       </c>
       <c r="AA13" s="2" t="n">
         <f aca="false">SUM(W13:Z13)</f>
-        <v>0.998104032541699</v>
+        <v>0.998513169671521</v>
       </c>
       <c r="AD13" s="0" t="n">
-        <v>0.0174422380068271</v>
+        <v>0.0177055813738214</v>
       </c>
       <c r="AE13" s="0" t="n">
-        <v>0.00358967991276696</v>
+        <v>0.00368221093439793</v>
       </c>
       <c r="AF13" s="0" t="n">
-        <v>0.00420661462210444</v>
+        <v>0.00425987736330177</v>
       </c>
       <c r="AG13" s="0" t="n">
-        <v>0.974761467458302</v>
+        <v>0.974352330328479</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9114,27 +9114,27 @@
       </c>
       <c r="O14" s="24" t="n">
         <f aca="false">(L14/$F$2)^(1/$F$3)</f>
-        <v>0.409546659001937</v>
+        <v>0.415636683685968</v>
       </c>
       <c r="P14" s="47" t="n">
         <f aca="false">(M14/$G$2)^(1/$G$3)</f>
-        <v>0.0811146306934456</v>
+        <v>0.0832685275675798</v>
       </c>
       <c r="Q14" s="26" t="n">
         <f aca="false">(N14/$H$2)^(1/$H$3)</f>
-        <v>0.0943032309987413</v>
+        <v>0.0955102482119172</v>
       </c>
       <c r="R14" s="25" t="n">
         <f aca="false">O14*$K14/$I14</f>
-        <v>1.6337503846547</v>
+        <v>1.65804451561975</v>
       </c>
       <c r="S14" s="47" t="n">
         <f aca="false">P14*$K14/$I14</f>
-        <v>0.323579880786951</v>
+        <v>0.332172137051961</v>
       </c>
       <c r="T14" s="26" t="n">
         <f aca="false">Q14*$K14/$I14</f>
-        <v>0.376191421738948</v>
+        <v>0.381006416057585</v>
       </c>
       <c r="U14" s="27" t="n">
         <v>97.0755</v>
@@ -9191,27 +9191,27 @@
       </c>
       <c r="O15" s="52" t="n">
         <f aca="false">(L15/$F$2)^(1/$F$3)</f>
-        <v>10.4640442937683</v>
+        <v>10.7742450320564</v>
       </c>
       <c r="P15" s="53" t="n">
         <f aca="false">(M15/$G$2)^(1/$G$3)</f>
-        <v>5.73505961065621</v>
+        <v>5.6823420411346</v>
       </c>
       <c r="Q15" s="54" t="n">
         <f aca="false">(N15/$H$2)^(1/$H$3)</f>
-        <v>6.18788146419771</v>
+        <v>6.23137788834257</v>
       </c>
       <c r="R15" s="55" t="n">
         <f aca="false">O15*$K15/$I15</f>
-        <v>42.5389768823057</v>
+        <v>43.8000210507418</v>
       </c>
       <c r="S15" s="53" t="n">
         <f aca="false">P15*$K15/$I15</f>
-        <v>23.3144624914899</v>
+        <v>23.1001522871164</v>
       </c>
       <c r="T15" s="54" t="n">
         <f aca="false">Q15*$K15/$I15</f>
-        <v>25.1552974324388</v>
+        <v>25.332121357225</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>4.1294</v>
@@ -9219,15 +9219,15 @@
       <c r="V15" s="2"/>
       <c r="W15" s="51" t="n">
         <f aca="false">AVERAGE(R15:R16)/100</f>
-        <v>0.407759479698317</v>
+        <v>0.419823233822702</v>
       </c>
       <c r="X15" s="0" t="n">
         <f aca="false">AVERAGE(S15:S16)/100</f>
-        <v>0.223529682337524</v>
+        <v>0.221498250562085</v>
       </c>
       <c r="Y15" s="1" t="n">
         <f aca="false">AVERAGE(T15:T16)/100</f>
-        <v>0.239831510226846</v>
+        <v>0.241523339026386</v>
       </c>
       <c r="Z15" s="33" t="n">
         <f aca="false">AVERAGE(U15:V16)/100</f>
@@ -9235,16 +9235,16 @@
       </c>
       <c r="AA15" s="2" t="n">
         <f aca="false">SUM(W15:Z15)</f>
-        <v>0.913040672262687</v>
+        <v>0.924764823411173</v>
       </c>
       <c r="AD15" s="0" t="n">
-        <v>0.448463932436169</v>
+        <v>0.455600161200157</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>0.245843457597749</v>
+        <v>0.240374115893397</v>
       </c>
       <c r="AF15" s="0" t="n">
-        <v>0.263772609966082</v>
+        <v>0.262105722906447</v>
       </c>
       <c r="AG15" s="0" t="n">
         <v>0.04192</v>
@@ -9297,27 +9297,27 @@
       </c>
       <c r="O16" s="52" t="n">
         <f aca="false">(L16/$F$2)^(1/$F$3)</f>
-        <v>10.1868454886477</v>
+        <v>10.4875729922769</v>
       </c>
       <c r="P16" s="53" t="n">
         <f aca="false">(M16/$G$2)^(1/$G$3)</f>
-        <v>5.58562766984217</v>
+        <v>5.53549988058456</v>
       </c>
       <c r="Q16" s="54" t="n">
         <f aca="false">(N16/$H$2)^(1/$H$3)</f>
-        <v>5.95628794377349</v>
+        <v>5.99846888675597</v>
       </c>
       <c r="R16" s="55" t="n">
         <f aca="false">O16*$K16/$I16</f>
-        <v>39.0129190573577</v>
+        <v>40.1646257137985</v>
       </c>
       <c r="S16" s="53" t="n">
         <f aca="false">P16*$K16/$I16</f>
-        <v>21.3914739760148</v>
+        <v>21.1994978253006</v>
       </c>
       <c r="T16" s="54" t="n">
         <f aca="false">Q16*$K16/$I16</f>
-        <v>22.8110046129304</v>
+        <v>22.9725464480522</v>
       </c>
       <c r="U16" s="2" t="n">
         <v>4.2546</v>
@@ -9376,27 +9376,27 @@
       </c>
       <c r="O17" s="24" t="n">
         <f aca="false">(L17/$F$2)^(1/$F$3)</f>
-        <v>0.382963479112082</v>
+        <v>0.38854189697943</v>
       </c>
       <c r="P17" s="47" t="n">
         <f aca="false">(M17/$G$2)^(1/$G$3)</f>
-        <v>0.00277289039303249</v>
+        <v>0.00292763413186487</v>
       </c>
       <c r="Q17" s="26" t="n">
         <f aca="false">(N17/$H$2)^(1/$H$3)</f>
-        <v>0.00723586983884516</v>
+        <v>0.00735422357458272</v>
       </c>
       <c r="R17" s="25" t="n">
         <f aca="false">O17*$K17/$I17</f>
-        <v>1.56807246350223</v>
+        <v>1.59091371057879</v>
       </c>
       <c r="S17" s="47" t="n">
         <f aca="false">P17*$K17/$I17</f>
-        <v>0.0113538060592759</v>
+        <v>0.0119874158132008</v>
       </c>
       <c r="T17" s="26" t="n">
         <f aca="false">Q17*$K17/$I17</f>
-        <v>0.02962780751336</v>
+        <v>0.0301124156916463</v>
       </c>
       <c r="U17" s="27" t="n">
         <v>98.3636</v>
@@ -9404,15 +9404,15 @@
       <c r="V17" s="27"/>
       <c r="W17" s="56" t="n">
         <f aca="false">AVERAGE(R17:R18)/100</f>
-        <v>0.0155227650154516</v>
+        <v>0.015748546470514</v>
       </c>
       <c r="X17" s="57" t="n">
         <f aca="false">AVERAGE(S17:S18)/100</f>
-        <v>0.000110416181143723</v>
+        <v>0.000116599609525434</v>
       </c>
       <c r="Y17" s="57" t="n">
         <f aca="false">AVERAGE(T17:T18)/100</f>
-        <v>0.000288936088933308</v>
+        <v>0.000293669893355705</v>
       </c>
       <c r="Z17" s="29" t="n">
         <f aca="false">AVERAGE(U17:V18)/100</f>
@@ -9420,19 +9420,19 @@
       </c>
       <c r="AA17" s="2" t="n">
         <f aca="false">SUM(W17:Z17)</f>
-        <v>1.00074261728553</v>
+        <v>1.0009793159734</v>
       </c>
       <c r="AD17" s="0" t="n">
-        <v>0.0155227650154516</v>
+        <v>0.015748546470514</v>
       </c>
       <c r="AE17" s="0" t="n">
-        <v>0.000110416181143723</v>
+        <v>0.000116599609525434</v>
       </c>
       <c r="AF17" s="0" t="n">
-        <v>0.000288936088933308</v>
+        <v>0.000293669893355705</v>
       </c>
       <c r="AG17" s="0" t="n">
-        <v>0.984077882714471</v>
+        <v>0.983841184026605</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9482,27 +9482,27 @@
       </c>
       <c r="O18" s="24" t="n">
         <f aca="false">(L18/$F$2)^(1/$F$3)</f>
-        <v>0.379343892186682</v>
+        <v>0.384853285506583</v>
       </c>
       <c r="P18" s="47" t="n">
         <f aca="false">(M18/$G$2)^(1/$G$3)</f>
-        <v>0.00264900445958306</v>
+        <v>0.00279789874219807</v>
       </c>
       <c r="Q18" s="26" t="n">
         <f aca="false">(N18/$H$2)^(1/$H$3)</f>
-        <v>0.00695231733792054</v>
+        <v>0.00706641888482262</v>
       </c>
       <c r="R18" s="25" t="n">
         <f aca="false">O18*$K18/$I18</f>
-        <v>1.53648053958809</v>
+        <v>1.558795583524</v>
       </c>
       <c r="S18" s="47" t="n">
         <f aca="false">P18*$K18/$I18</f>
-        <v>0.0107294301694686</v>
+        <v>0.0113325060918861</v>
       </c>
       <c r="T18" s="26" t="n">
         <f aca="false">Q18*$K18/$I18</f>
-        <v>0.0281594102733015</v>
+        <v>0.0286215629794947</v>
       </c>
       <c r="U18" s="27" t="n">
         <v>98.6005</v>
@@ -9559,27 +9559,27 @@
       </c>
       <c r="O19" s="52" t="n">
         <f aca="false">(L19/$F$2)^(1/$F$3)</f>
-        <v>13.9506611492736</v>
+        <v>14.3826557176542</v>
       </c>
       <c r="P19" s="53" t="n">
         <f aca="false">(M19/$G$2)^(1/$G$3)</f>
-        <v>3.0052590953675</v>
+        <v>2.99369230542574</v>
       </c>
       <c r="Q19" s="54" t="n">
         <f aca="false">(N19/$H$2)^(1/$H$3)</f>
-        <v>3.22480942407326</v>
+        <v>3.25036902935619</v>
       </c>
       <c r="R19" s="55" t="n">
         <f aca="false">O19*$K19/$I19</f>
-        <v>59.1407593877093</v>
+        <v>60.9721053398491</v>
       </c>
       <c r="S19" s="53" t="n">
         <f aca="false">P19*$K19/$I19</f>
-        <v>12.7401349050836</v>
+        <v>12.6911000433294</v>
       </c>
       <c r="T19" s="54" t="n">
         <f aca="false">Q19*$K19/$I19</f>
-        <v>13.6708702318574</v>
+        <v>13.7792245564237</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>5.4714</v>
@@ -9587,15 +9587,15 @@
       <c r="V19" s="2"/>
       <c r="W19" s="51" t="n">
         <f aca="false">AVERAGE(R19:R20)/100</f>
-        <v>0.589818560132147</v>
+        <v>0.608251024820617</v>
       </c>
       <c r="X19" s="0" t="n">
         <f aca="false">AVERAGE(S19:S20)/100</f>
-        <v>0.127568324457594</v>
+        <v>0.127007288007324</v>
       </c>
       <c r="Y19" s="1" t="n">
         <f aca="false">AVERAGE(T19:T20)/100</f>
-        <v>0.137074834761931</v>
+        <v>0.138148504027565</v>
       </c>
       <c r="Z19" s="33" t="n">
         <f aca="false">AVERAGE(U19:V20)/100</f>
@@ -9603,16 +9603,16 @@
       </c>
       <c r="AA19" s="2" t="n">
         <f aca="false">SUM(W19:Z19)</f>
-        <v>0.910251219351672</v>
+        <v>0.929196316855506</v>
       </c>
       <c r="AD19" s="0" t="n">
-        <v>0.651770424536064</v>
+        <v>0.657559562380197</v>
       </c>
       <c r="AE19" s="0" t="n">
-        <v>0.140967522233366</v>
+        <v>0.137303273341498</v>
       </c>
       <c r="AF19" s="0" t="n">
-        <v>0.15147255323057</v>
+        <v>0.149347664278305</v>
       </c>
       <c r="AG19" s="0" t="n">
         <v>0.0557895</v>
@@ -9665,27 +9665,27 @@
       </c>
       <c r="O20" s="52" t="n">
         <f aca="false">(L20/$F$2)^(1/$F$3)</f>
-        <v>15.7979228337339</v>
+        <v>16.2961546906592</v>
       </c>
       <c r="P20" s="53" t="n">
         <f aca="false">(M20/$G$2)^(1/$G$3)</f>
-        <v>3.43055273473739</v>
+        <v>3.41358668487537</v>
       </c>
       <c r="Q20" s="54" t="n">
         <f aca="false">(N20/$H$2)^(1/$H$3)</f>
-        <v>3.69121524286364</v>
+        <v>3.71978530791304</v>
       </c>
       <c r="R20" s="55" t="n">
         <f aca="false">O20*$K20/$I20</f>
-        <v>58.8229526387201</v>
+        <v>60.6780996242743</v>
       </c>
       <c r="S20" s="53" t="n">
         <f aca="false">P20*$K20/$I20</f>
-        <v>12.7735299864352</v>
+        <v>12.7103575581354</v>
       </c>
       <c r="T20" s="54" t="n">
         <f aca="false">Q20*$K20/$I20</f>
-        <v>13.7440967205288</v>
+        <v>13.8504762490892</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>5.6865</v>
@@ -9744,27 +9744,27 @@
       </c>
       <c r="O21" s="24" t="n">
         <f aca="false">(L21/$F$2)^(1/$F$3)</f>
-        <v>0.197861924441783</v>
+        <v>0.20015371614961</v>
       </c>
       <c r="P21" s="47" t="n">
         <f aca="false">(M21/$G$2)^(1/$G$3)</f>
-        <v>0.108947672350498</v>
+        <v>0.111566383858277</v>
       </c>
       <c r="Q21" s="26" t="n">
         <f aca="false">(N21/$H$2)^(1/$H$3)</f>
-        <v>0.124209506267659</v>
+        <v>0.125751992005274</v>
       </c>
       <c r="R21" s="25" t="n">
         <f aca="false">O21*$K21/$I21</f>
-        <v>0.810928881774823</v>
+        <v>0.820321694930424</v>
       </c>
       <c r="S21" s="47" t="n">
         <f aca="false">P21*$K21/$I21</f>
-        <v>0.446517511443461</v>
+        <v>0.45725019182492</v>
       </c>
       <c r="T21" s="26" t="n">
         <f aca="false">Q21*$K21/$I21</f>
-        <v>0.509067504056709</v>
+        <v>0.515389317805803</v>
       </c>
       <c r="U21" s="27" t="n">
         <v>99.6359</v>
@@ -9772,15 +9772,15 @@
       <c r="V21" s="27"/>
       <c r="W21" s="56" t="n">
         <f aca="false">AVERAGE(R21:R22)/100</f>
-        <v>0.007364574603056</v>
+        <v>0.00744754305251486</v>
       </c>
       <c r="X21" s="57" t="n">
         <f aca="false">AVERAGE(S21:S22)/100</f>
-        <v>0.00353168091761004</v>
+        <v>0.00362206061128188</v>
       </c>
       <c r="Y21" s="57" t="n">
         <f aca="false">AVERAGE(T21:T22)/100</f>
-        <v>0.00410647912599192</v>
+        <v>0.00415842993128495</v>
       </c>
       <c r="Z21" s="29" t="n">
         <f aca="false">AVERAGE(U21:V22)/100</f>
@@ -9788,19 +9788,19 @@
       </c>
       <c r="AA21" s="2" t="n">
         <f aca="false">SUM(W21:Z21)</f>
-        <v>1.00801223464666</v>
+        <v>1.00823753359508</v>
       </c>
       <c r="AD21" s="0" t="n">
-        <v>0.007364574603056</v>
+        <v>0.00744754305251486</v>
       </c>
       <c r="AE21" s="0" t="n">
-        <v>0.00353168091761004</v>
+        <v>0.00362206061128188</v>
       </c>
       <c r="AF21" s="0" t="n">
-        <v>0.00410647912599192</v>
+        <v>0.00415842993128495</v>
       </c>
       <c r="AG21" s="0" t="n">
-        <v>0.984997265353342</v>
+        <v>0.984771966404918</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9850,27 +9850,27 @@
       </c>
       <c r="O22" s="24" t="n">
         <f aca="false">(L22/$F$2)^(1/$F$3)</f>
-        <v>0.169224638723109</v>
+        <v>0.171065411326577</v>
       </c>
       <c r="P22" s="47" t="n">
         <f aca="false">(M22/$G$2)^(1/$G$3)</f>
-        <v>0.0664178975636641</v>
+        <v>0.0682950674266502</v>
       </c>
       <c r="Q22" s="26" t="n">
         <f aca="false">(N22/$H$2)^(1/$H$3)</f>
-        <v>0.0798154670107514</v>
+        <v>0.0808554656863467</v>
       </c>
       <c r="R22" s="25" t="n">
         <f aca="false">O22*$K22/$I22</f>
-        <v>0.661986038836376</v>
+        <v>0.669186915572547</v>
       </c>
       <c r="S22" s="47" t="n">
         <f aca="false">P22*$K22/$I22</f>
-        <v>0.259818672078548</v>
+        <v>0.267161930431455</v>
       </c>
       <c r="T22" s="26" t="n">
         <f aca="false">Q22*$K22/$I22</f>
-        <v>0.312228321141675</v>
+        <v>0.316296668451188</v>
       </c>
       <c r="U22" s="27" t="n">
         <v>98.966</v>
@@ -9927,27 +9927,27 @@
       </c>
       <c r="O23" s="52" t="n">
         <f aca="false">(L23/$F$2)^(1/$F$3)</f>
-        <v>5.00771075038498</v>
+        <v>5.13924224359308</v>
       </c>
       <c r="P23" s="53" t="n">
         <f aca="false">(M23/$G$2)^(1/$G$3)</f>
-        <v>7.16265518550563</v>
+        <v>7.08369808228938</v>
       </c>
       <c r="Q23" s="54" t="n">
         <f aca="false">(N23/$H$2)^(1/$H$3)</f>
-        <v>7.62700312494806</v>
+        <v>7.67842268483604</v>
       </c>
       <c r="R23" s="55" t="n">
         <f aca="false">O23*$K23/$I23</f>
-        <v>20.5439820432241</v>
+        <v>21.0835860198272</v>
       </c>
       <c r="S23" s="53" t="n">
         <f aca="false">P23*$K23/$I23</f>
-        <v>29.3845764756923</v>
+        <v>29.060657345472</v>
       </c>
       <c r="T23" s="54" t="n">
         <f aca="false">Q23*$K23/$I23</f>
-        <v>31.2895498667732</v>
+        <v>31.5004970575486</v>
       </c>
       <c r="U23" s="2" t="n">
         <v>3.5236</v>
@@ -9955,15 +9955,15 @@
       <c r="V23" s="2"/>
       <c r="W23" s="51" t="n">
         <f aca="false">AVERAGE(R23:R24)/100</f>
-        <v>0.210701212814855</v>
+        <v>0.216297585375874</v>
       </c>
       <c r="X23" s="0" t="n">
         <f aca="false">AVERAGE(S23:S24)/100</f>
-        <v>0.301336289956508</v>
+        <v>0.297855148748125</v>
       </c>
       <c r="Y23" s="1" t="n">
         <f aca="false">AVERAGE(T23:T24)/100</f>
-        <v>0.321915565070503</v>
+        <v>0.324055869814382</v>
       </c>
       <c r="Z23" s="33" t="n">
         <f aca="false">AVERAGE(U23:V24)/100</f>
@@ -9971,16 +9971,16 @@
       </c>
       <c r="AA23" s="2" t="n">
         <f aca="false">SUM(W23:Z23)</f>
-        <v>0.869113567841866</v>
+        <v>0.873369103938381</v>
       </c>
       <c r="AD23" s="0" t="n">
-        <v>0.243770136067449</v>
+        <v>0.248974364072034</v>
       </c>
       <c r="AE23" s="0" t="n">
-        <v>0.348630116663378</v>
+        <v>0.342853093418847</v>
       </c>
       <c r="AF23" s="0" t="n">
-        <v>0.372439247269173</v>
+        <v>0.37301204250912</v>
       </c>
       <c r="AG23" s="0" t="n">
         <v>0.0351605</v>
@@ -10033,27 +10033,27 @@
       </c>
       <c r="O24" s="58" t="n">
         <f aca="false">(L24/$F$2)^(1/$F$3)</f>
-        <v>5.67840607389441</v>
+        <v>5.83082156671566</v>
       </c>
       <c r="P24" s="59" t="n">
         <f aca="false">(M24/$G$2)^(1/$G$3)</f>
-        <v>8.12012830351049</v>
+        <v>8.02223532255085</v>
       </c>
       <c r="Q24" s="60" t="n">
         <f aca="false">(N24/$H$2)^(1/$H$3)</f>
-        <v>8.70144578089188</v>
+        <v>8.75853251963667</v>
       </c>
       <c r="R24" s="55" t="n">
         <f aca="false">O24*$K24/$I24</f>
-        <v>21.5962605197468</v>
+        <v>22.1759310553476</v>
       </c>
       <c r="S24" s="53" t="n">
         <f aca="false">P24*$K24/$I24</f>
-        <v>30.8826815156092</v>
+        <v>30.5103724041531</v>
       </c>
       <c r="T24" s="54" t="n">
         <f aca="false">Q24*$K24/$I24</f>
-        <v>33.0935631473275</v>
+        <v>33.3106769053278</v>
       </c>
       <c r="U24" s="42" t="n">
         <v>3.5085</v>
@@ -10108,27 +10108,27 @@
       </c>
       <c r="P25" s="1" t="n">
         <f aca="false">(M25/$G$2)^(1/$G$3)</f>
-        <v>0.0273742184686809</v>
+        <v>0.0283563087879794</v>
       </c>
       <c r="Q25" s="1" t="n">
         <f aca="false">(N25/$H$2)^(1/$H$3)</f>
-        <v>0.0298195478363678</v>
+        <v>0.030248739694197</v>
       </c>
       <c r="S25" s="1" t="n">
         <f aca="false">P25*$K25/$I25</f>
-        <v>0.0654624343728528</v>
+        <v>0.0678109954157496</v>
       </c>
       <c r="T25" s="1" t="n">
         <f aca="false">Q25*$K25/$I25</f>
-        <v>0.0713101707542716</v>
+        <v>0.0723365359036056</v>
       </c>
       <c r="X25" s="1" t="n">
         <f aca="false">AVERAGE(S25:S26)/100</f>
-        <v>0.000614812083227204</v>
+        <v>0.000637227199553521</v>
       </c>
       <c r="Y25" s="1" t="n">
         <f aca="false">AVERAGE(T25:T26)/100</f>
-        <v>0.000702968295364527</v>
+        <v>0.00071310693407201</v>
       </c>
       <c r="Z25" s="1" t="e">
         <f aca="false">AVERAGE(U25:V26)/100</f>
@@ -10192,19 +10192,19 @@
       </c>
       <c r="P26" s="1" t="n">
         <f aca="false">(M26/$G$2)^(1/$G$3)</f>
-        <v>0.0236963568167877</v>
+        <v>0.0245759914955147</v>
       </c>
       <c r="Q26" s="1" t="n">
         <f aca="false">(N26/$H$2)^(1/$H$3)</f>
-        <v>0.0285524655108071</v>
+        <v>0.0289651377299807</v>
       </c>
       <c r="S26" s="1" t="n">
         <f aca="false">P26*$K26/$I26</f>
-        <v>0.0574999822725881</v>
+        <v>0.0596344444949547</v>
       </c>
       <c r="T26" s="1" t="n">
         <f aca="false">Q26*$K26/$I26</f>
-        <v>0.0692834883186338</v>
+        <v>0.0702848509107965</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10248,30 +10248,30 @@
       </c>
       <c r="P27" s="1" t="n">
         <f aca="false">(M27/$G$2)^(1/$G$3)</f>
-        <v>17.6167182287165</v>
+        <v>17.2925119951485</v>
       </c>
       <c r="Q27" s="1" t="n">
         <f aca="false">(N27/$H$2)^(1/$H$3)</f>
-        <v>18.0620696309114</v>
+        <v>18.1624448306182</v>
       </c>
       <c r="S27" s="1" t="n">
         <f aca="false">P27*$K27/$I27</f>
-        <v>46.0590222057712</v>
+        <v>45.2113829396327</v>
       </c>
       <c r="T27" s="1" t="n">
         <f aca="false">Q27*$K27/$I27</f>
-        <v>47.2233962882055</v>
+        <v>47.4858278882449</v>
       </c>
       <c r="U27" s="1" t="n">
         <v>2.9064</v>
       </c>
       <c r="X27" s="1" t="n">
         <f aca="false">AVERAGE(S27:S28)/100</f>
-        <v>0.461782281124586</v>
+        <v>0.45324270269083</v>
       </c>
       <c r="Y27" s="1" t="n">
         <f aca="false">AVERAGE(T27:T28)/100</f>
-        <v>0.473514302831314</v>
+        <v>0.47613854337922</v>
       </c>
       <c r="Z27" s="1" t="n">
         <f aca="false">AVERAGE(U27:V28)/100</f>
@@ -10279,19 +10279,19 @@
       </c>
       <c r="AA27" s="1" t="n">
         <f aca="false">SUM(W27:Z27)</f>
-        <v>0.9645125839559</v>
+        <v>0.95859724607005</v>
       </c>
       <c r="AE27" s="1" t="n">
         <f aca="false">IFERROR(X27/$AA27,"")</f>
-        <v>0.478772686646149</v>
+        <v>0.472818698936372</v>
       </c>
       <c r="AF27" s="1" t="n">
         <f aca="false">IFERROR(Y27/$AA27,"")</f>
-        <v>0.490936365899156</v>
+        <v>0.496703433408806</v>
       </c>
       <c r="AG27" s="1" t="n">
         <f aca="false">IFERROR(Z27/$AA27,"")</f>
-        <v>0.0302909474546947</v>
+        <v>0.0304778676548222</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10335,19 +10335,19 @@
       </c>
       <c r="P28" s="1" t="n">
         <f aca="false">(M28/$G$2)^(1/$G$3)</f>
-        <v>18.0052168436837</v>
+        <v>17.6706526539657</v>
       </c>
       <c r="Q28" s="1" t="n">
         <f aca="false">(N28/$H$2)^(1/$H$3)</f>
-        <v>18.4649121071122</v>
+        <v>18.5669667081449</v>
       </c>
       <c r="S28" s="1" t="n">
         <f aca="false">P28*$K28/$I28</f>
-        <v>46.2974340191459</v>
+        <v>45.4371575985333</v>
       </c>
       <c r="T28" s="1" t="n">
         <f aca="false">Q28*$K28/$I28</f>
-        <v>47.4794642780572</v>
+        <v>47.741880787599</v>
       </c>
       <c r="U28" s="1" t="n">
         <v>2.9368</v>
@@ -10411,13 +10411,13 @@
         <v>2</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>157.651809</v>
+        <v>154.574631</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>156.413729</v>
+        <v>155.54848</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>141.723567</v>
+        <v>139.485507</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10425,13 +10425,13 @@
         <v>3</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>1.05643576</v>
+        <v>1.05174512</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.03759299</v>
+        <v>1.046301</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.05899702</v>
+        <v>1.06895477</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>4</v>
@@ -10583,27 +10583,27 @@
       </c>
       <c r="O5" s="24" t="n">
         <f aca="false">(L5/$F$2)^(1/$F$3)</f>
-        <v>1.23252865289927</v>
+        <v>1.25701807989117</v>
       </c>
       <c r="P5" s="47" t="n">
         <f aca="false">(M5/$G$2)^(1/$G$3)</f>
-        <v>12.0959617831771</v>
+        <v>11.9105672664945</v>
       </c>
       <c r="Q5" s="26" t="n">
         <f aca="false">(N5/$H$2)^(1/$H$3)</f>
-        <v>11.8365845646425</v>
+        <v>11.7407520931948</v>
       </c>
       <c r="R5" s="25" t="n">
         <f aca="false">O5*$K5/$I5</f>
-        <v>6.00669373445349</v>
+        <v>6.12604226832046</v>
       </c>
       <c r="S5" s="47" t="n">
         <f aca="false">P5*$K5/$I5</f>
-        <v>58.9493296438089</v>
+        <v>58.0458146795605</v>
       </c>
       <c r="T5" s="26" t="n">
         <f aca="false">Q5*$K5/$I5</f>
-        <v>57.6852620622829</v>
+        <v>57.2182252072384</v>
       </c>
       <c r="U5" s="27" t="n">
         <v>1.6603</v>
@@ -10613,15 +10613,15 @@
       </c>
       <c r="W5" s="48" t="n">
         <f aca="false">AVERAGE(R5:R6)/100</f>
-        <v>0.0371682083093487</v>
+        <v>0.0378641670534031</v>
       </c>
       <c r="X5" s="49" t="n">
         <f aca="false">AVERAGE(S5:S6)/100</f>
-        <v>0.294776056881034</v>
+        <v>0.290260307098293</v>
       </c>
       <c r="Y5" s="49" t="n">
         <f aca="false">AVERAGE(T5:T6)/100</f>
-        <v>0.2884668648548</v>
+        <v>0.286134767220147</v>
       </c>
       <c r="Z5" s="50" t="n">
         <f aca="false">AVERAGE(U5:V6)/100</f>
@@ -10629,16 +10629,16 @@
       </c>
       <c r="AA5" s="2" t="n">
         <f aca="false">SUM(W5:Z5)</f>
-        <v>0.637039130045182</v>
+        <v>0.630887241371843</v>
       </c>
       <c r="AD5" s="0" t="n">
-        <v>0.0589128298502947</v>
+        <v>0.0606170150578151</v>
       </c>
       <c r="AE5" s="0" t="n">
-        <v>0.467229723274154</v>
+        <v>0.464679795576856</v>
       </c>
       <c r="AF5" s="0" t="n">
-        <v>0.457229446875551</v>
+        <v>0.458075189365329</v>
       </c>
       <c r="AG5" s="0" t="n">
         <v>0.016628</v>
@@ -10691,27 +10691,27 @@
       </c>
       <c r="O6" s="24" t="n">
         <f aca="false">(L6/$F$2)^(1/$F$3)</f>
-        <v>0.330941953169823</v>
+        <v>0.3355440498438</v>
       </c>
       <c r="P6" s="47" t="n">
         <f aca="false">(M6/$G$2)^(1/$G$3)</f>
-        <v>0.00136410864781436</v>
+        <v>0.00144876230540947</v>
       </c>
       <c r="Q6" s="26" t="n">
         <f aca="false">(N6/$H$2)^(1/$H$3)</f>
-        <v>0.00188110575587301</v>
+        <v>0.00202427830464385</v>
       </c>
       <c r="R6" s="25" t="n">
         <f aca="false">O6*$K6/$I6</f>
-        <v>1.42694792741626</v>
+        <v>1.44679114236015</v>
       </c>
       <c r="S6" s="47" t="n">
         <f aca="false">P6*$K6/$I6</f>
-        <v>0.00588173239785784</v>
+        <v>0.00624674009814041</v>
       </c>
       <c r="T6" s="26" t="n">
         <f aca="false">Q6*$K6/$I6</f>
-        <v>0.00811090867713699</v>
+        <v>0.0087282367909486</v>
       </c>
       <c r="U6" s="27" t="n">
         <v>1.6197</v>
@@ -10768,27 +10768,27 @@
       </c>
       <c r="O7" s="52" t="n">
         <f aca="false">(L7/$F$2)^(1/$F$3)</f>
-        <v>0.0392115591625741</v>
+        <v>0.0393804330512682</v>
       </c>
       <c r="P7" s="53" t="n">
         <f aca="false">(M7/$G$2)^(1/$G$3)</f>
-        <v>0.00585442132563692</v>
+        <v>0.0061428080129521</v>
       </c>
       <c r="Q7" s="54" t="n">
         <f aca="false">(N7/$H$2)^(1/$H$3)</f>
-        <v>0.0137392895308659</v>
+        <v>0.0145136602751698</v>
       </c>
       <c r="R7" s="55" t="n">
         <f aca="false">O7*$K7/$I7</f>
-        <v>0.163964943650385</v>
+        <v>0.164671097606899</v>
       </c>
       <c r="S7" s="53" t="n">
         <f aca="false">P7*$K7/$I7</f>
-        <v>0.0244805328649077</v>
+        <v>0.0256864351025389</v>
       </c>
       <c r="T7" s="54" t="n">
         <f aca="false">Q7*$K7/$I7</f>
-        <v>0.0574514730308127</v>
+        <v>0.0606895400234532</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>98.0875</v>
@@ -10796,15 +10796,15 @@
       <c r="V7" s="2"/>
       <c r="W7" s="51" t="n">
         <f aca="false">AVERAGE(R7:R8)/100</f>
-        <v>0.00162434254587306</v>
+        <v>0.00163139153517796</v>
       </c>
       <c r="X7" s="0" t="n">
         <f aca="false">AVERAGE(S7:S8)/100</f>
-        <v>0.000246400830026448</v>
+        <v>0.000258487986468277</v>
       </c>
       <c r="Y7" s="1" t="n">
         <f aca="false">AVERAGE(T7:T8)/100</f>
-        <v>0.000575143848132982</v>
+        <v>0.000607458444121444</v>
       </c>
       <c r="Z7" s="33" t="n">
         <f aca="false">AVERAGE(U7:V8)/100</f>
@@ -10812,19 +10812,19 @@
       </c>
       <c r="AA7" s="2" t="n">
         <f aca="false">SUM(W7:Z7)</f>
-        <v>0.986732887224033</v>
+        <v>0.986784337965768</v>
       </c>
       <c r="AD7" s="0" t="n">
-        <v>0.00162434254587306</v>
+        <v>0.00163139153517796</v>
       </c>
       <c r="AE7" s="0" t="n">
-        <v>0.000246400830026448</v>
+        <v>0.000258487986468277</v>
       </c>
       <c r="AF7" s="0" t="n">
-        <v>0.000575143848132982</v>
+        <v>0.000607458444121444</v>
       </c>
       <c r="AG7" s="0" t="n">
-        <v>0.997554112775968</v>
+        <v>0.997502662034232</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10874,27 +10874,27 @@
       </c>
       <c r="O8" s="52" t="n">
         <f aca="false">(L8/$F$2)^(1/$F$3)</f>
-        <v>0.0397966371453092</v>
+        <v>0.0399706709590058</v>
       </c>
       <c r="P8" s="53" t="n">
         <f aca="false">(M8/$G$2)^(1/$G$3)</f>
-        <v>0.00613374848598964</v>
+        <v>0.00643339866382133</v>
       </c>
       <c r="Q8" s="54" t="n">
         <f aca="false">(N8/$H$2)^(1/$H$3)</f>
-        <v>0.0142407209744848</v>
+        <v>0.0150383308511433</v>
       </c>
       <c r="R8" s="55" t="n">
         <f aca="false">O8*$K8/$I8</f>
-        <v>0.160903565524228</v>
+        <v>0.161607209428694</v>
       </c>
       <c r="S8" s="53" t="n">
         <f aca="false">P8*$K8/$I8</f>
-        <v>0.0247996331403819</v>
+        <v>0.0260111621911166</v>
       </c>
       <c r="T8" s="54" t="n">
         <f aca="false">Q8*$K8/$I8</f>
-        <v>0.0575772965957836</v>
+        <v>0.0608021488008356</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>98.808</v>
@@ -10955,27 +10955,27 @@
       </c>
       <c r="O9" s="24" t="n">
         <f aca="false">(L9/$F$2)^(1/$F$3)</f>
-        <v>0.323110404339002</v>
+        <v>0.327568605956775</v>
       </c>
       <c r="P9" s="47" t="n">
         <f aca="false">(M9/$G$2)^(1/$G$3)</f>
-        <v>0.000256487610533892</v>
+        <v>0.000276219929810291</v>
       </c>
       <c r="Q9" s="26" t="n">
         <f aca="false">(N9/$H$2)^(1/$H$3)</f>
-        <v>0.000841108732681711</v>
+        <v>0.000911938296869935</v>
       </c>
       <c r="R9" s="25" t="n">
         <f aca="false">O9*$K9/$I9</f>
-        <v>2.03622057166707</v>
+        <v>2.06431586579824</v>
       </c>
       <c r="S9" s="47" t="n">
         <f aca="false">P9*$K9/$I9</f>
-        <v>0.00161636809565219</v>
+        <v>0.00174071987726536</v>
       </c>
       <c r="T9" s="26" t="n">
         <f aca="false">Q9*$K9/$I9</f>
-        <v>0.00530061205549543</v>
+        <v>0.00574697532249489</v>
       </c>
       <c r="U9" s="27" t="n">
         <v>88.714</v>
@@ -10985,15 +10985,15 @@
       </c>
       <c r="W9" s="56" t="n">
         <f aca="false">AVERAGE(R9:R10)/100</f>
-        <v>0.0548043740600342</v>
+        <v>0.0558644672205221</v>
       </c>
       <c r="X9" s="57" t="n">
         <f aca="false">AVERAGE(S9:S10)/100</f>
-        <v>0.444956914537688</v>
+        <v>0.437487937746624</v>
       </c>
       <c r="Y9" s="57" t="n">
         <f aca="false">AVERAGE(T9:T10)/100</f>
-        <v>0.431767192496147</v>
+        <v>0.427596684873136</v>
       </c>
       <c r="Z9" s="29" t="n">
         <f aca="false">AVERAGE(U9:V10)/100</f>
@@ -11001,19 +11001,19 @@
       </c>
       <c r="AA9" s="2" t="n">
         <f aca="false">SUM(W9:Z9)</f>
-        <v>1.85865623109387</v>
+        <v>1.84807683984028</v>
       </c>
       <c r="AD9" s="0" t="n">
-        <v>0.0203622057166707</v>
+        <v>0.0206431586579825</v>
       </c>
       <c r="AE9" s="0" t="n">
-        <v>1.61636809565219E-005</v>
+        <v>1.74071987726536E-005</v>
       </c>
       <c r="AF9" s="0" t="n">
-        <v>5.30061205549543E-005</v>
+        <v>5.74697532249489E-005</v>
       </c>
       <c r="AG9" s="0" t="n">
-        <v>0.979568624481818</v>
+        <v>0.97928196439002</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11063,27 +11063,27 @@
       </c>
       <c r="O10" s="24" t="n">
         <f aca="false">(L10/$F$2)^(1/$F$3)</f>
-        <v>1.44994382616164</v>
+        <v>1.4798249286884</v>
       </c>
       <c r="P10" s="47" t="n">
         <f aca="false">(M10/$G$2)^(1/$G$3)</f>
-        <v>14.4577211744751</v>
+        <v>14.2150115297142</v>
       </c>
       <c r="Q10" s="26" t="n">
         <f aca="false">(N10/$H$2)^(1/$H$3)</f>
-        <v>14.028549012482</v>
+        <v>13.8929642015677</v>
       </c>
       <c r="R10" s="25" t="n">
         <f aca="false">O10*$K10/$I10</f>
-        <v>8.92465424033978</v>
+        <v>9.10857757830618</v>
       </c>
       <c r="S10" s="47" t="n">
         <f aca="false">P10*$K10/$I10</f>
-        <v>88.9897665394419</v>
+        <v>87.4958468294476</v>
       </c>
       <c r="T10" s="26" t="n">
         <f aca="false">Q10*$K10/$I10</f>
-        <v>86.348137887174</v>
+        <v>85.5135899993047</v>
       </c>
       <c r="U10" s="27" t="n">
         <v>99.5197</v>
@@ -11142,27 +11142,27 @@
       </c>
       <c r="O11" s="52" t="n">
         <f aca="false">(L11/$F$2)^(1/$F$3)</f>
-        <v>12.041804984059</v>
+        <v>12.4065458409033</v>
       </c>
       <c r="P11" s="53" t="n">
         <f aca="false">(M11/$G$2)^(1/$G$3)</f>
-        <v>0.271039945267602</v>
+        <v>0.275457412832031</v>
       </c>
       <c r="Q11" s="54" t="n">
         <f aca="false">(N11/$H$2)^(1/$H$3)</f>
-        <v>0.291483063512154</v>
+        <v>0.299273129837932</v>
       </c>
       <c r="R11" s="55" t="n">
         <f aca="false">O11*$K11/$I11</f>
-        <v>73.9049780951323</v>
+        <v>76.1435266408993</v>
       </c>
       <c r="S11" s="53" t="n">
         <f aca="false">P11*$K11/$I11</f>
-        <v>1.66347165100459</v>
+        <v>1.6905832712324</v>
       </c>
       <c r="T11" s="54" t="n">
         <f aca="false">Q11*$K11/$I11</f>
-        <v>1.78893857295358</v>
+        <v>1.83674906996199</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>8.078</v>
@@ -11170,15 +11170,15 @@
       <c r="V11" s="2"/>
       <c r="W11" s="51" t="n">
         <f aca="false">AVERAGE(R11:R12)/100</f>
-        <v>0.735334099628945</v>
+        <v>0.757721315084296</v>
       </c>
       <c r="X11" s="0" t="n">
         <f aca="false">AVERAGE(S11:S12)/100</f>
-        <v>0.0165595971269269</v>
+        <v>0.0168246793815169</v>
       </c>
       <c r="Y11" s="1" t="n">
         <f aca="false">AVERAGE(T11:T12)/100</f>
-        <v>0.0177858907038867</v>
+        <v>0.0182556129021259</v>
       </c>
       <c r="Z11" s="33" t="n">
         <f aca="false">AVERAGE(U11:V12)/100</f>
@@ -11186,16 +11186,16 @@
       </c>
       <c r="AA11" s="2" t="n">
         <f aca="false">SUM(W11:Z11)</f>
-        <v>0.851212587459759</v>
+        <v>0.874334607367939</v>
       </c>
       <c r="AD11" s="0" t="n">
-        <v>0.877482156845181</v>
+        <v>0.877826200948331</v>
       </c>
       <c r="AE11" s="0" t="n">
-        <v>0.0197607468642559</v>
+        <v>0.0194915255643925</v>
       </c>
       <c r="AF11" s="0" t="n">
-        <v>0.021224096290563</v>
+        <v>0.0211492734872764</v>
       </c>
       <c r="AG11" s="0" t="n">
         <v>0.081533</v>
@@ -11248,27 +11248,27 @@
       </c>
       <c r="O12" s="52" t="n">
         <f aca="false">(L12/$F$2)^(1/$F$3)</f>
-        <v>12.8888194740849</v>
+        <v>13.2832423985749</v>
       </c>
       <c r="P12" s="53" t="n">
         <f aca="false">(M12/$G$2)^(1/$G$3)</f>
-        <v>0.290404741663408</v>
+        <v>0.294968359499128</v>
       </c>
       <c r="Q12" s="54" t="n">
         <f aca="false">(N12/$H$2)^(1/$H$3)</f>
-        <v>0.311508294574734</v>
+        <v>0.319635646804106</v>
       </c>
       <c r="R12" s="55" t="n">
         <f aca="false">O12*$K12/$I12</f>
-        <v>73.1618418306567</v>
+        <v>75.40073637596</v>
       </c>
       <c r="S12" s="53" t="n">
         <f aca="false">P12*$K12/$I12</f>
-        <v>1.64844777438079</v>
+        <v>1.67435260507097</v>
       </c>
       <c r="T12" s="54" t="n">
         <f aca="false">Q12*$K12/$I12</f>
-        <v>1.76823956782376</v>
+        <v>1.81437351046319</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>8.2286</v>
@@ -11327,27 +11327,27 @@
       </c>
       <c r="O13" s="24" t="n">
         <f aca="false">(L13/$F$2)^(1/$F$3)</f>
-        <v>8.79919789165704</v>
+        <v>9.05304606454047</v>
       </c>
       <c r="P13" s="47" t="n">
         <f aca="false">(M13/$G$2)^(1/$G$3)</f>
-        <v>5.05186457743362</v>
+        <v>5.01071382670096</v>
       </c>
       <c r="Q13" s="26" t="n">
         <f aca="false">(N13/$H$2)^(1/$H$3)</f>
-        <v>5.13497204844964</v>
+        <v>5.13317637100666</v>
       </c>
       <c r="R13" s="25" t="n">
         <f aca="false">O13*$K13/$I13</f>
-        <v>39.8754604952312</v>
+        <v>41.0258281667206</v>
       </c>
       <c r="S13" s="47" t="n">
         <f aca="false">P13*$K13/$I13</f>
-        <v>22.8936124479838</v>
+        <v>22.7071289576255</v>
       </c>
       <c r="T13" s="26" t="n">
         <f aca="false">Q13*$K13/$I13</f>
-        <v>23.2702318533161</v>
+        <v>23.2620943542144</v>
       </c>
       <c r="U13" s="27" t="n">
         <v>3.6077</v>
@@ -11355,15 +11355,15 @@
       <c r="V13" s="27"/>
       <c r="W13" s="56" t="n">
         <f aca="false">AVERAGE(R13:R14)/100</f>
-        <v>0.42471596076918</v>
+        <v>0.437176251980643</v>
       </c>
       <c r="X13" s="57" t="n">
         <f aca="false">AVERAGE(S13:S14)/100</f>
-        <v>0.245641198687674</v>
+        <v>0.243408168926117</v>
       </c>
       <c r="Y13" s="57" t="n">
         <f aca="false">AVERAGE(T13:T14)/100</f>
-        <v>0.247494294870205</v>
+        <v>0.247166151136155</v>
       </c>
       <c r="Z13" s="29" t="n">
         <f aca="false">AVERAGE(U13:V14)/100</f>
@@ -11371,16 +11371,16 @@
       </c>
       <c r="AA13" s="2" t="n">
         <f aca="false">SUM(W13:Z13)</f>
-        <v>0.953506954327059</v>
+        <v>0.963406072042916</v>
       </c>
       <c r="AD13" s="0" t="n">
-        <v>0.446229614715009</v>
+        <v>0.454420106904171</v>
       </c>
       <c r="AE13" s="0" t="n">
-        <v>0.258083960984233</v>
+        <v>0.253009091055688</v>
       </c>
       <c r="AF13" s="0" t="n">
-        <v>0.260030924300758</v>
+        <v>0.256915302040142</v>
       </c>
       <c r="AG13" s="0" t="n">
         <v>0.0356555</v>
@@ -11433,27 +11433,27 @@
       </c>
       <c r="O14" s="24" t="n">
         <f aca="false">(L14/$F$2)^(1/$F$3)</f>
-        <v>10.7553460377915</v>
+        <v>11.0755384644693</v>
       </c>
       <c r="P14" s="47" t="n">
         <f aca="false">(M14/$G$2)^(1/$G$3)</f>
-        <v>6.26085414746491</v>
+        <v>6.19877631511023</v>
       </c>
       <c r="Q14" s="26" t="n">
         <f aca="false">(N14/$H$2)^(1/$H$3)</f>
-        <v>6.25942221624411</v>
+        <v>6.24570201687997</v>
       </c>
       <c r="R14" s="25" t="n">
         <f aca="false">O14*$K14/$I14</f>
-        <v>45.0677316586047</v>
+        <v>46.4094222294081</v>
       </c>
       <c r="S14" s="47" t="n">
         <f aca="false">P14*$K14/$I14</f>
-        <v>26.2346272895511</v>
+        <v>25.974504827598</v>
       </c>
       <c r="T14" s="26" t="n">
         <f aca="false">Q14*$K14/$I14</f>
-        <v>26.2286271207248</v>
+        <v>26.1711358730166</v>
       </c>
       <c r="U14" s="27" t="n">
         <v>3.5234</v>
@@ -11510,27 +11510,27 @@
       </c>
       <c r="O15" s="52" t="n">
         <f aca="false">(L15/$F$2)^(1/$F$3)</f>
-        <v>0.296199401365627</v>
+        <v>0.300169852296395</v>
       </c>
       <c r="P15" s="53" t="n">
         <f aca="false">(M15/$G$2)^(1/$G$3)</f>
-        <v>0.00356242899858512</v>
+        <v>0.00375339868791963</v>
       </c>
       <c r="Q15" s="54" t="n">
         <f aca="false">(N15/$H$2)^(1/$H$3)</f>
-        <v>0.0105903592021933</v>
+        <v>0.0112144120321199</v>
       </c>
       <c r="R15" s="55" t="n">
         <f aca="false">O15*$K15/$I15</f>
-        <v>1.2408192226222</v>
+        <v>1.25745197682313</v>
       </c>
       <c r="S15" s="53" t="n">
         <f aca="false">P15*$K15/$I15</f>
-        <v>0.0149234953220407</v>
+        <v>0.0157234930950677</v>
       </c>
       <c r="T15" s="54" t="n">
         <f aca="false">Q15*$K15/$I15</f>
-        <v>0.0443644423721657</v>
+        <v>0.0469786838045746</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>98.1203</v>
@@ -11538,15 +11538,15 @@
       <c r="V15" s="2"/>
       <c r="W15" s="51" t="n">
         <f aca="false">AVERAGE(R15:R16)/100</f>
-        <v>0.0123845931177132</v>
+        <v>0.0125515292950584</v>
       </c>
       <c r="X15" s="0" t="n">
         <f aca="false">AVERAGE(S15:S16)/100</f>
-        <v>0.00013876520863503</v>
+        <v>0.000146268243121633</v>
       </c>
       <c r="Y15" s="1" t="n">
         <f aca="false">AVERAGE(T15:T16)/100</f>
-        <v>0.000425334397401514</v>
+        <v>0.000450496715408967</v>
       </c>
       <c r="Z15" s="33" t="n">
         <f aca="false">AVERAGE(U15:V16)/100</f>
@@ -11554,19 +11554,19 @@
       </c>
       <c r="AA15" s="2" t="n">
         <f aca="false">SUM(W15:Z15)</f>
-        <v>0.98855819272375</v>
+        <v>0.988757794253589</v>
       </c>
       <c r="AD15" s="0" t="n">
-        <v>0.0123845931177132</v>
+        <v>0.0125515292950584</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>0.00013876520863503</v>
+        <v>0.000146268243121633</v>
       </c>
       <c r="AF15" s="0" t="n">
-        <v>0.000425334397401514</v>
+        <v>0.000450496715408967</v>
       </c>
       <c r="AG15" s="0" t="n">
-        <v>0.98705130727625</v>
+        <v>0.986851705746411</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11616,27 +11616,27 @@
       </c>
       <c r="O16" s="52" t="n">
         <f aca="false">(L16/$F$2)^(1/$F$3)</f>
-        <v>0.306170962198146</v>
+        <v>0.310320900016394</v>
       </c>
       <c r="P16" s="53" t="n">
         <f aca="false">(M16/$G$2)^(1/$G$3)</f>
-        <v>0.00317776593407382</v>
+        <v>0.00335130065915337</v>
       </c>
       <c r="Q16" s="54" t="n">
         <f aca="false">(N16/$H$2)^(1/$H$3)</f>
-        <v>0.0100816360916674</v>
+        <v>0.010680608478326</v>
       </c>
       <c r="R16" s="55" t="n">
         <f aca="false">O16*$K16/$I16</f>
-        <v>1.23609940092043</v>
+        <v>1.25285388218856</v>
       </c>
       <c r="S16" s="53" t="n">
         <f aca="false">P16*$K16/$I16</f>
-        <v>0.0128295464049653</v>
+        <v>0.0135301555292588</v>
       </c>
       <c r="T16" s="54" t="n">
         <f aca="false">Q16*$K16/$I16</f>
-        <v>0.0407024371081372</v>
+        <v>0.0431206592772188</v>
       </c>
       <c r="U16" s="2" t="n">
         <v>97.0016</v>
@@ -11695,27 +11695,27 @@
       </c>
       <c r="O17" s="24" t="n">
         <f aca="false">(L17/$F$2)^(1/$F$3)</f>
-        <v>5.96518018649959</v>
+        <v>6.12663912235963</v>
       </c>
       <c r="P17" s="47" t="n">
         <f aca="false">(M17/$G$2)^(1/$G$3)</f>
-        <v>9.2685466997966</v>
+        <v>9.14673341961011</v>
       </c>
       <c r="Q17" s="26" t="n">
         <f aca="false">(N17/$H$2)^(1/$H$3)</f>
-        <v>9.0079666883826</v>
+        <v>8.95779435892392</v>
       </c>
       <c r="R17" s="25" t="n">
         <f aca="false">O17*$K17/$I17</f>
-        <v>27.6037781600143</v>
+        <v>28.3509268643434</v>
       </c>
       <c r="S17" s="47" t="n">
         <f aca="false">P17*$K17/$I17</f>
-        <v>42.8900551145046</v>
+        <v>42.3263660626933</v>
       </c>
       <c r="T17" s="26" t="n">
         <f aca="false">Q17*$K17/$I17</f>
-        <v>41.6842251809369</v>
+        <v>41.4520535098643</v>
       </c>
       <c r="U17" s="27" t="n">
         <v>2.3119</v>
@@ -11723,15 +11723,15 @@
       <c r="V17" s="27"/>
       <c r="W17" s="56" t="n">
         <f aca="false">AVERAGE(R17:R18)/100</f>
-        <v>0.273924177695734</v>
+        <v>0.281392807006491</v>
       </c>
       <c r="X17" s="57" t="n">
         <f aca="false">AVERAGE(S17:S18)/100</f>
-        <v>0.42547239424527</v>
+        <v>0.419730505772256</v>
       </c>
       <c r="Y17" s="57" t="n">
         <f aca="false">AVERAGE(T17:T18)/100</f>
-        <v>0.41425818651336</v>
+        <v>0.411778854153103</v>
       </c>
       <c r="Z17" s="29" t="n">
         <f aca="false">AVERAGE(U17:V18)/100</f>
@@ -11739,16 +11739,16 @@
       </c>
       <c r="AA17" s="2" t="n">
         <f aca="false">SUM(W17:Z17)</f>
-        <v>1.13711025845436</v>
+        <v>1.13635766693185</v>
       </c>
       <c r="AD17" s="0" t="n">
-        <v>0.240199350036499</v>
+        <v>0.246915323005726</v>
       </c>
       <c r="AE17" s="0" t="n">
-        <v>0.373089346898414</v>
+        <v>0.368303278646788</v>
       </c>
       <c r="AF17" s="0" t="n">
-        <v>0.363255803065087</v>
+        <v>0.361325898347486</v>
       </c>
       <c r="AG17" s="0" t="n">
         <v>0.0234555</v>
@@ -11801,27 +11801,27 @@
       </c>
       <c r="O18" s="24" t="n">
         <f aca="false">(L18/$F$2)^(1/$F$3)</f>
-        <v>6.50928478364449</v>
+        <v>6.68807412452421</v>
       </c>
       <c r="P18" s="47" t="n">
         <f aca="false">(M18/$G$2)^(1/$G$3)</f>
-        <v>10.1070613032404</v>
+        <v>9.96704081645041</v>
       </c>
       <c r="Q18" s="26" t="n">
         <f aca="false">(N18/$H$2)^(1/$H$3)</f>
-        <v>9.85871909132415</v>
+        <v>9.79556979835899</v>
       </c>
       <c r="R18" s="25" t="n">
         <f aca="false">O18*$K18/$I18</f>
-        <v>27.1810573791326</v>
+        <v>27.9276345369548</v>
       </c>
       <c r="S18" s="47" t="n">
         <f aca="false">P18*$K18/$I18</f>
-        <v>42.2044237345494</v>
+        <v>41.619735091758</v>
       </c>
       <c r="T18" s="26" t="n">
         <f aca="false">Q18*$K18/$I18</f>
-        <v>41.167412121735</v>
+        <v>40.9037173207562</v>
       </c>
       <c r="U18" s="27" t="n">
         <v>2.3792</v>
@@ -11878,27 +11878,27 @@
       </c>
       <c r="O19" s="52" t="n">
         <f aca="false">(L19/$F$2)^(1/$F$3)</f>
-        <v>0.169784122236401</v>
+        <v>0.171633507272418</v>
       </c>
       <c r="P19" s="53" t="n">
         <f aca="false">(M19/$G$2)^(1/$G$3)</f>
-        <v>0.00532499471071268</v>
+        <v>0.00559171141190829</v>
       </c>
       <c r="Q19" s="54" t="n">
         <f aca="false">(N19/$H$2)^(1/$H$3)</f>
-        <v>0.0128813331481244</v>
+        <v>0.0136155238041727</v>
       </c>
       <c r="R19" s="55" t="n">
         <f aca="false">O19*$K19/$I19</f>
-        <v>0.707081007817432</v>
+        <v>0.714782935523537</v>
       </c>
       <c r="S19" s="53" t="n">
         <f aca="false">P19*$K19/$I19</f>
-        <v>0.0221764118875067</v>
+        <v>0.0232871772017128</v>
       </c>
       <c r="T19" s="54" t="n">
         <f aca="false">Q19*$K19/$I19</f>
-        <v>0.0536454522627624</v>
+        <v>0.0567030542468038</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>99.6209</v>
@@ -11906,15 +11906,15 @@
       <c r="V19" s="2"/>
       <c r="W19" s="51" t="n">
         <f aca="false">AVERAGE(R19:R20)/100</f>
-        <v>0.00704455845077207</v>
+        <v>0.00712153851695347</v>
       </c>
       <c r="X19" s="0" t="n">
         <f aca="false">AVERAGE(S19:S20)/100</f>
-        <v>0.00020048831385979</v>
+        <v>0.000210679215893882</v>
       </c>
       <c r="Y19" s="1" t="n">
         <f aca="false">AVERAGE(T19:T20)/100</f>
-        <v>0.000507374478552317</v>
+        <v>0.000536509075681631</v>
       </c>
       <c r="Z19" s="33" t="n">
         <f aca="false">AVERAGE(U19:V20)/100</f>
@@ -11922,19 +11922,19 @@
       </c>
       <c r="AA19" s="2" t="n">
         <f aca="false">SUM(W19:Z19)</f>
-        <v>1.00605342124318</v>
+        <v>1.00616972680853</v>
       </c>
       <c r="AD19" s="0" t="n">
-        <v>0.00704455845077207</v>
+        <v>0.00712153851695347</v>
       </c>
       <c r="AE19" s="0" t="n">
-        <v>0.00020048831385979</v>
+        <v>0.000210679215893882</v>
       </c>
       <c r="AF19" s="0" t="n">
-        <v>0.000507374478552317</v>
+        <v>0.000536509075681631</v>
       </c>
       <c r="AG19" s="0" t="n">
-        <v>0.992247578756816</v>
+        <v>0.992131273191471</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11984,27 +11984,27 @@
       </c>
       <c r="O20" s="52" t="n">
         <f aca="false">(L20/$F$2)^(1/$F$3)</f>
-        <v>0.172452686692222</v>
+        <v>0.174343264797044</v>
       </c>
       <c r="P20" s="53" t="n">
         <f aca="false">(M20/$G$2)^(1/$G$3)</f>
-        <v>0.0044035804385438</v>
+        <v>0.00463146335735174</v>
       </c>
       <c r="Q20" s="54" t="n">
         <f aca="false">(N20/$H$2)^(1/$H$3)</f>
-        <v>0.0117525725693328</v>
+        <v>0.0124330447190477</v>
       </c>
       <c r="R20" s="55" t="n">
         <f aca="false">O20*$K20/$I20</f>
-        <v>0.701830682336982</v>
+        <v>0.709524767867156</v>
       </c>
       <c r="S20" s="53" t="n">
         <f aca="false">P20*$K20/$I20</f>
-        <v>0.0179212508844512</v>
+        <v>0.0188486659770636</v>
       </c>
       <c r="T20" s="54" t="n">
         <f aca="false">Q20*$K20/$I20</f>
-        <v>0.047829443447701</v>
+        <v>0.0505987608895223</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>99.2358</v>
@@ -12065,27 +12065,27 @@
       </c>
       <c r="O21" s="24" t="n">
         <f aca="false">(L21/$F$2)^(1/$F$3)</f>
-        <v>0.374426523052287</v>
+        <v>0.379842395230488</v>
       </c>
       <c r="P21" s="47" t="n">
         <f aca="false">(M21/$G$2)^(1/$G$3)</f>
-        <v>0.00155549823039483</v>
+        <v>0.00165022489348844</v>
       </c>
       <c r="Q21" s="26" t="n">
         <f aca="false">(N21/$H$2)^(1/$H$3)</f>
-        <v>0.00568596563130453</v>
+        <v>0.0060560046522217</v>
       </c>
       <c r="R21" s="25" t="n">
         <f aca="false">O21*$K21/$I21</f>
-        <v>1.55506741874517</v>
+        <v>1.57756060726118</v>
       </c>
       <c r="S21" s="47" t="n">
         <f aca="false">P21*$K21/$I21</f>
-        <v>0.00646029185722237</v>
+        <v>0.00685371042774055</v>
       </c>
       <c r="T21" s="26" t="n">
         <f aca="false">Q21*$K21/$I21</f>
-        <v>0.023614940056241</v>
+        <v>0.0251517853106898</v>
       </c>
       <c r="U21" s="27" t="n">
         <v>97.6309</v>
@@ -12093,15 +12093,15 @@
       <c r="V21" s="27"/>
       <c r="W21" s="56" t="n">
         <f aca="false">AVERAGE(R21:R22)/100</f>
-        <v>0.015828272966593</v>
+        <v>0.0160589950353215</v>
       </c>
       <c r="X21" s="57" t="n">
         <f aca="false">AVERAGE(S21:S22)/100</f>
-        <v>6.71542737384379E-005</v>
+        <v>7.12162537083959E-005</v>
       </c>
       <c r="Y21" s="57" t="n">
         <f aca="false">AVERAGE(T21:T22)/100</f>
-        <v>0.000242423712325938</v>
+        <v>0.000258119826172835</v>
       </c>
       <c r="Z21" s="29" t="n">
         <f aca="false">AVERAGE(U21:V22)/100</f>
@@ -12109,19 +12109,19 @@
       </c>
       <c r="AA21" s="2" t="n">
         <f aca="false">SUM(W21:Z21)</f>
-        <v>0.993130850952657</v>
+        <v>0.993381331115203</v>
       </c>
       <c r="AD21" s="0" t="n">
-        <v>0.015828272966593</v>
+        <v>0.0160589950353215</v>
       </c>
       <c r="AE21" s="0" t="n">
-        <v>6.71542737384379E-005</v>
+        <v>7.12162537083959E-005</v>
       </c>
       <c r="AF21" s="0" t="n">
-        <v>0.000242423712325938</v>
+        <v>0.000258119826172836</v>
       </c>
       <c r="AG21" s="0" t="n">
-        <v>0.983862149047343</v>
+        <v>0.983611668884797</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12171,27 +12171,27 @@
       </c>
       <c r="O22" s="24" t="n">
         <f aca="false">(L22/$F$2)^(1/$F$3)</f>
-        <v>0.393115841825227</v>
+        <v>0.398888687569406</v>
       </c>
       <c r="P22" s="47" t="n">
         <f aca="false">(M22/$G$2)^(1/$G$3)</f>
-        <v>0.00170139110874683</v>
+        <v>0.00180365608709433</v>
       </c>
       <c r="Q22" s="26" t="n">
         <f aca="false">(N22/$H$2)^(1/$H$3)</f>
-        <v>0.00607027887988089</v>
+        <v>0.00646139088899682</v>
       </c>
       <c r="R22" s="25" t="n">
         <f aca="false">O22*$K22/$I22</f>
-        <v>1.61058717457343</v>
+        <v>1.63423839980312</v>
       </c>
       <c r="S22" s="47" t="n">
         <f aca="false">P22*$K22/$I22</f>
-        <v>0.00697056289046521</v>
+        <v>0.00738954031393862</v>
       </c>
       <c r="T22" s="26" t="n">
         <f aca="false">Q22*$K22/$I22</f>
-        <v>0.0248698024089467</v>
+        <v>0.0264721799238773</v>
       </c>
       <c r="U22" s="27" t="n">
         <v>97.7677</v>
@@ -12248,27 +12248,27 @@
       </c>
       <c r="O23" s="52" t="n">
         <f aca="false">(L23/$F$2)^(1/$F$3)</f>
-        <v>14.9632595170875</v>
+        <v>15.4314317640129</v>
       </c>
       <c r="P23" s="53" t="n">
         <f aca="false">(M23/$G$2)^(1/$G$3)</f>
-        <v>3.28530731968043</v>
+        <v>3.27023682300473</v>
       </c>
       <c r="Q23" s="54" t="n">
         <f aca="false">(N23/$H$2)^(1/$H$3)</f>
-        <v>3.22530176539625</v>
+        <v>3.23817166814413</v>
       </c>
       <c r="R23" s="55" t="n">
         <f aca="false">O23*$K23/$I23</f>
-        <v>67.222754251558</v>
+        <v>69.3260277974407</v>
       </c>
       <c r="S23" s="53" t="n">
         <f aca="false">P23*$K23/$I23</f>
-        <v>14.7593113879715</v>
+        <v>14.691606868557</v>
       </c>
       <c r="T23" s="54" t="n">
         <f aca="false">Q23*$K23/$I23</f>
-        <v>14.4897351886971</v>
+        <v>14.5475534941722</v>
       </c>
       <c r="U23" s="2" t="n">
         <v>6.2927</v>
@@ -12276,15 +12276,15 @@
       <c r="V23" s="2"/>
       <c r="W23" s="51" t="n">
         <f aca="false">AVERAGE(R23:R24)/100</f>
-        <v>0.656371633161351</v>
+        <v>0.676890823319061</v>
       </c>
       <c r="X23" s="0" t="n">
         <f aca="false">AVERAGE(S23:S24)/100</f>
-        <v>0.143392920452288</v>
+        <v>0.14274789699773</v>
       </c>
       <c r="Y23" s="1" t="n">
         <f aca="false">AVERAGE(T23:T24)/100</f>
-        <v>0.141892808137823</v>
+        <v>0.142462818155592</v>
       </c>
       <c r="Z23" s="33" t="n">
         <f aca="false">AVERAGE(U23:V24)/100</f>
@@ -12292,16 +12292,16 @@
       </c>
       <c r="AA23" s="2" t="n">
         <f aca="false">SUM(W23:Z23)</f>
-        <v>1.00263386175146</v>
+        <v>1.02307803847238</v>
       </c>
       <c r="AD23" s="0" t="n">
-        <v>0.654535729562496</v>
+        <v>0.660654166544804</v>
       </c>
       <c r="AE23" s="0" t="n">
-        <v>0.142991843432185</v>
+        <v>0.139323787039444</v>
       </c>
       <c r="AF23" s="0" t="n">
-        <v>0.14149592700532</v>
+        <v>0.139045546415751</v>
       </c>
       <c r="AG23" s="0" t="n">
         <v>0.0609765</v>
@@ -12354,27 +12354,27 @@
       </c>
       <c r="O24" s="58" t="n">
         <f aca="false">(L24/$F$2)^(1/$F$3)</f>
-        <v>14.7870999221944</v>
+        <v>15.2489550469118</v>
       </c>
       <c r="P24" s="59" t="n">
         <f aca="false">(M24/$G$2)^(1/$G$3)</f>
-        <v>3.21343674551095</v>
+        <v>3.19928484060866</v>
       </c>
       <c r="Q24" s="60" t="n">
         <f aca="false">(N24/$H$2)^(1/$H$3)</f>
-        <v>3.20640784792654</v>
+        <v>3.21937855148007</v>
       </c>
       <c r="R24" s="55" t="n">
         <f aca="false">O24*$K24/$I24</f>
-        <v>64.0515723807122</v>
+        <v>66.0521368663714</v>
       </c>
       <c r="S24" s="53" t="n">
         <f aca="false">P24*$K24/$I24</f>
-        <v>13.919272702486</v>
+        <v>13.857972530989</v>
       </c>
       <c r="T24" s="54" t="n">
         <f aca="false">Q24*$K24/$I24</f>
-        <v>13.8888264388675</v>
+        <v>13.9450101369462</v>
       </c>
       <c r="U24" s="42" t="n">
         <v>5.9026</v>
@@ -12429,30 +12429,30 @@
       </c>
       <c r="P25" s="1" t="n">
         <f aca="false">(M25/$G$2)^(1/$G$3)</f>
-        <v>17.1099021551831</v>
+        <v>16.7991038145623</v>
       </c>
       <c r="Q25" s="1" t="n">
         <f aca="false">(N25/$H$2)^(1/$H$3)</f>
-        <v>16.775482200408</v>
+        <v>16.5856967186212</v>
       </c>
       <c r="S25" s="1" t="n">
         <f aca="false">P25*$K25/$I25</f>
-        <v>49.485244257523</v>
+        <v>48.586353564814</v>
       </c>
       <c r="T25" s="1" t="n">
         <f aca="false">Q25*$K25/$I25</f>
-        <v>48.5180351527286</v>
+        <v>47.9691377459769</v>
       </c>
       <c r="U25" s="1" t="n">
         <v>1.5991</v>
       </c>
       <c r="X25" s="1" t="n">
         <f aca="false">AVERAGE(S25:S26)/100</f>
-        <v>0.489988476990679</v>
+        <v>0.481085102529106</v>
       </c>
       <c r="Y25" s="1" t="n">
         <f aca="false">AVERAGE(T25:T26)/100</f>
-        <v>0.480761659296679</v>
+        <v>0.475316325823524</v>
       </c>
       <c r="Z25" s="1" t="n">
         <f aca="false">AVERAGE(U25:V26)/100</f>
@@ -12460,19 +12460,19 @@
       </c>
       <c r="AA25" s="1" t="n">
         <f aca="false">SUM(W25:Z25)</f>
-        <v>0.986687136287358</v>
+        <v>0.97233842835263</v>
       </c>
       <c r="AE25" s="1" t="n">
         <f aca="false">IFERROR(X25/$AA25,"")</f>
-        <v>0.496599640322033</v>
+        <v>0.494771252992827</v>
       </c>
       <c r="AF25" s="1" t="n">
         <f aca="false">IFERROR(Y25/$AA25,"")</f>
-        <v>0.487248329906943</v>
+        <v>0.48883836323205</v>
       </c>
       <c r="AG25" s="1" t="n">
         <f aca="false">IFERROR(Z25/$AA25,"")</f>
-        <v>0.0161520297710242</v>
+        <v>0.0163903837751235</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12516,19 +12516,19 @@
       </c>
       <c r="P26" s="1" t="n">
         <f aca="false">(M26/$G$2)^(1/$G$3)</f>
-        <v>17.1342677880488</v>
+        <v>16.8228276061557</v>
       </c>
       <c r="Q26" s="1" t="n">
         <f aca="false">(N26/$H$2)^(1/$H$3)</f>
-        <v>16.824109614678</v>
+        <v>16.6333254961312</v>
       </c>
       <c r="S26" s="1" t="n">
         <f aca="false">P26*$K26/$I26</f>
-        <v>48.5124511406127</v>
+        <v>47.6306669410073</v>
       </c>
       <c r="T26" s="1" t="n">
         <f aca="false">Q26*$K26/$I26</f>
-        <v>47.6342967066073</v>
+        <v>47.0941274187279</v>
       </c>
       <c r="U26" s="1" t="n">
         <v>1.5883</v>
@@ -12575,27 +12575,27 @@
       </c>
       <c r="P27" s="1" t="n">
         <f aca="false">(M27/$G$2)^(1/$G$3)</f>
-        <v>0.0108376189835164</v>
+        <v>0.0113133429190523</v>
       </c>
       <c r="Q27" s="1" t="n">
         <f aca="false">(N27/$H$2)^(1/$H$3)</f>
-        <v>0.0196617173600746</v>
+        <v>0.0207006563764354</v>
       </c>
       <c r="S27" s="1" t="n">
         <f aca="false">P27*$K27/$I27</f>
-        <v>0.0289702938445573</v>
+        <v>0.0302419626698153</v>
       </c>
       <c r="T27" s="1" t="n">
         <f aca="false">Q27*$K27/$I27</f>
-        <v>0.0525581984637345</v>
+        <v>0.0553354107495998</v>
       </c>
       <c r="X27" s="1" t="n">
         <f aca="false">AVERAGE(S27:S28)/100</f>
-        <v>0.000439946358277229</v>
+        <v>0.000456937995062183</v>
       </c>
       <c r="Y27" s="1" t="n">
         <f aca="false">AVERAGE(T27:T28)/100</f>
-        <v>0.000681684663919369</v>
+        <v>0.000714989755793403</v>
       </c>
       <c r="Z27" s="1" t="e">
         <f aca="false">AVERAGE(U27:V28)/100</f>
@@ -12659,19 +12659,19 @@
       </c>
       <c r="P28" s="1" t="n">
         <f aca="false">(M28/$G$2)^(1/$G$3)</f>
-        <v>0.0268802612626746</v>
+        <v>0.0278488503346955</v>
       </c>
       <c r="Q28" s="1" t="n">
         <f aca="false">(N28/$H$2)^(1/$H$3)</f>
-        <v>0.0381571208162482</v>
+        <v>0.039926004762338</v>
       </c>
       <c r="S28" s="1" t="n">
         <f aca="false">P28*$K28/$I28</f>
-        <v>0.0590189778108885</v>
+        <v>0.0611456363426214</v>
       </c>
       <c r="T28" s="1" t="n">
         <f aca="false">Q28*$K28/$I28</f>
-        <v>0.0837787343201394</v>
+        <v>0.0876625404090808</v>
       </c>
     </row>
   </sheetData>
@@ -12733,13 +12733,13 @@
         <v>2</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>157.651809</v>
+        <v>154.574631</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>141.723567</v>
+        <v>139.485507</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>141.744175</v>
+        <v>139.868341</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12747,13 +12747,13 @@
         <v>3</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>1.05643576</v>
+        <v>1.05174512</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.05899702</v>
+        <v>1.06895477</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.06384666</v>
+        <v>1.06554432</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>62</v>
@@ -12905,27 +12905,27 @@
       </c>
       <c r="O5" s="24" t="n">
         <f aca="false">(L5/$F$2)^(1/$F$3)</f>
-        <v>0.833516865788781</v>
+        <v>0.848596504710413</v>
       </c>
       <c r="P5" s="47" t="n">
         <f aca="false">(M5/$G$2)^(1/$G$3)</f>
-        <v>8.5991952043939</v>
+        <v>8.55499985663465</v>
       </c>
       <c r="Q5" s="26" t="n">
         <f aca="false">(N5/$H$2)^(1/$H$3)</f>
-        <v>8.46273927574493</v>
+        <v>8.54010318932517</v>
       </c>
       <c r="R5" s="25" t="n">
         <f aca="false">O5*$K5/$I5</f>
-        <v>3.96838211850584</v>
+        <v>4.04017642994248</v>
       </c>
       <c r="S5" s="47" t="n">
         <f aca="false">P5*$K5/$I5</f>
-        <v>40.9408542085883</v>
+        <v>40.7304397167316</v>
       </c>
       <c r="T5" s="26" t="n">
         <f aca="false">Q5*$K5/$I5</f>
-        <v>40.291186170135</v>
+        <v>40.6595165349669</v>
       </c>
       <c r="U5" s="27" t="n">
         <v>1.1008</v>
@@ -12933,15 +12933,15 @@
       <c r="V5" s="27"/>
       <c r="W5" s="48" t="n">
         <f aca="false">AVERAGE(R5:R6)/100</f>
-        <v>0.0588024135137537</v>
+        <v>0.0599643040898394</v>
       </c>
       <c r="X5" s="49" t="n">
         <f aca="false">AVERAGE(S5:S6)/100</f>
-        <v>0.589787206729282</v>
+        <v>0.584937467500253</v>
       </c>
       <c r="Y5" s="49" t="n">
         <f aca="false">AVERAGE(T5:T6)/100</f>
-        <v>0.577328703410746</v>
+        <v>0.582302878643276</v>
       </c>
       <c r="Z5" s="50" t="n">
         <f aca="false">AVERAGE(U5:V6)/100</f>
@@ -12949,16 +12949,16 @@
       </c>
       <c r="AA5" s="2" t="n">
         <f aca="false">SUM(W5:Z5)</f>
-        <v>1.23697532365378</v>
+        <v>1.23826165023337</v>
       </c>
       <c r="AD5" s="0" t="n">
-        <v>0.0474356522008845</v>
+        <v>0.0483222409304277</v>
       </c>
       <c r="AE5" s="0" t="n">
-        <v>0.475778784222822</v>
+        <v>0.471371921392328</v>
       </c>
       <c r="AF5" s="0" t="n">
-        <v>0.465728563576293</v>
+        <v>0.469248837677245</v>
       </c>
       <c r="AG5" s="0" t="n">
         <v>0.011057</v>
@@ -13011,27 +13011,27 @@
       </c>
       <c r="O6" s="24" t="n">
         <f aca="false">(L6/$F$2)^(1/$F$3)</f>
-        <v>1.44997028460331</v>
+        <v>1.47985205283165</v>
       </c>
       <c r="P6" s="47" t="n">
         <f aca="false">(M6/$G$2)^(1/$G$3)</f>
-        <v>14.3314067321453</v>
+        <v>14.190071185782</v>
       </c>
       <c r="Q6" s="26" t="n">
         <f aca="false">(N6/$H$2)^(1/$H$3)</f>
-        <v>13.988637469735</v>
+        <v>14.1052187640562</v>
       </c>
       <c r="R6" s="25" t="n">
         <f aca="false">O6*$K6/$I6</f>
-        <v>7.79210058424491</v>
+        <v>7.9526843880254</v>
       </c>
       <c r="S6" s="47" t="n">
         <f aca="false">P6*$K6/$I6</f>
-        <v>77.0165871372682</v>
+        <v>76.2570537833189</v>
       </c>
       <c r="T6" s="26" t="n">
         <f aca="false">Q6*$K6/$I6</f>
-        <v>75.1745545120141</v>
+        <v>75.8010591936883</v>
       </c>
       <c r="U6" s="27" t="n">
         <v>1.1106</v>
@@ -13088,27 +13088,27 @@
       </c>
       <c r="O7" s="52" t="n">
         <f aca="false">(L7/$F$2)^(1/$F$3)</f>
-        <v>0.037464173478706</v>
+        <v>0.0376178729883458</v>
       </c>
       <c r="P7" s="53" t="n">
         <f aca="false">(M7/$G$2)^(1/$G$3)</f>
-        <v>0.0318057435052272</v>
+        <v>0.0333366825229519</v>
       </c>
       <c r="Q7" s="54" t="n">
         <f aca="false">(N7/$H$2)^(1/$H$3)</f>
-        <v>0.0168494738737394</v>
+        <v>0.0171728233670356</v>
       </c>
       <c r="R7" s="55" t="n">
         <f aca="false">O7*$K7/$I7</f>
-        <v>0.146486450230688</v>
+        <v>0.14708742159823</v>
       </c>
       <c r="S7" s="53" t="n">
         <f aca="false">P7*$K7/$I7</f>
-        <v>0.124361757658331</v>
+        <v>0.130347791818503</v>
       </c>
       <c r="T7" s="54" t="n">
         <f aca="false">Q7*$K7/$I7</f>
-        <v>0.0658821318298053</v>
+        <v>0.0671464415705173</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>99.4816</v>
@@ -13116,15 +13116,15 @@
       <c r="V7" s="2"/>
       <c r="W7" s="51" t="n">
         <f aca="false">AVERAGE(R7:R8)/100</f>
-        <v>0.00141964536663802</v>
+        <v>0.00142524039504853</v>
       </c>
       <c r="X7" s="0" t="n">
         <f aca="false">AVERAGE(S7:S8)/100</f>
-        <v>0.00121447004839594</v>
+        <v>0.00127326753543119</v>
       </c>
       <c r="Y7" s="1" t="n">
         <f aca="false">AVERAGE(T7:T8)/100</f>
-        <v>0.000656136935082007</v>
+        <v>0.000668738564374399</v>
       </c>
       <c r="Z7" s="33" t="n">
         <f aca="false">AVERAGE(U7:V8)/100</f>
@@ -13132,19 +13132,19 @@
       </c>
       <c r="AA7" s="2" t="n">
         <f aca="false">SUM(W7:Z7)</f>
-        <v>0.991904752350116</v>
+        <v>0.991981746494854</v>
       </c>
       <c r="AD7" s="0" t="n">
-        <v>0.00141964536663802</v>
+        <v>0.00142524039504853</v>
       </c>
       <c r="AE7" s="0" t="n">
-        <v>0.00121447004839594</v>
+        <v>0.00127326753543119</v>
       </c>
       <c r="AF7" s="0" t="n">
-        <v>0.000656136935082007</v>
+        <v>0.000668738564374399</v>
       </c>
       <c r="AG7" s="0" t="n">
-        <v>0.996709747649884</v>
+        <v>0.996632753505146</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13194,27 +13194,27 @@
       </c>
       <c r="O8" s="52" t="n">
         <f aca="false">(L8/$F$2)^(1/$F$3)</f>
-        <v>0.0347752214934213</v>
+        <v>0.0349062926096744</v>
       </c>
       <c r="P8" s="53" t="n">
         <f aca="false">(M8/$G$2)^(1/$G$3)</f>
-        <v>0.0299905897112631</v>
+        <v>0.0314513699166345</v>
       </c>
       <c r="Q8" s="54" t="n">
         <f aca="false">(N8/$H$2)^(1/$H$3)</f>
-        <v>0.0165334135179861</v>
+        <v>0.0168512060463187</v>
       </c>
       <c r="R8" s="55" t="n">
         <f aca="false">O8*$K8/$I8</f>
-        <v>0.137442623096915</v>
+        <v>0.137960657411477</v>
       </c>
       <c r="S8" s="53" t="n">
         <f aca="false">P8*$K8/$I8</f>
-        <v>0.118532252020858</v>
+        <v>0.124305715267736</v>
       </c>
       <c r="T8" s="54" t="n">
         <f aca="false">Q8*$K8/$I8</f>
-        <v>0.0653452551865962</v>
+        <v>0.0666012713043625</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>98.2413</v>
@@ -13273,27 +13273,27 @@
       </c>
       <c r="O9" s="24" t="n">
         <f aca="false">(L9/$F$2)^(1/$F$3)</f>
-        <v>0.608652817356206</v>
+        <v>0.618796020766668</v>
       </c>
       <c r="P9" s="47" t="n">
         <f aca="false">(M9/$G$2)^(1/$G$3)</f>
-        <v>0.00158147959253469</v>
+        <v>0.00170460011284814</v>
       </c>
       <c r="Q9" s="26" t="n">
         <f aca="false">(N9/$H$2)^(1/$H$3)</f>
-        <v>0.000908048788660286</v>
+        <v>0.000929791391759964</v>
       </c>
       <c r="R9" s="25" t="n">
         <f aca="false">O9*$K9/$I9</f>
-        <v>4.43128941416651</v>
+        <v>4.50513688289878</v>
       </c>
       <c r="S9" s="47" t="n">
         <f aca="false">P9*$K9/$I9</f>
-        <v>0.0115139428871123</v>
+        <v>0.0124103203337846</v>
       </c>
       <c r="T9" s="26" t="n">
         <f aca="false">Q9*$K9/$I9</f>
-        <v>0.00661103813207548</v>
+        <v>0.00676933488878899</v>
       </c>
       <c r="U9" s="27" t="n">
         <v>97.6096</v>
@@ -13303,15 +13303,15 @@
       </c>
       <c r="W9" s="56" t="n">
         <f aca="false">AVERAGE(R9:R10)/100</f>
-        <v>0.0339573406791631</v>
+        <v>0.0345139852641209</v>
       </c>
       <c r="X9" s="57" t="n">
         <f aca="false">AVERAGE(S9:S10)/100</f>
-        <v>9.12543026979722E-005</v>
+        <v>9.83853241807006E-005</v>
       </c>
       <c r="Y9" s="57" t="n">
         <f aca="false">AVERAGE(T9:T10)/100</f>
-        <v>5.33405318469013E-005</v>
+        <v>5.46187718239917E-005</v>
       </c>
       <c r="Z9" s="29" t="n">
         <f aca="false">AVERAGE(U9:V10)/100</f>
@@ -13319,19 +13319,19 @@
       </c>
       <c r="AA9" s="2" t="n">
         <f aca="false">SUM(W9:Z9)</f>
-        <v>1.02019593551371</v>
+        <v>1.02076098936013</v>
       </c>
       <c r="AD9" s="0" t="n">
-        <v>0.0339573406791631</v>
+        <v>0.0345139852641209</v>
       </c>
       <c r="AE9" s="0" t="n">
-        <v>9.12543026979722E-005</v>
+        <v>9.83853241807006E-005</v>
       </c>
       <c r="AF9" s="0" t="n">
-        <v>5.33405318469013E-005</v>
+        <v>5.46187718239917E-005</v>
       </c>
       <c r="AG9" s="0" t="n">
-        <v>0.965898064486292</v>
+        <v>0.965333010639874</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13381,27 +13381,27 @@
       </c>
       <c r="O10" s="24" t="n">
         <f aca="false">(L10/$F$2)^(1/$F$3)</f>
-        <v>0.511946309091322</v>
+        <v>0.520076409121289</v>
       </c>
       <c r="P10" s="47" t="n">
         <f aca="false">(M10/$G$2)^(1/$G$3)</f>
-        <v>0.00146130464408463</v>
+        <v>0.00157622937319949</v>
       </c>
       <c r="Q10" s="26" t="n">
         <f aca="false">(N10/$H$2)^(1/$H$3)</f>
-        <v>0.000880018572641658</v>
+        <v>0.000901135027460423</v>
       </c>
       <c r="R10" s="25" t="n">
         <f aca="false">O10*$K10/$I10</f>
-        <v>2.3601787216661</v>
+        <v>2.3976601699254</v>
       </c>
       <c r="S10" s="47" t="n">
         <f aca="false">P10*$K10/$I10</f>
-        <v>0.00673691765248216</v>
+        <v>0.00726674450235549</v>
       </c>
       <c r="T10" s="26" t="n">
         <f aca="false">Q10*$K10/$I10</f>
-        <v>0.00405706823730478</v>
+        <v>0.00415441947600935</v>
       </c>
       <c r="U10" s="27" t="n">
         <v>98.4877</v>
@@ -13458,27 +13458,27 @@
       </c>
       <c r="O11" s="52" t="n">
         <f aca="false">(L11/$F$2)^(1/$F$3)</f>
-        <v>22.1872366177871</v>
+        <v>22.9216675667521</v>
       </c>
       <c r="P11" s="53" t="n">
         <f aca="false">(M11/$G$2)^(1/$G$3)</f>
-        <v>0.552111736677391</v>
+        <v>0.563504201083192</v>
       </c>
       <c r="Q11" s="54" t="n">
         <f aca="false">(N11/$H$2)^(1/$H$3)</f>
-        <v>0.547212897018199</v>
+        <v>0.554630055414462</v>
       </c>
       <c r="R11" s="55" t="n">
         <f aca="false">O11*$K11/$I11</f>
-        <v>103.476790858285</v>
+        <v>106.902028485443</v>
       </c>
       <c r="S11" s="53" t="n">
         <f aca="false">P11*$K11/$I11</f>
-        <v>2.57493764053385</v>
+        <v>2.62806979380681</v>
       </c>
       <c r="T11" s="54" t="n">
         <f aca="false">Q11*$K11/$I11</f>
-        <v>2.55209044168729</v>
+        <v>2.58668257054742</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>7.8468</v>
@@ -13486,15 +13486,15 @@
       <c r="V11" s="2"/>
       <c r="W11" s="51" t="n">
         <f aca="false">AVERAGE(R11:R12)/100</f>
-        <v>1.32148426083074</v>
+        <v>1.36599756828819</v>
       </c>
       <c r="X11" s="0" t="n">
         <f aca="false">AVERAGE(S11:S12)/100</f>
-        <v>0.0325305530145158</v>
+        <v>0.0331663308876275</v>
       </c>
       <c r="Y11" s="1" t="n">
         <f aca="false">AVERAGE(T11:T12)/100</f>
-        <v>0.032264845852342</v>
+        <v>0.0326961581920351</v>
       </c>
       <c r="Z11" s="33" t="n">
         <f aca="false">AVERAGE(U11:V12)/100</f>
@@ -13502,16 +13502,16 @@
       </c>
       <c r="AA11" s="2" t="n">
         <f aca="false">SUM(W11:Z11)</f>
-        <v>1.4654801596976</v>
+        <v>1.51106055736786</v>
       </c>
       <c r="AD11" s="0" t="n">
-        <v>0.87776087466814</v>
+        <v>0.878444699542201</v>
       </c>
       <c r="AE11" s="0" t="n">
-        <v>0.0216075571339075</v>
+        <v>0.0213285793824726</v>
       </c>
       <c r="AF11" s="0" t="n">
-        <v>0.0214310681979525</v>
+        <v>0.0210262210753269</v>
       </c>
       <c r="AG11" s="0" t="n">
         <v>0.0792005</v>
@@ -13564,27 +13564,27 @@
       </c>
       <c r="O12" s="52" t="n">
         <f aca="false">(L12/$F$2)^(1/$F$3)</f>
-        <v>27.3114308219533</v>
+        <v>28.2416399123905</v>
       </c>
       <c r="P12" s="53" t="n">
         <f aca="false">(M12/$G$2)^(1/$G$3)</f>
-        <v>0.667615455047918</v>
+        <v>0.680186558024419</v>
       </c>
       <c r="Q12" s="54" t="n">
         <f aca="false">(N12/$H$2)^(1/$H$3)</f>
-        <v>0.66247070595244</v>
+        <v>0.67124567394967</v>
       </c>
       <c r="R12" s="55" t="n">
         <f aca="false">O12*$K12/$I12</f>
-        <v>160.820061307863</v>
+        <v>166.297485172195</v>
       </c>
       <c r="S12" s="53" t="n">
         <f aca="false">P12*$K12/$I12</f>
-        <v>3.93117296236931</v>
+        <v>4.0051963837187</v>
       </c>
       <c r="T12" s="54" t="n">
         <f aca="false">Q12*$K12/$I12</f>
-        <v>3.9008787287811</v>
+        <v>3.95254906785959</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>7.9933</v>
@@ -13643,27 +13643,27 @@
       </c>
       <c r="O13" s="24" t="n">
         <f aca="false">(L13/$F$2)^(1/$F$3)</f>
-        <v>13.4357685690124</v>
+        <v>13.8494960053439</v>
       </c>
       <c r="P13" s="47" t="n">
         <f aca="false">(M13/$G$2)^(1/$G$3)</f>
-        <v>7.0697686576056</v>
+        <v>7.04627682796868</v>
       </c>
       <c r="Q13" s="26" t="n">
         <f aca="false">(N13/$H$2)^(1/$H$3)</f>
-        <v>6.96066032562738</v>
+        <v>7.02647977886145</v>
       </c>
       <c r="R13" s="25" t="n">
         <f aca="false">O13*$K13/$I13</f>
-        <v>49.643735525419</v>
+        <v>51.1724143891067</v>
       </c>
       <c r="S13" s="47" t="n">
         <f aca="false">P13*$K13/$I13</f>
-        <v>26.122043086804</v>
+        <v>26.0352432754264</v>
       </c>
       <c r="T13" s="26" t="n">
         <f aca="false">Q13*$K13/$I13</f>
-        <v>25.7188994074139</v>
+        <v>25.9620952850443</v>
       </c>
       <c r="U13" s="27" t="n">
         <v>4.4671</v>
@@ -13671,15 +13671,15 @@
       <c r="V13" s="27"/>
       <c r="W13" s="56" t="n">
         <f aca="false">AVERAGE(R13:R14)/100</f>
-        <v>0.654813136411526</v>
+        <v>0.675047770091417</v>
       </c>
       <c r="X13" s="57" t="n">
         <f aca="false">AVERAGE(S13:S14)/100</f>
-        <v>0.344244923151325</v>
+        <v>0.343028631375977</v>
       </c>
       <c r="Y13" s="57" t="n">
         <f aca="false">AVERAGE(T13:T14)/100</f>
-        <v>0.338827834302274</v>
+        <v>0.342019585107165</v>
       </c>
       <c r="Z13" s="29" t="n">
         <f aca="false">AVERAGE(U13:V14)/100</f>
@@ -13687,16 +13687,16 @@
       </c>
       <c r="AA13" s="2" t="n">
         <f aca="false">SUM(W13:Z13)</f>
-        <v>1.38209839386512</v>
+        <v>1.40430848657456</v>
       </c>
       <c r="AD13" s="0" t="n">
-        <v>0.46779939416943</v>
+        <v>0.474379916509577</v>
       </c>
       <c r="AE13" s="0" t="n">
-        <v>0.245929040731531</v>
+        <v>0.241058337975835</v>
       </c>
       <c r="AF13" s="0" t="n">
-        <v>0.242059065099039</v>
+        <v>0.240349245514588</v>
       </c>
       <c r="AG13" s="0" t="n">
         <v>0.0442125</v>
@@ -13749,27 +13749,27 @@
       </c>
       <c r="O14" s="24" t="n">
         <f aca="false">(L14/$F$2)^(1/$F$3)</f>
-        <v>13.9557522109691</v>
+        <v>14.3879278414063</v>
       </c>
       <c r="P14" s="47" t="n">
         <f aca="false">(M14/$G$2)^(1/$G$3)</f>
-        <v>7.33269472849902</v>
+        <v>7.30584369032227</v>
       </c>
       <c r="Q14" s="26" t="n">
         <f aca="false">(N14/$H$2)^(1/$H$3)</f>
-        <v>7.21594772867729</v>
+        <v>7.28376315439648</v>
       </c>
       <c r="R14" s="25" t="n">
         <f aca="false">O14*$K14/$I14</f>
-        <v>81.3188917568862</v>
+        <v>83.8371396291766</v>
       </c>
       <c r="S14" s="47" t="n">
         <f aca="false">P14*$K14/$I14</f>
-        <v>42.7269415434609</v>
+        <v>42.5704829997689</v>
       </c>
       <c r="T14" s="26" t="n">
         <f aca="false">Q14*$K14/$I14</f>
-        <v>42.0466674530409</v>
+        <v>42.4418217363887</v>
       </c>
       <c r="U14" s="27" t="n">
         <v>4.3754</v>
@@ -13826,27 +13826,27 @@
       </c>
       <c r="O15" s="52" t="n">
         <f aca="false">(L15/$F$2)^(1/$F$3)</f>
-        <v>0.276854515515498</v>
+        <v>0.280481154970568</v>
       </c>
       <c r="P15" s="53" t="n">
         <f aca="false">(M15/$G$2)^(1/$G$3)</f>
-        <v>0.0167440554548908</v>
+        <v>0.0176552215384351</v>
       </c>
       <c r="Q15" s="54" t="n">
         <f aca="false">(N15/$H$2)^(1/$H$3)</f>
-        <v>0.0096859274763173</v>
+        <v>0.00988051669651979</v>
       </c>
       <c r="R15" s="55" t="n">
         <f aca="false">O15*$K15/$I15</f>
-        <v>1.45800214229533</v>
+        <v>1.47710115567057</v>
       </c>
       <c r="S15" s="53" t="n">
         <f aca="false">P15*$K15/$I15</f>
-        <v>0.0881794132145044</v>
+        <v>0.0929778977157266</v>
       </c>
       <c r="T15" s="54" t="n">
         <f aca="false">Q15*$K15/$I15</f>
-        <v>0.0510091120756789</v>
+        <v>0.0520338795402606</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>98.793</v>
@@ -13854,15 +13854,15 @@
       <c r="V15" s="2"/>
       <c r="W15" s="51" t="n">
         <f aca="false">AVERAGE(R15:R16)/100</f>
-        <v>0.0121175102711583</v>
+        <v>0.0122748370913457</v>
       </c>
       <c r="X15" s="0" t="n">
         <f aca="false">AVERAGE(S15:S16)/100</f>
-        <v>0.00071746652648987</v>
+        <v>0.000756831559461948</v>
       </c>
       <c r="Y15" s="1" t="n">
         <f aca="false">AVERAGE(T15:T16)/100</f>
-        <v>0.000408820679200022</v>
+        <v>0.000417073392914513</v>
       </c>
       <c r="Z15" s="33" t="n">
         <f aca="false">AVERAGE(U15:V16)/100</f>
@@ -13870,19 +13870,19 @@
       </c>
       <c r="AA15" s="2" t="n">
         <f aca="false">SUM(W15:Z15)</f>
-        <v>1.00076579747685</v>
+        <v>1.00097074204372</v>
       </c>
       <c r="AD15" s="0" t="n">
-        <v>0.0121175102711583</v>
+        <v>0.0122748370913457</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>0.00071746652648987</v>
+        <v>0.000756831559461948</v>
       </c>
       <c r="AF15" s="0" t="n">
-        <v>0.000408820679200022</v>
+        <v>0.000417073392914513</v>
       </c>
       <c r="AG15" s="0" t="n">
-        <v>0.986756202523152</v>
+        <v>0.986551257956278</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13932,27 +13932,27 @@
       </c>
       <c r="O16" s="52" t="n">
         <f aca="false">(L16/$F$2)^(1/$F$3)</f>
-        <v>0.25957157701283</v>
+        <v>0.262896231011872</v>
       </c>
       <c r="P16" s="53" t="n">
         <f aca="false">(M16/$G$2)^(1/$G$3)</f>
-        <v>0.0148709637580688</v>
+        <v>0.0156975392330375</v>
       </c>
       <c r="Q16" s="54" t="n">
         <f aca="false">(N16/$H$2)^(1/$H$3)</f>
-        <v>0.00826839020996151</v>
+        <v>0.00843662790096502</v>
       </c>
       <c r="R16" s="55" t="n">
         <f aca="false">O16*$K16/$I16</f>
-        <v>0.965499911936328</v>
+        <v>0.977866262598575</v>
       </c>
       <c r="S16" s="53" t="n">
         <f aca="false">P16*$K16/$I16</f>
-        <v>0.0553138920834696</v>
+        <v>0.058388414176663</v>
       </c>
       <c r="T16" s="54" t="n">
         <f aca="false">Q16*$K16/$I16</f>
-        <v>0.0307550237643254</v>
+        <v>0.031380799042642</v>
       </c>
       <c r="U16" s="2" t="n">
         <v>98.7114</v>
@@ -14011,27 +14011,27 @@
       </c>
       <c r="O17" s="24" t="n">
         <f aca="false">(L17/$F$2)^(1/$F$3)</f>
-        <v>13.4387335713652</v>
+        <v>13.8525659411818</v>
       </c>
       <c r="P17" s="47" t="n">
         <f aca="false">(M17/$G$2)^(1/$G$3)</f>
-        <v>2.97152315301192</v>
+        <v>2.98565883115647</v>
       </c>
       <c r="Q17" s="26" t="n">
         <f aca="false">(N17/$H$2)^(1/$H$3)</f>
-        <v>2.94036066664036</v>
+        <v>2.97224244138746</v>
       </c>
       <c r="R17" s="25" t="n">
         <f aca="false">O17*$K17/$I17</f>
-        <v>55.1620247504447</v>
+        <v>56.8606841743504</v>
       </c>
       <c r="S17" s="47" t="n">
         <f aca="false">P17*$K17/$I17</f>
-        <v>12.1972232608456</v>
+        <v>12.255246036841</v>
       </c>
       <c r="T17" s="26" t="n">
         <f aca="false">Q17*$K17/$I17</f>
-        <v>12.0693104753599</v>
+        <v>12.2001757267877</v>
       </c>
       <c r="U17" s="27" t="n">
         <v>6.4258</v>
@@ -14039,15 +14039,15 @@
       <c r="V17" s="27"/>
       <c r="W17" s="56" t="n">
         <f aca="false">AVERAGE(R17:R18)/100</f>
-        <v>0.727471400907627</v>
+        <v>0.750330161081445</v>
       </c>
       <c r="X17" s="57" t="n">
         <f aca="false">AVERAGE(S17:S18)/100</f>
-        <v>0.158611847764609</v>
+        <v>0.15918628704996</v>
       </c>
       <c r="Y17" s="57" t="n">
         <f aca="false">AVERAGE(T17:T18)/100</f>
-        <v>0.156897788633089</v>
+        <v>0.158568414153672</v>
       </c>
       <c r="Z17" s="29" t="n">
         <f aca="false">AVERAGE(U17:V18)/100</f>
@@ -14055,16 +14055,16 @@
       </c>
       <c r="AA17" s="2" t="n">
         <f aca="false">SUM(W17:Z17)</f>
-        <v>1.10586403730533</v>
+        <v>1.13096786228508</v>
       </c>
       <c r="AD17" s="0" t="n">
-        <v>0.653632033968401</v>
+        <v>0.658325170958642</v>
       </c>
       <c r="AE17" s="0" t="n">
-        <v>0.142512522879277</v>
+        <v>0.139666969385042</v>
       </c>
       <c r="AF17" s="0" t="n">
-        <v>0.140972443152322</v>
+        <v>0.139124859656315</v>
       </c>
       <c r="AG17" s="0" t="n">
         <v>0.062883</v>
@@ -14117,27 +14117,27 @@
       </c>
       <c r="O18" s="24" t="n">
         <f aca="false">(L18/$F$2)^(1/$F$3)</f>
-        <v>16.7455172335934</v>
+        <v>17.2781223545354</v>
       </c>
       <c r="P18" s="47" t="n">
         <f aca="false">(M18/$G$2)^(1/$G$3)</f>
-        <v>3.61951190260992</v>
+        <v>3.63005337741955</v>
       </c>
       <c r="Q18" s="26" t="n">
         <f aca="false">(N18/$H$2)^(1/$H$3)</f>
-        <v>3.57967457568463</v>
+        <v>3.61735426551252</v>
       </c>
       <c r="R18" s="25" t="n">
         <f aca="false">O18*$K18/$I18</f>
-        <v>90.3322554310808</v>
+        <v>93.2053480419385</v>
       </c>
       <c r="S18" s="47" t="n">
         <f aca="false">P18*$K18/$I18</f>
-        <v>19.5251462920763</v>
+        <v>19.5820113731509</v>
       </c>
       <c r="T18" s="26" t="n">
         <f aca="false">Q18*$K18/$I18</f>
-        <v>19.3102472512579</v>
+        <v>19.5135071039466</v>
       </c>
       <c r="U18" s="27" t="n">
         <v>6.1508</v>
@@ -14194,27 +14194,27 @@
       </c>
       <c r="O19" s="52" t="n">
         <f aca="false">(L19/$F$2)^(1/$F$3)</f>
-        <v>0.408416278163266</v>
+        <v>0.414484384690936</v>
       </c>
       <c r="P19" s="53" t="n">
         <f aca="false">(M19/$G$2)^(1/$G$3)</f>
-        <v>0.0120805202405174</v>
+        <v>0.0127767044039608</v>
       </c>
       <c r="Q19" s="54" t="n">
         <f aca="false">(N19/$H$2)^(1/$H$3)</f>
-        <v>0.00817197900319304</v>
+        <v>0.00833841082159686</v>
       </c>
       <c r="R19" s="55" t="n">
         <f aca="false">O19*$K19/$I19</f>
-        <v>1.9545119230235</v>
+        <v>1.98355137907027</v>
       </c>
       <c r="S19" s="53" t="n">
         <f aca="false">P19*$K19/$I19</f>
-        <v>0.0578123892431614</v>
+        <v>0.061144039622499</v>
       </c>
       <c r="T19" s="54" t="n">
         <f aca="false">Q19*$K19/$I19</f>
-        <v>0.0391077223177024</v>
+        <v>0.0399041963830939</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>98.6729</v>
@@ -14222,15 +14222,15 @@
       <c r="V19" s="2"/>
       <c r="W19" s="51" t="n">
         <f aca="false">AVERAGE(R19:R20)/100</f>
-        <v>0.0173037698738769</v>
+        <v>0.0175578550060032</v>
       </c>
       <c r="X19" s="0" t="n">
         <f aca="false">AVERAGE(S19:S20)/100</f>
-        <v>0.000499086490289764</v>
+        <v>0.00052815289434853</v>
       </c>
       <c r="Y19" s="1" t="n">
         <f aca="false">AVERAGE(T19:T20)/100</f>
-        <v>0.000334787451129759</v>
+        <v>0.000341643649535169</v>
       </c>
       <c r="Z19" s="33" t="n">
         <f aca="false">AVERAGE(U19:V20)/100</f>
@@ -14238,19 +14238,19 @@
       </c>
       <c r="AA19" s="2" t="n">
         <f aca="false">SUM(W19:Z19)</f>
-        <v>1.0020886438153</v>
+        <v>1.00237865154989</v>
       </c>
       <c r="AD19" s="0" t="n">
-        <v>0.0173037698738769</v>
+        <v>0.0175578550060032</v>
       </c>
       <c r="AE19" s="0" t="n">
-        <v>0.000499086490289764</v>
+        <v>0.00052815289434853</v>
       </c>
       <c r="AF19" s="0" t="n">
-        <v>0.000334787451129759</v>
+        <v>0.000341643649535169</v>
       </c>
       <c r="AG19" s="0" t="n">
-        <v>0.981862356184704</v>
+        <v>0.981572348450113</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14300,27 +14300,27 @@
       </c>
       <c r="O20" s="52" t="n">
         <f aca="false">(L20/$F$2)^(1/$F$3)</f>
-        <v>0.373911165989534</v>
+        <v>0.379317253758209</v>
       </c>
       <c r="P20" s="53" t="n">
         <f aca="false">(M20/$G$2)^(1/$G$3)</f>
-        <v>0.0104273442730902</v>
+        <v>0.011043386912094</v>
       </c>
       <c r="Q20" s="54" t="n">
         <f aca="false">(N20/$H$2)^(1/$H$3)</f>
-        <v>0.0069134566911074</v>
+        <v>0.00705613713299495</v>
       </c>
       <c r="R20" s="55" t="n">
         <f aca="false">O20*$K20/$I20</f>
-        <v>1.50624205175189</v>
+        <v>1.52801962213038</v>
       </c>
       <c r="S20" s="53" t="n">
         <f aca="false">P20*$K20/$I20</f>
-        <v>0.0420049088147913</v>
+        <v>0.0444865392472071</v>
       </c>
       <c r="T20" s="54" t="n">
         <f aca="false">Q20*$K20/$I20</f>
-        <v>0.0278497679082494</v>
+        <v>0.02842453352394</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>98.1173</v>
@@ -14379,27 +14379,27 @@
       </c>
       <c r="O21" s="24" t="n">
         <f aca="false">(L21/$F$2)^(1/$F$3)</f>
-        <v>6.71980117739867</v>
+        <v>6.90535289922092</v>
       </c>
       <c r="P21" s="47" t="n">
         <f aca="false">(M21/$G$2)^(1/$G$3)</f>
-        <v>8.39376409426297</v>
+        <v>8.35250568149966</v>
       </c>
       <c r="Q21" s="26" t="n">
         <f aca="false">(N21/$H$2)^(1/$H$3)</f>
-        <v>8.24659906810592</v>
+        <v>8.32233013120606</v>
       </c>
       <c r="R21" s="25" t="n">
         <f aca="false">O21*$K21/$I21</f>
-        <v>28.5038517292787</v>
+        <v>29.2909194753785</v>
       </c>
       <c r="S21" s="47" t="n">
         <f aca="false">P21*$K21/$I21</f>
-        <v>35.6044175827884</v>
+        <v>35.4294088810508</v>
       </c>
       <c r="T21" s="26" t="n">
         <f aca="false">Q21*$K21/$I21</f>
-        <v>34.9801773746964</v>
+        <v>35.3014111339879</v>
       </c>
       <c r="U21" s="27" t="n">
         <v>2.8273</v>
@@ -14407,15 +14407,15 @@
       <c r="V21" s="27"/>
       <c r="W21" s="56" t="n">
         <f aca="false">AVERAGE(R21:R22)/100</f>
-        <v>0.298010969821185</v>
+        <v>0.306262564152774</v>
       </c>
       <c r="X21" s="57" t="n">
         <f aca="false">AVERAGE(S21:S22)/100</f>
-        <v>0.371780808839847</v>
+        <v>0.369900464574574</v>
       </c>
       <c r="Y21" s="57" t="n">
         <f aca="false">AVERAGE(T21:T22)/100</f>
-        <v>0.365119707282739</v>
+        <v>0.368463933500291</v>
       </c>
       <c r="Z21" s="29" t="n">
         <f aca="false">AVERAGE(U21:V22)/100</f>
@@ -14423,16 +14423,16 @@
       </c>
       <c r="AA21" s="2" t="n">
         <f aca="false">SUM(W21:Z21)</f>
-        <v>1.06290748594377</v>
+        <v>1.07262296222764</v>
       </c>
       <c r="AD21" s="0" t="n">
-        <v>0.279896260351109</v>
+        <v>0.284971045330804</v>
       </c>
       <c r="AE21" s="0" t="n">
-        <v>0.349181971814738</v>
+        <v>0.344184808710686</v>
       </c>
       <c r="AF21" s="0" t="n">
-        <v>0.342925767834153</v>
+        <v>0.34284814595851</v>
       </c>
       <c r="AG21" s="0" t="n">
         <v>0.027996</v>
@@ -14485,27 +14485,27 @@
       </c>
       <c r="O22" s="24" t="n">
         <f aca="false">(L22/$F$2)^(1/$F$3)</f>
-        <v>6.93740903589446</v>
+        <v>7.12998284180346</v>
       </c>
       <c r="P22" s="47" t="n">
         <f aca="false">(M22/$G$2)^(1/$G$3)</f>
-        <v>8.64472769113529</v>
+        <v>8.59987525173621</v>
       </c>
       <c r="Q22" s="26" t="n">
         <f aca="false">(N22/$H$2)^(1/$H$3)</f>
-        <v>8.48679169798928</v>
+        <v>8.56433676561316</v>
       </c>
       <c r="R22" s="25" t="n">
         <f aca="false">O22*$K22/$I22</f>
-        <v>31.0983422349582</v>
+        <v>31.9615933551763</v>
       </c>
       <c r="S22" s="47" t="n">
         <f aca="false">P22*$K22/$I22</f>
-        <v>38.751744185181</v>
+        <v>38.550684033864</v>
       </c>
       <c r="T22" s="26" t="n">
         <f aca="false">Q22*$K22/$I22</f>
-        <v>38.0437640818514</v>
+        <v>38.3913755660702</v>
       </c>
       <c r="U22" s="27" t="n">
         <v>2.7719</v>
@@ -14562,27 +14562,27 @@
       </c>
       <c r="O23" s="52" t="n">
         <f aca="false">(L23/$F$2)^(1/$F$3)</f>
-        <v>0.216872917186105</v>
+        <v>0.219474690402427</v>
       </c>
       <c r="P23" s="53" t="n">
         <f aca="false">(M23/$G$2)^(1/$G$3)</f>
-        <v>0.0960605153586892</v>
+        <v>0.0996529080080981</v>
       </c>
       <c r="Q23" s="54" t="n">
         <f aca="false">(N23/$H$2)^(1/$H$3)</f>
-        <v>0.0900174006524946</v>
+        <v>0.091500268226276</v>
       </c>
       <c r="R23" s="55" t="n">
         <f aca="false">O23*$K23/$I23</f>
-        <v>0.844939218369171</v>
+        <v>0.855075754808557</v>
       </c>
       <c r="S23" s="53" t="n">
         <f aca="false">P23*$K23/$I23</f>
-        <v>0.3742528012092</v>
+        <v>0.388248801616489</v>
       </c>
       <c r="T23" s="54" t="n">
         <f aca="false">Q23*$K23/$I23</f>
-        <v>0.350708761305012</v>
+        <v>0.356486029324424</v>
       </c>
       <c r="U23" s="2" t="n">
         <v>97.482</v>
@@ -14592,15 +14592,15 @@
       </c>
       <c r="W23" s="51" t="n">
         <f aca="false">AVERAGE(R23:R24)/100</f>
-        <v>0.00760136273957739</v>
+        <v>0.00769281793172293</v>
       </c>
       <c r="X23" s="0" t="n">
         <f aca="false">AVERAGE(S23:S24)/100</f>
-        <v>0.00329322854848022</v>
+        <v>0.00341684273974584</v>
       </c>
       <c r="Y23" s="1" t="n">
         <f aca="false">AVERAGE(T23:T24)/100</f>
-        <v>0.0030783847293802</v>
+        <v>0.00312917902045536</v>
       </c>
       <c r="Z23" s="33" t="n">
         <f aca="false">AVERAGE(U23:V24)/100</f>
@@ -14608,19 +14608,19 @@
       </c>
       <c r="AA23" s="2" t="n">
         <f aca="false">SUM(W23:Z23)</f>
-        <v>0.999826976017438</v>
+        <v>1.00009283969192</v>
       </c>
       <c r="AD23" s="0" t="n">
-        <v>0.00760136273957739</v>
+        <v>0.00769281793172293</v>
       </c>
       <c r="AE23" s="0" t="n">
-        <v>0.00329322854848022</v>
+        <v>0.00341684273974584</v>
       </c>
       <c r="AF23" s="0" t="n">
-        <v>0.0030783847293802</v>
+        <v>0.00312917902045536</v>
       </c>
       <c r="AG23" s="0" t="n">
-        <v>0.986027023982562</v>
+        <v>0.985761160308076</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14670,27 +14670,27 @@
       </c>
       <c r="O24" s="58" t="n">
         <f aca="false">(L24/$F$2)^(1/$F$3)</f>
-        <v>0.220654164556351</v>
+        <v>0.223318515248363</v>
       </c>
       <c r="P24" s="59" t="n">
         <f aca="false">(M24/$G$2)^(1/$G$3)</f>
-        <v>0.0929207502168934</v>
+        <v>0.0964255697477082</v>
       </c>
       <c r="Q24" s="60" t="n">
         <f aca="false">(N24/$H$2)^(1/$H$3)</f>
-        <v>0.0865740380973217</v>
+        <v>0.0880056513196287</v>
       </c>
       <c r="R24" s="55" t="n">
         <f aca="false">O24*$K24/$I24</f>
-        <v>0.675333329546306</v>
+        <v>0.683487831536028</v>
       </c>
       <c r="S24" s="53" t="n">
         <f aca="false">P24*$K24/$I24</f>
-        <v>0.284392908486843</v>
+        <v>0.295119746332678</v>
       </c>
       <c r="T24" s="54" t="n">
         <f aca="false">Q24*$K24/$I24</f>
-        <v>0.264968184571027</v>
+        <v>0.269349774766648</v>
       </c>
       <c r="U24" s="42" t="n">
         <v>97.981</v>
@@ -14745,30 +14745,30 @@
       </c>
       <c r="P25" s="1" t="n">
         <f aca="false">(M25/$G$2)^(1/$G$3)</f>
-        <v>17.934179047852</v>
+        <v>17.7202563855404</v>
       </c>
       <c r="Q25" s="1" t="n">
         <f aca="false">(N25/$H$2)^(1/$H$3)</f>
-        <v>17.510719946123</v>
+        <v>17.6503380489262</v>
       </c>
       <c r="S25" s="1" t="n">
         <f aca="false">P25*$K25/$I25</f>
-        <v>49.2310797392017</v>
+        <v>48.6438410583463</v>
       </c>
       <c r="T25" s="1" t="n">
         <f aca="false">Q25*$K25/$I25</f>
-        <v>48.0686429893574</v>
+        <v>48.4519083696013</v>
       </c>
       <c r="U25" s="1" t="n">
         <v>0.9213</v>
       </c>
       <c r="X25" s="1" t="n">
         <f aca="false">AVERAGE(S25:S26)/100</f>
-        <v>0.492644898431765</v>
+        <v>0.486722806664988</v>
       </c>
       <c r="Y25" s="1" t="n">
         <f aca="false">AVERAGE(T25:T26)/100</f>
-        <v>0.481475660452234</v>
+        <v>0.485306058479608</v>
       </c>
       <c r="Z25" s="1" t="n">
         <f aca="false">AVERAGE(U25:V26)/100</f>
@@ -14776,19 +14776,19 @@
       </c>
       <c r="AA25" s="1" t="n">
         <f aca="false">SUM(W25:Z25)</f>
-        <v>0.983354058883998</v>
+        <v>0.981262365144596</v>
       </c>
       <c r="AE25" s="1" t="n">
         <f aca="false">IFERROR(X25/$AA25,"")</f>
-        <v>0.500984252803984</v>
+        <v>0.496016991942075</v>
       </c>
       <c r="AF25" s="1" t="n">
         <f aca="false">IFERROR(Y25/$AA25,"")</f>
-        <v>0.48962594510329</v>
+        <v>0.49457319032927</v>
       </c>
       <c r="AG25" s="1" t="n">
         <f aca="false">IFERROR(Z25/$AA25,"")</f>
-        <v>0.00938980209272643</v>
+        <v>0.00940981772865545</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14832,19 +14832,19 @@
       </c>
       <c r="P26" s="1" t="n">
         <f aca="false">(M26/$G$2)^(1/$G$3)</f>
-        <v>18.2992865844557</v>
+        <v>18.0776146272079</v>
       </c>
       <c r="Q26" s="1" t="n">
         <f aca="false">(N26/$H$2)^(1/$H$3)</f>
-        <v>17.9015809186403</v>
+        <v>18.0436808300689</v>
       </c>
       <c r="S26" s="1" t="n">
         <f aca="false">P26*$K26/$I26</f>
-        <v>49.2978999471513</v>
+        <v>48.7007202746514</v>
       </c>
       <c r="T26" s="1" t="n">
         <f aca="false">Q26*$K26/$I26</f>
-        <v>48.2264891010893</v>
+        <v>48.6093033263204</v>
       </c>
       <c r="U26" s="1" t="n">
         <v>0.9254</v>
@@ -14891,27 +14891,27 @@
       </c>
       <c r="P27" s="1" t="n">
         <f aca="false">(M27/$G$2)^(1/$G$3)</f>
-        <v>0.0636676077279383</v>
+        <v>0.0663021442115561</v>
       </c>
       <c r="Q27" s="1" t="n">
         <f aca="false">(N27/$H$2)^(1/$H$3)</f>
-        <v>0.0350399829976463</v>
+        <v>0.0356707822163643</v>
       </c>
       <c r="S27" s="1" t="n">
         <f aca="false">P27*$K27/$I27</f>
-        <v>0.177125893817641</v>
+        <v>0.184455282279196</v>
       </c>
       <c r="T27" s="1" t="n">
         <f aca="false">Q27*$K27/$I27</f>
-        <v>0.0974826686489359</v>
+        <v>0.0992375779257591</v>
       </c>
       <c r="X27" s="1" t="n">
         <f aca="false">AVERAGE(S27:S28)/100</f>
-        <v>0.00834067350382362</v>
+        <v>0.00854353427846911</v>
       </c>
       <c r="Y27" s="1" t="n">
         <f aca="false">AVERAGE(T27:T28)/100</f>
-        <v>0.00738615399148002</v>
+        <v>0.00749114702681185</v>
       </c>
       <c r="Z27" s="1" t="e">
         <f aca="false">AVERAGE(U27:V28)/100</f>
@@ -14975,19 +14975,19 @@
       </c>
       <c r="P28" s="1" t="n">
         <f aca="false">(M28/$G$2)^(1/$G$3)</f>
-        <v>0.463671256496145</v>
+        <v>0.47400903265521</v>
       </c>
       <c r="Q28" s="1" t="n">
         <f aca="false">(N28/$H$2)^(1/$H$3)</f>
-        <v>0.429071609732194</v>
+        <v>0.435055980509975</v>
       </c>
       <c r="S28" s="1" t="n">
         <f aca="false">P28*$K28/$I28</f>
-        <v>1.49100880694708</v>
+        <v>1.52425157341462</v>
       </c>
       <c r="T28" s="1" t="n">
         <f aca="false">Q28*$K28/$I28</f>
-        <v>1.37974812964707</v>
+        <v>1.39899182743661</v>
       </c>
     </row>
   </sheetData>
@@ -15048,13 +15048,13 @@
         <v>2</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>157.651809</v>
+        <v>154.574631</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>141.723567</v>
+        <v>139.485507</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>164.347912</v>
+        <v>162.845817</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15062,13 +15062,13 @@
         <v>3</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>1.05643576</v>
+        <v>1.05174512</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.05899702</v>
+        <v>1.06895477</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.02652889</v>
+        <v>1.02796306</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>70</v>
@@ -15220,27 +15220,27 @@
       </c>
       <c r="O5" s="24" t="n">
         <f aca="false">(L5/$F$2)^(1/$F$3)</f>
-        <v>0.964329075007112</v>
+        <v>0.982413825463908</v>
       </c>
       <c r="P5" s="47" t="n">
         <f aca="false">(M5/$G$2)^(1/$G$3)</f>
-        <v>9.48201618644589</v>
+        <v>9.42469964230678</v>
       </c>
       <c r="Q5" s="26" t="n">
         <f aca="false">(N5/$H$2)^(1/$H$3)</f>
-        <v>9.18236818292739</v>
+        <v>9.23613646576944</v>
       </c>
       <c r="R5" s="25" t="n">
         <f aca="false">O5*$K5/$I5</f>
-        <v>4.37030291747248</v>
+        <v>4.45226232296123</v>
       </c>
       <c r="S5" s="47" t="n">
         <f aca="false">P5*$K5/$I5</f>
-        <v>42.9721389483565</v>
+        <v>42.7123825368133</v>
       </c>
       <c r="T5" s="26" t="n">
         <f aca="false">Q5*$K5/$I5</f>
-        <v>41.6141455227388</v>
+        <v>41.8578213482036</v>
       </c>
       <c r="U5" s="27" t="n">
         <v>1.9283</v>
@@ -15248,15 +15248,15 @@
       <c r="V5" s="27"/>
       <c r="W5" s="48" t="n">
         <f aca="false">AVERAGE(R5:R6)/100</f>
-        <v>0.0511786477275603</v>
+        <v>0.0521851489057713</v>
       </c>
       <c r="X5" s="49" t="n">
         <f aca="false">AVERAGE(S5:S6)/100</f>
-        <v>0.502504829129983</v>
+        <v>0.498542557715458</v>
       </c>
       <c r="Y5" s="49" t="n">
         <f aca="false">AVERAGE(T5:T6)/100</f>
-        <v>0.49219532654854</v>
+        <v>0.494930902472923</v>
       </c>
       <c r="Z5" s="50" t="n">
         <f aca="false">AVERAGE(U5:V6)/100</f>
@@ -15264,16 +15264,16 @@
       </c>
       <c r="AA5" s="2" t="n">
         <f aca="false">SUM(W5:Z5)</f>
-        <v>1.06478830340608</v>
+        <v>1.06456810909415</v>
       </c>
       <c r="AD5" s="0" t="n">
-        <v>0.0480083207775468</v>
+        <v>0.0489627813392083</v>
       </c>
       <c r="AE5" s="0" t="n">
-        <v>0.471376523224299</v>
+        <v>0.467758179358419</v>
       </c>
       <c r="AF5" s="0" t="n">
-        <v>0.461705655998155</v>
+        <v>0.464369539302373</v>
       </c>
       <c r="AG5" s="0" t="n">
         <v>0.0189095</v>
@@ -15326,27 +15326,27 @@
       </c>
       <c r="O6" s="24" t="n">
         <f aca="false">(L6/$F$2)^(1/$F$3)</f>
-        <v>1.36884122048686</v>
+        <v>1.39669233140525</v>
       </c>
       <c r="P6" s="47" t="n">
         <f aca="false">(M6/$G$2)^(1/$G$3)</f>
-        <v>13.4257633059313</v>
+        <v>13.3014451871265</v>
       </c>
       <c r="Q6" s="26" t="n">
         <f aca="false">(N6/$H$2)^(1/$H$3)</f>
-        <v>13.2614893149318</v>
+        <v>13.3323043347797</v>
       </c>
       <c r="R6" s="25" t="n">
         <f aca="false">O6*$K6/$I6</f>
-        <v>5.86542662803958</v>
+        <v>5.98476745819303</v>
       </c>
       <c r="S6" s="47" t="n">
         <f aca="false">P6*$K6/$I6</f>
-        <v>57.5288268776401</v>
+        <v>56.9961290062783</v>
       </c>
       <c r="T6" s="26" t="n">
         <f aca="false">Q6*$K6/$I6</f>
-        <v>56.8249197869693</v>
+        <v>57.128359146381</v>
       </c>
       <c r="U6" s="27" t="n">
         <v>1.8536</v>
@@ -15403,27 +15403,27 @@
       </c>
       <c r="O7" s="52" t="n">
         <f aca="false">(L7/$F$2)^(1/$F$3)</f>
-        <v>0.0428913559176161</v>
+        <v>0.0430933135039329</v>
       </c>
       <c r="P7" s="53" t="n">
         <f aca="false">(M7/$G$2)^(1/$G$3)</f>
-        <v>0.0290982496537844</v>
+        <v>0.0305241534133846</v>
       </c>
       <c r="Q7" s="54" t="n">
         <f aca="false">(N7/$H$2)^(1/$H$3)</f>
-        <v>0.0161332106870213</v>
+        <v>0.0163719506973378</v>
       </c>
       <c r="R7" s="55" t="n">
         <f aca="false">O7*$K7/$I7</f>
-        <v>0.171311628665034</v>
+        <v>0.172118263994998</v>
       </c>
       <c r="S7" s="53" t="n">
         <f aca="false">P7*$K7/$I7</f>
-        <v>0.116220819623103</v>
+        <v>0.121915997361151</v>
       </c>
       <c r="T7" s="54" t="n">
         <f aca="false">Q7*$K7/$I7</f>
-        <v>0.0644373799629549</v>
+        <v>0.0653909273414378</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>98.5301</v>
@@ -15431,15 +15431,15 @@
       <c r="V7" s="2"/>
       <c r="W7" s="51" t="n">
         <f aca="false">AVERAGE(R7:R8)/100</f>
-        <v>0.0016755521182813</v>
+        <v>0.0016831601075488</v>
       </c>
       <c r="X7" s="0" t="n">
         <f aca="false">AVERAGE(S7:S8)/100</f>
-        <v>0.00190530150090893</v>
+        <v>0.00198845952239916</v>
       </c>
       <c r="Y7" s="1" t="n">
         <f aca="false">AVERAGE(T7:T8)/100</f>
-        <v>0.0013090241973592</v>
+        <v>0.00132687693021176</v>
       </c>
       <c r="Z7" s="33" t="n">
         <f aca="false">AVERAGE(U7:V8)/100</f>
@@ -15447,19 +15447,19 @@
       </c>
       <c r="AA7" s="2" t="n">
         <f aca="false">SUM(W7:Z7)</f>
-        <v>0.99622537781655</v>
+        <v>0.99633399656016</v>
       </c>
       <c r="AD7" s="0" t="n">
-        <v>0.00171311628665034</v>
+        <v>0.00172118263994998</v>
       </c>
       <c r="AE7" s="0" t="n">
-        <v>0.00116220819623103</v>
+        <v>0.00121915997361151</v>
       </c>
       <c r="AF7" s="0" t="n">
-        <v>0.000644373799629549</v>
+        <v>0.000653909273414378</v>
       </c>
       <c r="AG7" s="0" t="n">
-        <v>0.996480301717489</v>
+        <v>0.996405748113024</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15509,27 +15509,27 @@
       </c>
       <c r="O8" s="52" t="n">
         <f aca="false">(L8/$F$2)^(1/$F$3)</f>
-        <v>0.0397238892436625</v>
+        <v>0.039897279359871</v>
       </c>
       <c r="P8" s="53" t="n">
         <f aca="false">(M8/$G$2)^(1/$G$3)</f>
-        <v>0.0642279095742174</v>
+        <v>0.066880172049128</v>
       </c>
       <c r="Q8" s="54" t="n">
         <f aca="false">(N8/$H$2)^(1/$H$3)</f>
-        <v>0.0478648399229921</v>
+        <v>0.0484995050684866</v>
       </c>
       <c r="R8" s="55" t="n">
         <f aca="false">O8*$K8/$I8</f>
-        <v>0.163798794991226</v>
+        <v>0.164513757514762</v>
       </c>
       <c r="S8" s="53" t="n">
         <f aca="false">P8*$K8/$I8</f>
-        <v>0.264839480558683</v>
+        <v>0.275775907118681</v>
       </c>
       <c r="T8" s="54" t="n">
         <f aca="false">Q8*$K8/$I8</f>
-        <v>0.197367459508885</v>
+        <v>0.199984458700915</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>99.737</v>
@@ -15588,27 +15588,27 @@
       </c>
       <c r="O9" s="24" t="n">
         <f aca="false">(L9/$F$2)^(1/$F$3)</f>
-        <v>0.479592765918819</v>
+        <v>0.48706723626616</v>
       </c>
       <c r="P9" s="47" t="n">
         <f aca="false">(M9/$G$2)^(1/$G$3)</f>
-        <v>0.00293799927407238</v>
+        <v>0.00314850850650347</v>
       </c>
       <c r="Q9" s="26" t="n">
         <f aca="false">(N9/$H$2)^(1/$H$3)</f>
-        <v>0.00191512122893122</v>
+        <v>0.00194924821559036</v>
       </c>
       <c r="R9" s="25" t="n">
         <f aca="false">O9*$K9/$I9</f>
-        <v>1.98516805211487</v>
+        <v>2.0161069669494</v>
       </c>
       <c r="S9" s="47" t="n">
         <f aca="false">P9*$K9/$I9</f>
-        <v>0.0121611973959849</v>
+        <v>0.0130325537478615</v>
       </c>
       <c r="T9" s="26" t="n">
         <f aca="false">Q9*$K9/$I9</f>
-        <v>0.00792722023718926</v>
+        <v>0.00806848134128634</v>
       </c>
       <c r="U9" s="27" t="n">
         <v>99.3513</v>
@@ -15616,15 +15616,15 @@
       <c r="V9" s="27"/>
       <c r="W9" s="56" t="n">
         <f aca="false">AVERAGE(R9:R10)/100</f>
-        <v>0.0199932236064912</v>
+        <v>0.020307085950242</v>
       </c>
       <c r="X9" s="57" t="n">
         <f aca="false">AVERAGE(S9:S10)/100</f>
-        <v>9.10874643392223E-005</v>
+        <v>9.78145453972402E-005</v>
       </c>
       <c r="Y9" s="57" t="n">
         <f aca="false">AVERAGE(T9:T10)/100</f>
-        <v>4.73751805035506E-005</v>
+        <v>4.82369744427494E-005</v>
       </c>
       <c r="Z9" s="29" t="n">
         <f aca="false">AVERAGE(U9:V10)/100</f>
@@ -15632,19 +15632,19 @@
       </c>
       <c r="AA9" s="2" t="n">
         <f aca="false">SUM(W9:Z9)</f>
-        <v>0.993660352918001</v>
+        <v>0.993981804136749</v>
       </c>
       <c r="AD9" s="0" t="n">
-        <v>0.0199932236064912</v>
+        <v>0.020307085950242</v>
       </c>
       <c r="AE9" s="0" t="n">
-        <v>9.10874643392223E-005</v>
+        <v>9.78145453972403E-005</v>
       </c>
       <c r="AF9" s="0" t="n">
-        <v>4.73751805035506E-005</v>
+        <v>4.82369744427494E-005</v>
       </c>
       <c r="AG9" s="0" t="n">
-        <v>0.979868313748666</v>
+        <v>0.979546862529918</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15694,27 +15694,27 @@
       </c>
       <c r="O10" s="24" t="n">
         <f aca="false">(L10/$F$2)^(1/$F$3)</f>
-        <v>0.504038784037919</v>
+        <v>0.512007759319741</v>
       </c>
       <c r="P10" s="47" t="n">
         <f aca="false">(M10/$G$2)^(1/$G$3)</f>
-        <v>0.00151608799452766</v>
+        <v>0.00163476061632411</v>
       </c>
       <c r="Q10" s="26" t="n">
         <f aca="false">(N10/$H$2)^(1/$H$3)</f>
-        <v>0.000387468719009336</v>
+        <v>0.00039525348202147</v>
       </c>
       <c r="R10" s="25" t="n">
         <f aca="false">O10*$K10/$I10</f>
-        <v>2.01347666918336</v>
+        <v>2.04531022309901</v>
       </c>
       <c r="S10" s="47" t="n">
         <f aca="false">P10*$K10/$I10</f>
-        <v>0.00605629547185951</v>
+        <v>0.00653035533158653</v>
       </c>
       <c r="T10" s="26" t="n">
         <f aca="false">Q10*$K10/$I10</f>
-        <v>0.00154781586352087</v>
+        <v>0.00157891354726355</v>
       </c>
       <c r="U10" s="27" t="n">
         <v>96.8156</v>
@@ -15773,27 +15773,27 @@
       </c>
       <c r="O11" s="52" t="n">
         <f aca="false">(L11/$F$2)^(1/$F$3)</f>
-        <v>15.6792809404425</v>
+        <v>16.1732273417496</v>
       </c>
       <c r="P11" s="53" t="n">
         <f aca="false">(M11/$G$2)^(1/$G$3)</f>
-        <v>0.427701411648384</v>
+        <v>0.437566246577083</v>
       </c>
       <c r="Q11" s="54" t="n">
         <f aca="false">(N11/$H$2)^(1/$H$3)</f>
-        <v>0.374589913051385</v>
+        <v>0.37846885512816</v>
       </c>
       <c r="R11" s="55" t="n">
         <f aca="false">O11*$K11/$I11</f>
-        <v>65.0873382848403</v>
+        <v>67.1377930626183</v>
       </c>
       <c r="S11" s="53" t="n">
         <f aca="false">P11*$K11/$I11</f>
-        <v>1.77546065859807</v>
+        <v>1.81641125133043</v>
       </c>
       <c r="T11" s="54" t="n">
         <f aca="false">Q11*$K11/$I11</f>
-        <v>1.55498587476527</v>
+        <v>1.57108801721028</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>7.9147</v>
@@ -15801,15 +15801,15 @@
       <c r="V11" s="2"/>
       <c r="W11" s="51" t="n">
         <f aca="false">AVERAGE(R11:R12)/100</f>
-        <v>0.711559826820047</v>
+        <v>0.734289333198161</v>
       </c>
       <c r="X11" s="0" t="n">
         <f aca="false">AVERAGE(S11:S12)/100</f>
-        <v>0.0192869092792094</v>
+        <v>0.0197154540490328</v>
       </c>
       <c r="Y11" s="1" t="n">
         <f aca="false">AVERAGE(T11:T12)/100</f>
-        <v>0.0170671899539941</v>
+        <v>0.0172415202162556</v>
       </c>
       <c r="Z11" s="33" t="n">
         <f aca="false">AVERAGE(U11:V12)/100</f>
@@ -15817,16 +15817,16 @@
       </c>
       <c r="AA11" s="2" t="n">
         <f aca="false">SUM(W11:Z11)</f>
-        <v>0.825190926053251</v>
+        <v>0.84852330746345</v>
       </c>
       <c r="AD11" s="0" t="n">
-        <v>0.877871898371534</v>
+        <v>0.87850748825623</v>
       </c>
       <c r="AE11" s="0" t="n">
-        <v>0.0237948167174157</v>
+        <v>0.023587669374155</v>
       </c>
       <c r="AF11" s="0" t="n">
-        <v>0.0210562849110501</v>
+        <v>0.0206278423696154</v>
       </c>
       <c r="AG11" s="0" t="n">
         <v>0.077277</v>
@@ -15879,27 +15879,27 @@
       </c>
       <c r="O12" s="52" t="n">
         <f aca="false">(L12/$F$2)^(1/$F$3)</f>
-        <v>18.7007054964175</v>
+        <v>19.3050024908261</v>
       </c>
       <c r="P12" s="53" t="n">
         <f aca="false">(M12/$G$2)^(1/$G$3)</f>
-        <v>0.504157762218671</v>
+        <v>0.514996441064606</v>
       </c>
       <c r="Q12" s="54" t="n">
         <f aca="false">(N12/$H$2)^(1/$H$3)</f>
-        <v>0.450042519020622</v>
+        <v>0.454586384990316</v>
       </c>
       <c r="R12" s="55" t="n">
         <f aca="false">O12*$K12/$I12</f>
-        <v>77.2246270791691</v>
+        <v>79.7200735770139</v>
       </c>
       <c r="S12" s="53" t="n">
         <f aca="false">P12*$K12/$I12</f>
-        <v>2.0819211972438</v>
+        <v>2.12667955847614</v>
       </c>
       <c r="T12" s="54" t="n">
         <f aca="false">Q12*$K12/$I12</f>
-        <v>1.85845211603355</v>
+        <v>1.87721602604083</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>7.6881</v>
@@ -15960,27 +15960,27 @@
       </c>
       <c r="O13" s="24" t="n">
         <f aca="false">(L13/$F$2)^(1/$F$3)</f>
-        <v>8.26642098698944</v>
+        <v>8.50253029187062</v>
       </c>
       <c r="P13" s="47" t="n">
         <f aca="false">(M13/$G$2)^(1/$G$3)</f>
-        <v>4.79472453167782</v>
+        <v>4.7961098809998</v>
       </c>
       <c r="Q13" s="26" t="n">
         <f aca="false">(N13/$H$2)^(1/$H$3)</f>
-        <v>4.5623671814915</v>
+        <v>4.59356294944679</v>
       </c>
       <c r="R13" s="25" t="n">
         <f aca="false">O13*$K13/$I13</f>
-        <v>37.110081653989</v>
+        <v>38.1700368144143</v>
       </c>
       <c r="S13" s="47" t="n">
         <f aca="false">P13*$K13/$I13</f>
-        <v>21.5247468232016</v>
+        <v>21.5309660112322</v>
       </c>
       <c r="T13" s="26" t="n">
         <f aca="false">Q13*$K13/$I13</f>
-        <v>20.4816351486462</v>
+        <v>20.6216809433016</v>
       </c>
       <c r="U13" s="27" t="n">
         <v>3.7571</v>
@@ -15988,15 +15988,15 @@
       <c r="V13" s="27"/>
       <c r="W13" s="56" t="n">
         <f aca="false">AVERAGE(R13:R14)/100</f>
-        <v>0.361176945545563</v>
+        <v>0.37150273860173</v>
       </c>
       <c r="X13" s="57" t="n">
         <f aca="false">AVERAGE(S13:S14)/100</f>
-        <v>0.209501504956067</v>
+        <v>0.209550523433899</v>
       </c>
       <c r="Y13" s="57" t="n">
         <f aca="false">AVERAGE(T13:T14)/100</f>
-        <v>0.198960571071264</v>
+        <v>0.200319888712601</v>
       </c>
       <c r="Z13" s="29" t="n">
         <f aca="false">AVERAGE(U13:V14)/100</f>
@@ -16004,16 +16004,16 @@
       </c>
       <c r="AA13" s="2" t="n">
         <f aca="false">SUM(W13:Z13)</f>
-        <v>0.807112021572894</v>
+        <v>0.818846150748231</v>
       </c>
       <c r="AD13" s="0" t="n">
-        <v>0.45169560290052</v>
+        <v>0.45763207519441</v>
       </c>
       <c r="AE13" s="0" t="n">
-        <v>0.262007057085981</v>
+        <v>0.258132796700421</v>
       </c>
       <c r="AF13" s="0" t="n">
-        <v>0.248824340013499</v>
+        <v>0.246762128105168</v>
       </c>
       <c r="AG13" s="0" t="n">
         <v>0.037473</v>
@@ -16066,27 +16066,27 @@
       </c>
       <c r="O14" s="24" t="n">
         <f aca="false">(L14/$F$2)^(1/$F$3)</f>
-        <v>8.36646102769677</v>
+        <v>8.60588940869635</v>
       </c>
       <c r="P14" s="47" t="n">
         <f aca="false">(M14/$G$2)^(1/$G$3)</f>
-        <v>4.85323239041224</v>
+        <v>4.85408618059304</v>
       </c>
       <c r="Q14" s="26" t="n">
         <f aca="false">(N14/$H$2)^(1/$H$3)</f>
-        <v>4.59954324200473</v>
+        <v>4.63094077304223</v>
       </c>
       <c r="R14" s="25" t="n">
         <f aca="false">O14*$K14/$I14</f>
-        <v>35.1253074551236</v>
+        <v>36.1305109059318</v>
       </c>
       <c r="S14" s="47" t="n">
         <f aca="false">P14*$K14/$I14</f>
-        <v>20.3755541680117</v>
+        <v>20.3791386755476</v>
       </c>
       <c r="T14" s="26" t="n">
         <f aca="false">Q14*$K14/$I14</f>
-        <v>19.3104790656066</v>
+        <v>19.4422967992186</v>
       </c>
       <c r="U14" s="27" t="n">
         <v>3.7375</v>
@@ -16143,27 +16143,27 @@
       </c>
       <c r="O15" s="52" t="n">
         <f aca="false">(L15/$F$2)^(1/$F$3)</f>
-        <v>0.24878401154479</v>
+        <v>0.251922799941343</v>
       </c>
       <c r="P15" s="53" t="n">
         <f aca="false">(M15/$G$2)^(1/$G$3)</f>
-        <v>0.00979913914530533</v>
+        <v>0.0103840766168641</v>
       </c>
       <c r="Q15" s="54" t="n">
         <f aca="false">(N15/$H$2)^(1/$H$3)</f>
-        <v>0.00241456982156767</v>
+        <v>0.00245680241154308</v>
       </c>
       <c r="R15" s="55" t="n">
         <f aca="false">O15*$K15/$I15</f>
-        <v>1.05788188372426</v>
+        <v>1.07122867140945</v>
       </c>
       <c r="S15" s="53" t="n">
         <f aca="false">P15*$K15/$I15</f>
-        <v>0.0416679983313373</v>
+        <v>0.0441552753489849</v>
       </c>
       <c r="T15" s="54" t="n">
         <f aca="false">Q15*$K15/$I15</f>
-        <v>0.0102672581544248</v>
+        <v>0.0104468399995776</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>96.1251</v>
@@ -16171,15 +16171,15 @@
       <c r="V15" s="2"/>
       <c r="W15" s="51" t="n">
         <f aca="false">AVERAGE(R15:R16)/100</f>
-        <v>0.0105387202386728</v>
+        <v>0.0106713401134174</v>
       </c>
       <c r="X15" s="0" t="n">
         <f aca="false">AVERAGE(S15:S16)/100</f>
-        <v>0.00041621291029917</v>
+        <v>0.00044107640298022</v>
       </c>
       <c r="Y15" s="1" t="n">
         <f aca="false">AVERAGE(T15:T16)/100</f>
-        <v>0.000102279397953877</v>
+        <v>0.000104069388635398</v>
       </c>
       <c r="Z15" s="33" t="n">
         <f aca="false">AVERAGE(U15:V16)/100</f>
@@ -16187,19 +16187,19 @@
       </c>
       <c r="AA15" s="2" t="n">
         <f aca="false">SUM(W15:Z15)</f>
-        <v>0.972276879213593</v>
+        <v>0.9724361525717</v>
       </c>
       <c r="AD15" s="0" t="n">
-        <v>0.0105387202386728</v>
+        <v>0.0106713401134174</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>0.00041621291029917</v>
+        <v>0.00044107640298022</v>
       </c>
       <c r="AF15" s="0" t="n">
-        <v>0.000102279397953877</v>
+        <v>0.000104069388635398</v>
       </c>
       <c r="AG15" s="0" t="n">
-        <v>0.988942787453074</v>
+        <v>0.988783514094967</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16249,27 +16249,27 @@
       </c>
       <c r="O16" s="52" t="n">
         <f aca="false">(L16/$F$2)^(1/$F$3)</f>
-        <v>0.245219603776028</v>
+        <v>0.248297440801176</v>
       </c>
       <c r="P16" s="53" t="n">
         <f aca="false">(M16/$G$2)^(1/$G$3)</f>
-        <v>0.00971070612747142</v>
+        <v>0.010291233839481</v>
       </c>
       <c r="Q16" s="54" t="n">
         <f aca="false">(N16/$H$2)^(1/$H$3)</f>
-        <v>0.00237978831630828</v>
+        <v>0.00242146156992492</v>
       </c>
       <c r="R16" s="55" t="n">
         <f aca="false">O16*$K16/$I16</f>
-        <v>1.0498621640103</v>
+        <v>1.06303935127403</v>
       </c>
       <c r="S16" s="53" t="n">
         <f aca="false">P16*$K16/$I16</f>
-        <v>0.0415745837284967</v>
+        <v>0.044060005247059</v>
       </c>
       <c r="T16" s="54" t="n">
         <f aca="false">Q16*$K16/$I16</f>
-        <v>0.0101886214363506</v>
+        <v>0.010367037727502</v>
       </c>
       <c r="U16" s="2" t="n">
         <v>96.9043</v>
@@ -16330,27 +16330,27 @@
       </c>
       <c r="O17" s="24" t="n">
         <f aca="false">(L17/$F$2)^(1/$F$3)</f>
-        <v>0.302209623591112</v>
+        <v>0.306288078540341</v>
       </c>
       <c r="P17" s="47" t="n">
         <f aca="false">(M17/$G$2)^(1/$G$3)</f>
-        <v>0.00562357588530017</v>
+        <v>0.00599017025353638</v>
       </c>
       <c r="Q17" s="26" t="n">
         <f aca="false">(N17/$H$2)^(1/$H$3)</f>
-        <v>0.00128218118781856</v>
+        <v>0.00130576005045756</v>
       </c>
       <c r="R17" s="25" t="n">
         <f aca="false">O17*$K17/$I17</f>
-        <v>1.21652178987948</v>
+        <v>1.232939299209</v>
       </c>
       <c r="S17" s="47" t="n">
         <f aca="false">P17*$K17/$I17</f>
-        <v>0.022637275809471</v>
+        <v>0.0241129734782185</v>
       </c>
       <c r="T17" s="26" t="n">
         <f aca="false">Q17*$K17/$I17</f>
-        <v>0.00516132257808318</v>
+        <v>0.00525623749124866</v>
       </c>
       <c r="U17" s="27" t="n">
         <v>98.1075</v>
@@ -16358,15 +16358,15 @@
       <c r="V17" s="27"/>
       <c r="W17" s="56" t="n">
         <f aca="false">AVERAGE(R17:R18)/100</f>
-        <v>0.0117334469178797</v>
+        <v>0.0118897227611479</v>
       </c>
       <c r="X17" s="57" t="n">
         <f aca="false">AVERAGE(S17:S18)/100</f>
-        <v>0.000217258952848275</v>
+        <v>0.000231516305497412</v>
       </c>
       <c r="Y17" s="57" t="n">
         <f aca="false">AVERAGE(T17:T18)/100</f>
-        <v>5.02864256328093E-005</v>
+        <v>5.12132727659047E-005</v>
       </c>
       <c r="Z17" s="29" t="n">
         <f aca="false">AVERAGE(U17:V18)/100</f>
@@ -16374,19 +16374,19 @@
       </c>
       <c r="AA17" s="2" t="n">
         <f aca="false">SUM(W17:Z17)</f>
-        <v>0.996235492296361</v>
+        <v>0.996406952339411</v>
       </c>
       <c r="AD17" s="0" t="n">
-        <v>0.0117334469178797</v>
+        <v>0.0118897227611479</v>
       </c>
       <c r="AE17" s="0" t="n">
-        <v>0.000217258952848275</v>
+        <v>0.000231516305497412</v>
       </c>
       <c r="AF17" s="0" t="n">
-        <v>5.02864256328093E-005</v>
+        <v>5.12132727659047E-005</v>
       </c>
       <c r="AG17" s="0" t="n">
-        <v>0.987999007703639</v>
+        <v>0.987827547660589</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16436,27 +16436,27 @@
       </c>
       <c r="O18" s="24" t="n">
         <f aca="false">(L18/$F$2)^(1/$F$3)</f>
-        <v>0.27865464565796</v>
+        <v>0.282313025817166</v>
       </c>
       <c r="P18" s="47" t="n">
         <f aca="false">(M18/$G$2)^(1/$G$3)</f>
-        <v>0.0051320364053893</v>
+        <v>0.00547124759959475</v>
       </c>
       <c r="Q18" s="26" t="n">
         <f aca="false">(N18/$H$2)^(1/$H$3)</f>
-        <v>0.00120715079490006</v>
+        <v>0.00122945330165673</v>
       </c>
       <c r="R18" s="25" t="n">
         <f aca="false">O18*$K18/$I18</f>
-        <v>1.13016759369645</v>
+        <v>1.14500525302058</v>
       </c>
       <c r="S18" s="47" t="n">
         <f aca="false">P18*$K18/$I18</f>
-        <v>0.0208145147601839</v>
+        <v>0.0221902876212639</v>
       </c>
       <c r="T18" s="26" t="n">
         <f aca="false">Q18*$K18/$I18</f>
-        <v>0.00489596254847867</v>
+        <v>0.00498641706193228</v>
       </c>
       <c r="U18" s="27" t="n">
         <v>98.7394</v>
@@ -16513,27 +16513,27 @@
       </c>
       <c r="O19" s="52" t="n">
         <f aca="false">(L19/$F$2)^(1/$F$3)</f>
-        <v>7.73834338982771</v>
+        <v>7.95702649940259</v>
       </c>
       <c r="P19" s="53" t="n">
         <f aca="false">(M19/$G$2)^(1/$G$3)</f>
-        <v>1.73515553156925</v>
+        <v>1.75216874403373</v>
       </c>
       <c r="Q19" s="54" t="n">
         <f aca="false">(N19/$H$2)^(1/$H$3)</f>
-        <v>1.57670840305274</v>
+        <v>1.58984431987318</v>
       </c>
       <c r="R19" s="55" t="n">
         <f aca="false">O19*$K19/$I19</f>
-        <v>34.7844044598607</v>
+        <v>35.7674006062959</v>
       </c>
       <c r="S19" s="53" t="n">
         <f aca="false">P19*$K19/$I19</f>
-        <v>7.79964764683483</v>
+        <v>7.87612324809903</v>
       </c>
       <c r="T19" s="54" t="n">
         <f aca="false">Q19*$K19/$I19</f>
-        <v>7.0874165236894</v>
+        <v>7.14646340499402</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>5.2624</v>
@@ -16541,15 +16541,15 @@
       <c r="V19" s="2"/>
       <c r="W19" s="51" t="n">
         <f aca="false">AVERAGE(R19:R20)/100</f>
-        <v>0.366631152554902</v>
+        <v>0.377159855749177</v>
       </c>
       <c r="X19" s="0" t="n">
         <f aca="false">AVERAGE(S19:S20)/100</f>
-        <v>0.0819775264302381</v>
+        <v>0.0827068093624299</v>
       </c>
       <c r="Y19" s="1" t="n">
         <f aca="false">AVERAGE(T19:T20)/100</f>
-        <v>0.0749423378111749</v>
+        <v>0.0755558126447871</v>
       </c>
       <c r="Z19" s="33" t="n">
         <f aca="false">AVERAGE(U19:V20)/100</f>
@@ -16557,16 +16557,16 @@
       </c>
       <c r="AA19" s="2" t="n">
         <f aca="false">SUM(W19:Z19)</f>
-        <v>0.577268016796315</v>
+        <v>0.589139477756394</v>
       </c>
       <c r="AD19" s="0" t="n">
-        <v>0.662660974389979</v>
+        <v>0.66657634784672</v>
       </c>
       <c r="AE19" s="0" t="n">
-        <v>0.148168826254357</v>
+        <v>0.146172510373232</v>
       </c>
       <c r="AF19" s="0" t="n">
-        <v>0.135453199355664</v>
+        <v>0.133534141780048</v>
       </c>
       <c r="AG19" s="0" t="n">
         <v>0.053717</v>
@@ -16619,27 +16619,27 @@
       </c>
       <c r="O20" s="52" t="n">
         <f aca="false">(L20/$F$2)^(1/$F$3)</f>
-        <v>9.35591150194276</v>
+        <v>9.62845432584637</v>
       </c>
       <c r="P20" s="53" t="n">
         <f aca="false">(M20/$G$2)^(1/$G$3)</f>
-        <v>2.08661839864842</v>
+        <v>2.10346042259265</v>
       </c>
       <c r="Q20" s="54" t="n">
         <f aca="false">(N20/$H$2)^(1/$H$3)</f>
-        <v>1.9179562014244</v>
+        <v>1.933406581322</v>
       </c>
       <c r="R20" s="55" t="n">
         <f aca="false">O20*$K20/$I20</f>
-        <v>38.5418260511197</v>
+        <v>39.6645705435396</v>
       </c>
       <c r="S20" s="53" t="n">
         <f aca="false">P20*$K20/$I20</f>
-        <v>8.59585763921279</v>
+        <v>8.66523862438694</v>
       </c>
       <c r="T20" s="54" t="n">
         <f aca="false">Q20*$K20/$I20</f>
-        <v>7.90105103854559</v>
+        <v>7.9646991239634</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>5.481</v>
@@ -16698,27 +16698,27 @@
       </c>
       <c r="O21" s="24" t="n">
         <f aca="false">(L21/$F$2)^(1/$F$3)</f>
-        <v>4.63796565673842</v>
+        <v>4.75815752860883</v>
       </c>
       <c r="P21" s="47" t="n">
         <f aca="false">(M21/$G$2)^(1/$G$3)</f>
-        <v>6.45385271093435</v>
+        <v>6.43787158411199</v>
       </c>
       <c r="Q21" s="26" t="n">
         <f aca="false">(N21/$H$2)^(1/$H$3)</f>
-        <v>6.28395322864674</v>
+        <v>6.32409514476834</v>
       </c>
       <c r="R21" s="25" t="n">
         <f aca="false">O21*$K21/$I21</f>
-        <v>21.0113124768651</v>
+        <v>21.5558160726128</v>
       </c>
       <c r="S21" s="47" t="n">
         <f aca="false">P21*$K21/$I21</f>
-        <v>29.2378008000313</v>
+        <v>29.1654017194325</v>
       </c>
       <c r="T21" s="26" t="n">
         <f aca="false">Q21*$K21/$I21</f>
-        <v>28.468107495637</v>
+        <v>28.6499618700491</v>
       </c>
       <c r="U21" s="27" t="n">
         <v>2.7174</v>
@@ -16726,15 +16726,15 @@
       <c r="V21" s="27"/>
       <c r="W21" s="56" t="n">
         <f aca="false">AVERAGE(R21:R22)/100</f>
-        <v>0.209443310732854</v>
+        <v>0.214902160818875</v>
       </c>
       <c r="X21" s="57" t="n">
         <f aca="false">AVERAGE(S21:S22)/100</f>
-        <v>0.291365856514499</v>
+        <v>0.290557108657992</v>
       </c>
       <c r="Y21" s="57" t="n">
         <f aca="false">AVERAGE(T21:T22)/100</f>
-        <v>0.282063408157154</v>
+        <v>0.283854815069946</v>
       </c>
       <c r="Z21" s="29" t="n">
         <f aca="false">AVERAGE(U21:V22)/100</f>
@@ -16742,16 +16742,16 @@
       </c>
       <c r="AA21" s="2" t="n">
         <f aca="false">SUM(W21:Z21)</f>
-        <v>0.809973075404506</v>
+        <v>0.816414584546813</v>
       </c>
       <c r="AD21" s="0" t="n">
-        <v>0.260281556273769</v>
+        <v>0.264885941988031</v>
       </c>
       <c r="AE21" s="0" t="n">
-        <v>0.362089189257346</v>
+        <v>0.358137364161074</v>
       </c>
       <c r="AF21" s="0" t="n">
-        <v>0.350528754468886</v>
+        <v>0.349876193850895</v>
       </c>
       <c r="AG21" s="0" t="n">
         <v>0.0271005</v>
@@ -16804,27 +16804,27 @@
       </c>
       <c r="O22" s="24" t="n">
         <f aca="false">(L22/$F$2)^(1/$F$3)</f>
-        <v>4.9507183971598</v>
+        <v>5.08049358336476</v>
       </c>
       <c r="P22" s="47" t="n">
         <f aca="false">(M22/$G$2)^(1/$G$3)</f>
-        <v>6.88525819565527</v>
+        <v>6.86407020363931</v>
       </c>
       <c r="Q22" s="26" t="n">
         <f aca="false">(N22/$H$2)^(1/$H$3)</f>
-        <v>6.62659386673099</v>
+        <v>6.6684306155906</v>
       </c>
       <c r="R22" s="25" t="n">
         <f aca="false">O22*$K22/$I22</f>
-        <v>20.8773496697057</v>
+        <v>21.4246160911621</v>
       </c>
       <c r="S22" s="47" t="n">
         <f aca="false">P22*$K22/$I22</f>
-        <v>29.0353705028685</v>
+        <v>28.946020012166</v>
       </c>
       <c r="T22" s="26" t="n">
         <f aca="false">Q22*$K22/$I22</f>
-        <v>27.9445741357937</v>
+        <v>28.12100114394</v>
       </c>
       <c r="U22" s="27" t="n">
         <v>2.7027</v>
@@ -16881,27 +16881,27 @@
       </c>
       <c r="O23" s="52" t="n">
         <f aca="false">(L23/$F$2)^(1/$F$3)</f>
-        <v>0.166978350011516</v>
+        <v>0.168784628887013</v>
       </c>
       <c r="P23" s="53" t="n">
         <f aca="false">(M23/$G$2)^(1/$G$3)</f>
-        <v>0.0132040954049389</v>
+        <v>0.013953465226377</v>
       </c>
       <c r="Q23" s="54" t="n">
         <f aca="false">(N23/$H$2)^(1/$H$3)</f>
-        <v>0.00397791196003483</v>
+        <v>0.00404467040104209</v>
       </c>
       <c r="R23" s="55" t="n">
         <f aca="false">O23*$K23/$I23</f>
-        <v>0.682754077629012</v>
+        <v>0.690139731323017</v>
       </c>
       <c r="S23" s="53" t="n">
         <f aca="false">P23*$K23/$I23</f>
-        <v>0.0539899332967586</v>
+        <v>0.0570540149648534</v>
       </c>
       <c r="T23" s="54" t="n">
         <f aca="false">Q23*$K23/$I23</f>
-        <v>0.0162651961225853</v>
+        <v>0.0165381632336552</v>
       </c>
       <c r="U23" s="2" t="n">
         <v>98.712</v>
@@ -16909,15 +16909,15 @@
       <c r="V23" s="2"/>
       <c r="W23" s="51" t="n">
         <f aca="false">AVERAGE(R23:R24)/100</f>
-        <v>0.00594852754205581</v>
+        <v>0.00600981612283326</v>
       </c>
       <c r="X23" s="0" t="n">
         <f aca="false">AVERAGE(S23:S24)/100</f>
-        <v>0.000466638280023819</v>
+        <v>0.000493677333551138</v>
       </c>
       <c r="Y23" s="1" t="n">
         <f aca="false">AVERAGE(T23:T24)/100</f>
-        <v>0.000136636083907715</v>
+        <v>0.000138957062887524</v>
       </c>
       <c r="Z23" s="33" t="n">
         <f aca="false">AVERAGE(U23:V24)/100</f>
@@ -16925,19 +16925,19 @@
       </c>
       <c r="AA23" s="2" t="n">
         <f aca="false">SUM(W23:Z23)</f>
-        <v>0.989475801905987</v>
+        <v>0.989566450519272</v>
       </c>
       <c r="AD23" s="0" t="n">
-        <v>0.00594852754205581</v>
+        <v>0.00600981612283326</v>
       </c>
       <c r="AE23" s="0" t="n">
-        <v>0.000466638280023819</v>
+        <v>0.000493677333551138</v>
       </c>
       <c r="AF23" s="0" t="n">
-        <v>0.000136636083907715</v>
+        <v>0.000138957062887524</v>
       </c>
       <c r="AG23" s="0" t="n">
-        <v>0.993448198094013</v>
+        <v>0.993357549480728</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16987,27 +16987,27 @@
       </c>
       <c r="O24" s="58" t="n">
         <f aca="false">(L24/$F$2)^(1/$F$3)</f>
-        <v>0.127737761898264</v>
+        <v>0.128965387104289</v>
       </c>
       <c r="P24" s="59" t="n">
         <f aca="false">(M24/$G$2)^(1/$G$3)</f>
-        <v>0.00991201987366405</v>
+        <v>0.010502574872725</v>
       </c>
       <c r="Q24" s="60" t="n">
         <f aca="false">(N24/$H$2)^(1/$H$3)</f>
-        <v>0.00278732374592081</v>
+        <v>0.00283550809403706</v>
       </c>
       <c r="R24" s="55" t="n">
         <f aca="false">O24*$K24/$I24</f>
-        <v>0.506951430782149</v>
+        <v>0.511823493243635</v>
       </c>
       <c r="S24" s="53" t="n">
         <f aca="false">P24*$K24/$I24</f>
-        <v>0.0393377227080053</v>
+        <v>0.0416814517453742</v>
       </c>
       <c r="T24" s="54" t="n">
         <f aca="false">Q24*$K24/$I24</f>
-        <v>0.0110620206589577</v>
+        <v>0.0112532493438496</v>
       </c>
       <c r="U24" s="42" t="n">
         <v>97.8728</v>
@@ -17062,30 +17062,30 @@
       </c>
       <c r="P25" s="1" t="n">
         <f aca="false">(M25/$G$2)^(1/$G$3)</f>
-        <v>17.4852943902468</v>
+        <v>17.280806121993</v>
       </c>
       <c r="Q25" s="1" t="n">
         <f aca="false">(N25/$H$2)^(1/$H$3)</f>
-        <v>16.3105646428654</v>
+        <v>16.3929276704743</v>
       </c>
       <c r="S25" s="1" t="n">
         <f aca="false">P25*$K25/$I25</f>
-        <v>17.4852943902468</v>
+        <v>17.280806121993</v>
       </c>
       <c r="T25" s="1" t="n">
         <f aca="false">Q25*$K25/$I25</f>
-        <v>16.3105646428654</v>
+        <v>16.3929276704743</v>
       </c>
       <c r="U25" s="1" t="n">
         <v>1.6402</v>
       </c>
       <c r="X25" s="1" t="n">
         <f aca="false">AVERAGE(S25:S26)/100</f>
-        <v>0.175386376453612</v>
+        <v>0.173330329505173</v>
       </c>
       <c r="Y25" s="1" t="n">
         <f aca="false">AVERAGE(T25:T26)/100</f>
-        <v>0.163703626580661</v>
+        <v>0.16452943490993</v>
       </c>
       <c r="Z25" s="1" t="n">
         <f aca="false">AVERAGE(U25:V26)/100</f>
@@ -17093,19 +17093,19 @@
       </c>
       <c r="AA25" s="1" t="n">
         <f aca="false">SUM(W25:Z25)</f>
-        <v>0.355688003034273</v>
+        <v>0.354457764415103</v>
       </c>
       <c r="AE25" s="1" t="n">
         <f aca="false">IFERROR(X25/$AA25,"")</f>
-        <v>0.493090503355302</v>
+        <v>0.48900136181581</v>
       </c>
       <c r="AF25" s="1" t="n">
         <f aca="false">IFERROR(Y25/$AA25,"")</f>
-        <v>0.460245004566227</v>
+        <v>0.464172184749353</v>
       </c>
       <c r="AG25" s="1" t="n">
         <f aca="false">IFERROR(Z25/$AA25,"")</f>
-        <v>0.046664492078471</v>
+        <v>0.0468264534348363</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17149,19 +17149,19 @@
       </c>
       <c r="P26" s="1" t="n">
         <f aca="false">(M26/$G$2)^(1/$G$3)</f>
-        <v>17.5919809004757</v>
+        <v>17.3852597790416</v>
       </c>
       <c r="Q26" s="1" t="n">
         <f aca="false">(N26/$H$2)^(1/$H$3)</f>
-        <v>16.4301606732669</v>
+        <v>16.5129593115117</v>
       </c>
       <c r="S26" s="1" t="n">
         <f aca="false">P26*$K26/$I26</f>
-        <v>17.5919809004757</v>
+        <v>17.3852597790416</v>
       </c>
       <c r="T26" s="1" t="n">
         <f aca="false">Q26*$K26/$I26</f>
-        <v>16.4301606732669</v>
+        <v>16.5129593115117</v>
       </c>
       <c r="U26" s="1" t="n">
         <v>1.6794</v>
@@ -17208,27 +17208,27 @@
       </c>
       <c r="P27" s="1" t="n">
         <f aca="false">(M27/$G$2)^(1/$G$3)</f>
-        <v>0.241687739031325</v>
+        <v>0.248580414994283</v>
       </c>
       <c r="Q27" s="1" t="n">
         <f aca="false">(N27/$H$2)^(1/$H$3)</f>
-        <v>0.202995260863129</v>
+        <v>0.205272691431931</v>
       </c>
       <c r="S27" s="1" t="n">
         <f aca="false">P27*$K27/$I27</f>
-        <v>0.241687739031325</v>
+        <v>0.248580414994283</v>
       </c>
       <c r="T27" s="1" t="n">
         <f aca="false">Q27*$K27/$I27</f>
-        <v>0.202995260863129</v>
+        <v>0.205272691431931</v>
       </c>
       <c r="X27" s="1" t="n">
         <f aca="false">AVERAGE(S27:S28)/100</f>
-        <v>0.00132887258837791</v>
+        <v>0.00136946024088762</v>
       </c>
       <c r="Y27" s="1" t="n">
         <f aca="false">AVERAGE(T27:T28)/100</f>
-        <v>0.00105677034748015</v>
+        <v>0.0010688148978506</v>
       </c>
       <c r="Z27" s="1" t="e">
         <f aca="false">AVERAGE(U27:V28)/100</f>
@@ -17292,19 +17292,19 @@
       </c>
       <c r="P28" s="1" t="n">
         <f aca="false">(M28/$G$2)^(1/$G$3)</f>
-        <v>0.0240867786442566</v>
+        <v>0.0253116331832403</v>
       </c>
       <c r="Q28" s="1" t="n">
         <f aca="false">(N28/$H$2)^(1/$H$3)</f>
-        <v>0.00835880863290191</v>
+        <v>0.00849028813818957</v>
       </c>
       <c r="S28" s="1" t="n">
         <f aca="false">P28*$K28/$I28</f>
-        <v>0.0240867786442566</v>
+        <v>0.0253116331832403</v>
       </c>
       <c r="T28" s="1" t="n">
         <f aca="false">Q28*$K28/$I28</f>
-        <v>0.00835880863290191</v>
+        <v>0.00849028813818957</v>
       </c>
     </row>
   </sheetData>
@@ -17365,13 +17365,13 @@
         <v>2</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>157.651809</v>
+        <v>154.574631</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>141.723567</v>
+        <v>139.485507</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>129.780531</v>
+        <v>128.508587</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17379,13 +17379,13 @@
         <v>3</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>1.05643576</v>
+        <v>1.05174512</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.05899702</v>
+        <v>1.06895477</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.03602508</v>
+        <v>1.0374418</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>70</v>
@@ -17537,27 +17537,27 @@
       </c>
       <c r="O5" s="24" t="n">
         <f aca="false">(L5/$F$2)^(1/$F$3)</f>
-        <v>0.0502475741365826</v>
+        <v>0.0505198215163341</v>
       </c>
       <c r="P5" s="47" t="n">
         <f aca="false">(M5/$G$2)^(1/$G$3)</f>
-        <v>0.000190634938046535</v>
+        <v>0.00020956607740962</v>
       </c>
       <c r="Q5" s="26" t="n">
         <f aca="false">(N5/$H$2)^(1/$H$3)</f>
-        <v>0.000146161092831808</v>
+        <v>0.00014934547663136</v>
       </c>
       <c r="R5" s="25" t="n">
         <f aca="false">O5*$K5/$I5</f>
-        <v>0.209407663408843</v>
+        <v>0.210542259230483</v>
       </c>
       <c r="S5" s="47" t="n">
         <f aca="false">P5*$K5/$I5</f>
-        <v>0.000794474511981473</v>
+        <v>0.000873370373678498</v>
       </c>
       <c r="T5" s="26" t="n">
         <f aca="false">Q5*$K5/$I5</f>
-        <v>0.00060912896706208</v>
+        <v>0.000622399943468795</v>
       </c>
       <c r="U5" s="27" t="n">
         <v>97.8647</v>
@@ -17565,15 +17565,15 @@
       <c r="V5" s="27"/>
       <c r="W5" s="48" t="n">
         <f aca="false">AVERAGE(R5:R6)/100</f>
-        <v>0.0017337801887748</v>
+        <v>0.00174207999767895</v>
       </c>
       <c r="X5" s="49" t="n">
         <f aca="false">AVERAGE(S5:S6)/100</f>
-        <v>7.60405184761902E-006</v>
+        <v>8.36005031851114E-006</v>
       </c>
       <c r="Y5" s="49" t="n">
         <f aca="false">AVERAGE(T5:T6)/100</f>
-        <v>4.11555791803458E-006</v>
+        <v>4.20668670118973E-006</v>
       </c>
       <c r="Z5" s="50" t="n">
         <f aca="false">AVERAGE(U5:V6)/100</f>
@@ -17581,19 +17581,19 @@
       </c>
       <c r="AA5" s="2" t="n">
         <f aca="false">SUM(W5:Z5)</f>
-        <v>0.973618999798541</v>
+        <v>0.973628146734699</v>
       </c>
       <c r="AD5" s="0" t="n">
-        <v>0.0017337801887748</v>
+        <v>0.00174207999767895</v>
       </c>
       <c r="AE5" s="0" t="n">
-        <v>7.60405184761902E-006</v>
+        <v>8.36005031851114E-006</v>
       </c>
       <c r="AF5" s="0" t="n">
-        <v>4.11555791803458E-006</v>
+        <v>4.20668670118973E-006</v>
       </c>
       <c r="AG5" s="0" t="n">
-        <v>0.99825450020146</v>
+        <v>0.998245353265301</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17643,27 +17643,27 @@
       </c>
       <c r="O6" s="24" t="n">
         <f aca="false">(L6/$F$2)^(1/$F$3)</f>
-        <v>0.035212689472986</v>
+        <v>0.035347380170773</v>
       </c>
       <c r="P6" s="47" t="n">
         <f aca="false">(M6/$G$2)^(1/$G$3)</f>
-        <v>0.000186214355477415</v>
+        <v>0.000204751250529834</v>
       </c>
       <c r="Q6" s="26" t="n">
         <f aca="false">(N6/$H$2)^(1/$H$3)</f>
-        <v>5.48597933166821E-005</v>
+        <v>5.61300750966913E-005</v>
       </c>
       <c r="R6" s="25" t="n">
         <f aca="false">O6*$K6/$I6</f>
-        <v>0.137348374346118</v>
+        <v>0.137873740305307</v>
       </c>
       <c r="S6" s="47" t="n">
         <f aca="false">P6*$K6/$I6</f>
-        <v>0.000726335857542331</v>
+        <v>0.00079863969002373</v>
       </c>
       <c r="T6" s="26" t="n">
         <f aca="false">Q6*$K6/$I6</f>
-        <v>0.000213982616544835</v>
+        <v>0.000218937396769152</v>
       </c>
       <c r="U6" s="27" t="n">
         <v>96.51</v>
@@ -17720,27 +17720,27 @@
       </c>
       <c r="O7" s="52" t="n">
         <f aca="false">(L7/$F$2)^(1/$F$3)</f>
-        <v>1.3118749041286</v>
+        <v>1.33831321393585</v>
       </c>
       <c r="P7" s="53" t="n">
         <f aca="false">(M7/$G$2)^(1/$G$3)</f>
-        <v>0.0290678754035656</v>
+        <v>0.0304925873918147</v>
       </c>
       <c r="Q7" s="54" t="n">
         <f aca="false">(N7/$H$2)^(1/$H$3)</f>
-        <v>0.0253909369107006</v>
+        <v>0.0257620432990333</v>
       </c>
       <c r="R7" s="55" t="n">
         <f aca="false">O7*$K7/$I7</f>
-        <v>5.22696949281913</v>
+        <v>5.33230898698071</v>
       </c>
       <c r="S7" s="53" t="n">
         <f aca="false">P7*$K7/$I7</f>
-        <v>0.115816605285568</v>
+        <v>0.121493157276307</v>
       </c>
       <c r="T7" s="54" t="n">
         <f aca="false">Q7*$K7/$I7</f>
-        <v>0.101166393387549</v>
+        <v>0.102645011329169</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>7.505</v>
@@ -17748,15 +17748,15 @@
       <c r="V7" s="2"/>
       <c r="W7" s="51" t="n">
         <f aca="false">AVERAGE(R7:R8)/100</f>
-        <v>0.215878211662066</v>
+        <v>0.221982813234413</v>
       </c>
       <c r="X7" s="0" t="n">
         <f aca="false">AVERAGE(S7:S8)/100</f>
-        <v>0.00525521306096492</v>
+        <v>0.00541646203090846</v>
       </c>
       <c r="Y7" s="1" t="n">
         <f aca="false">AVERAGE(T7:T8)/100</f>
-        <v>0.00488409142537459</v>
+        <v>0.00494215961044987</v>
       </c>
       <c r="Z7" s="33" t="n">
         <f aca="false">AVERAGE(U7:V8)/100</f>
@@ -17764,16 +17764,16 @@
       </c>
       <c r="AA7" s="2" t="n">
         <f aca="false">SUM(W7:Z7)</f>
-        <v>0.301978016148405</v>
+        <v>0.308301934875772</v>
       </c>
       <c r="AD7" s="0" t="n">
-        <v>0.88258643915956</v>
+        <v>0.882842476458815</v>
       </c>
       <c r="AE7" s="0" t="n">
-        <v>0.0214851686364829</v>
+        <v>0.0215416801117964</v>
       </c>
       <c r="AF7" s="0" t="n">
-        <v>0.0199678922039568</v>
+        <v>0.019655343429389</v>
       </c>
       <c r="AG7" s="0" t="n">
         <v>0.0759605</v>
@@ -17826,27 +17826,27 @@
       </c>
       <c r="O8" s="52" t="n">
         <f aca="false">(L8/$F$2)^(1/$F$3)</f>
-        <v>9.91526459200457</v>
+        <v>10.2067445879948</v>
       </c>
       <c r="P8" s="53" t="n">
         <f aca="false">(M8/$G$2)^(1/$G$3)</f>
-        <v>0.244356722328794</v>
+        <v>0.251299803753299</v>
       </c>
       <c r="Q8" s="54" t="n">
         <f aca="false">(N8/$H$2)^(1/$H$3)</f>
-        <v>0.228791142005652</v>
+        <v>0.231439229230808</v>
       </c>
       <c r="R8" s="55" t="n">
         <f aca="false">O8*$K8/$I8</f>
-        <v>37.9486728395941</v>
+        <v>39.0642536599019</v>
       </c>
       <c r="S8" s="53" t="n">
         <f aca="false">P8*$K8/$I8</f>
-        <v>0.935226006907415</v>
+        <v>0.961799248905385</v>
       </c>
       <c r="T8" s="54" t="n">
         <f aca="false">Q8*$K8/$I8</f>
-        <v>0.87565189168737</v>
+        <v>0.885786910760806</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>7.6871</v>
@@ -17905,27 +17905,27 @@
       </c>
       <c r="O9" s="24" t="n">
         <f aca="false">(L9/$F$2)^(1/$F$3)</f>
-        <v>0.0371012794625793</v>
+        <v>0.0372518730065994</v>
       </c>
       <c r="P9" s="47" t="n">
         <f aca="false">(M9/$G$2)^(1/$G$3)</f>
-        <v>0.140955475756152</v>
+        <v>0.145705402690506</v>
       </c>
       <c r="Q9" s="26" t="n">
         <f aca="false">(N9/$H$2)^(1/$H$3)</f>
-        <v>0.133449110812237</v>
+        <v>0.135093100525103</v>
       </c>
       <c r="R9" s="25" t="n">
         <f aca="false">O9*$K9/$I9</f>
-        <v>0.15038846236303</v>
+        <v>0.150998886905122</v>
       </c>
       <c r="S9" s="47" t="n">
         <f aca="false">P9*$K9/$I9</f>
-        <v>0.571357041257772</v>
+        <v>0.590610668581183</v>
       </c>
       <c r="T9" s="26" t="n">
         <f aca="false">Q9*$K9/$I9</f>
-        <v>0.540930309398302</v>
+        <v>0.547594151956828</v>
       </c>
       <c r="U9" s="27"/>
       <c r="V9" s="27" t="n">
@@ -17933,15 +17933,15 @@
       </c>
       <c r="W9" s="56" t="n">
         <f aca="false">AVERAGE(R9:R10)/100</f>
-        <v>0.00121055917495156</v>
+        <v>0.00121445750357764</v>
       </c>
       <c r="X9" s="57" t="n">
         <f aca="false">AVERAGE(S9:S10)/100</f>
-        <v>0.00343562518302705</v>
+        <v>0.00356036659353755</v>
       </c>
       <c r="Y9" s="57" t="n">
         <f aca="false">AVERAGE(T9:T10)/100</f>
-        <v>0.00316894355177909</v>
+        <v>0.00320911522594554</v>
       </c>
       <c r="Z9" s="29" t="n">
         <f aca="false">AVERAGE(U9:V10)/100</f>
@@ -17949,19 +17949,19 @@
       </c>
       <c r="AA9" s="2" t="n">
         <f aca="false">SUM(W9:Z9)</f>
-        <v>0.996566127909758</v>
+        <v>0.996734939323061</v>
       </c>
       <c r="AD9" s="0" t="n">
-        <v>0.000917233726272819</v>
+        <v>0.000918926138104065</v>
       </c>
       <c r="AE9" s="0" t="n">
-        <v>0.00115767995347639</v>
+        <v>0.00121462650126326</v>
       </c>
       <c r="AF9" s="0" t="n">
-        <v>0.000928584009575148</v>
+        <v>0.000942288932322795</v>
       </c>
       <c r="AG9" s="0" t="n">
-        <v>0.996996502310676</v>
+        <v>0.99692415842831</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18011,27 +18011,27 @@
       </c>
       <c r="O10" s="24" t="n">
         <f aca="false">(L10/$F$2)^(1/$F$3)</f>
-        <v>0.0226173247927191</v>
+        <v>0.0226590566076032</v>
       </c>
       <c r="P10" s="47" t="n">
         <f aca="false">(M10/$G$2)^(1/$G$3)</f>
-        <v>0.0285462938875925</v>
+        <v>0.0299504927632197</v>
       </c>
       <c r="Q10" s="26" t="n">
         <f aca="false">(N10/$H$2)^(1/$H$3)</f>
-        <v>0.0228972022509775</v>
+        <v>0.0232351408593867</v>
       </c>
       <c r="R10" s="25" t="n">
         <f aca="false">O10*$K10/$I10</f>
-        <v>0.0917233726272819</v>
+        <v>0.0918926138104065</v>
       </c>
       <c r="S10" s="47" t="n">
         <f aca="false">P10*$K10/$I10</f>
-        <v>0.115767995347639</v>
+        <v>0.121462650126326</v>
       </c>
       <c r="T10" s="26" t="n">
         <f aca="false">Q10*$K10/$I10</f>
-        <v>0.0928584009575148</v>
+        <v>0.0942288932322795</v>
       </c>
       <c r="U10" s="27"/>
       <c r="V10" s="27"/>
@@ -18086,27 +18086,27 @@
       </c>
       <c r="O11" s="52" t="n">
         <f aca="false">(L11/$F$2)^(1/$F$3)</f>
-        <v>0.470238684026287</v>
+        <v>0.477525420300974</v>
       </c>
       <c r="P11" s="53" t="n">
         <f aca="false">(M11/$G$2)^(1/$G$3)</f>
-        <v>5.10940712858174</v>
+        <v>5.10785786738667</v>
       </c>
       <c r="Q11" s="54" t="n">
         <f aca="false">(N11/$H$2)^(1/$H$3)</f>
-        <v>5.32181796729607</v>
+        <v>5.36033016027047</v>
       </c>
       <c r="R11" s="55" t="n">
         <f aca="false">O11*$K11/$I11</f>
-        <v>1.91202573396488</v>
+        <v>1.94165414980367</v>
       </c>
       <c r="S11" s="53" t="n">
         <f aca="false">P11*$K11/$I11</f>
-        <v>20.7752323384049</v>
+        <v>20.7689329262675</v>
       </c>
       <c r="T11" s="54" t="n">
         <f aca="false">Q11*$K11/$I11</f>
-        <v>21.6389107289563</v>
+        <v>21.7955041921057</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>1.9451</v>
@@ -18114,15 +18114,15 @@
       <c r="V11" s="2"/>
       <c r="W11" s="51" t="n">
         <f aca="false">AVERAGE(R11:R12)/100</f>
-        <v>0.0260870356189322</v>
+        <v>0.0265342850121142</v>
       </c>
       <c r="X11" s="0" t="n">
         <f aca="false">AVERAGE(S11:S12)/100</f>
-        <v>0.283987472418256</v>
+        <v>0.282936391547775</v>
       </c>
       <c r="Y11" s="1" t="n">
         <f aca="false">AVERAGE(T11:T12)/100</f>
-        <v>0.295159306623553</v>
+        <v>0.297147855370616</v>
       </c>
       <c r="Z11" s="33" t="n">
         <f aca="false">AVERAGE(U11:V12)/100</f>
@@ -18130,16 +18130,16 @@
       </c>
       <c r="AA11" s="2" t="n">
         <f aca="false">SUM(W11:Z11)</f>
-        <v>0.624499314660742</v>
+        <v>0.625884031930506</v>
       </c>
       <c r="AD11" s="0" t="n">
-        <v>0.0422720198615419</v>
+        <v>0.0428986049295219</v>
       </c>
       <c r="AE11" s="0" t="n">
-        <v>0.460179694230241</v>
+        <v>0.45742994302093</v>
       </c>
       <c r="AF11" s="0" t="n">
-        <v>0.478282785908217</v>
+        <v>0.480405952049548</v>
       </c>
       <c r="AG11" s="0" t="n">
         <v>0.0192655</v>
@@ -18192,27 +18192,27 @@
       </c>
       <c r="O12" s="52" t="n">
         <f aca="false">(L12/$F$2)^(1/$F$3)</f>
-        <v>0.834733101379665</v>
+        <v>0.849840270350813</v>
       </c>
       <c r="P12" s="53" t="n">
         <f aca="false">(M12/$G$2)^(1/$G$3)</f>
-        <v>9.0969758260895</v>
+        <v>9.04547917530741</v>
       </c>
       <c r="Q12" s="54" t="n">
         <f aca="false">(N12/$H$2)^(1/$H$3)</f>
-        <v>9.44312620523821</v>
+        <v>9.50401713481305</v>
       </c>
       <c r="R12" s="55" t="n">
         <f aca="false">O12*$K12/$I12</f>
-        <v>3.30538138982156</v>
+        <v>3.36520285261917</v>
       </c>
       <c r="S12" s="53" t="n">
         <f aca="false">P12*$K12/$I12</f>
-        <v>36.0222621452464</v>
+        <v>35.8183453832875</v>
       </c>
       <c r="T12" s="54" t="n">
         <f aca="false">Q12*$K12/$I12</f>
-        <v>37.3929505957544</v>
+        <v>37.6340668820176</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>1.908</v>
@@ -18271,27 +18271,27 @@
       </c>
       <c r="O13" s="24" t="n">
         <f aca="false">(L13/$F$2)^(1/$F$3)</f>
-        <v>0.281072719696053</v>
+        <v>0.284773819429059</v>
       </c>
       <c r="P13" s="47" t="n">
         <f aca="false">(M13/$G$2)^(1/$G$3)</f>
-        <v>0.0146513735585112</v>
+        <v>0.015467886910512</v>
       </c>
       <c r="Q13" s="26" t="n">
         <f aca="false">(N13/$H$2)^(1/$H$3)</f>
-        <v>0.00989103138244456</v>
+        <v>0.0100485241929928</v>
       </c>
       <c r="R13" s="25" t="n">
         <f aca="false">O13*$K13/$I13</f>
-        <v>1.13734770342543</v>
+        <v>1.15232403156583</v>
       </c>
       <c r="S13" s="47" t="n">
         <f aca="false">P13*$K13/$I13</f>
-        <v>0.0592861024962534</v>
+        <v>0.0625900858451834</v>
       </c>
       <c r="T13" s="26" t="n">
         <f aca="false">Q13*$K13/$I13</f>
-        <v>0.0400235990155761</v>
+        <v>0.04066088635736</v>
       </c>
       <c r="U13" s="27" t="n">
         <v>94.9485</v>
@@ -18299,15 +18299,15 @@
       <c r="V13" s="27"/>
       <c r="W13" s="56" t="n">
         <f aca="false">AVERAGE(R13:R14)/100</f>
-        <v>0.0110138786782069</v>
+        <v>0.0111578413416647</v>
       </c>
       <c r="X13" s="57" t="n">
         <f aca="false">AVERAGE(S13:S14)/100</f>
-        <v>0.000572728331612156</v>
+        <v>0.000604780119741901</v>
       </c>
       <c r="Y13" s="57" t="n">
         <f aca="false">AVERAGE(T13:T14)/100</f>
-        <v>0.000385303064517594</v>
+        <v>0.000391452679899662</v>
       </c>
       <c r="Z13" s="29" t="n">
         <f aca="false">AVERAGE(U13:V14)/100</f>
@@ -18315,19 +18315,19 @@
       </c>
       <c r="AA13" s="2" t="n">
         <f aca="false">SUM(W13:Z13)</f>
-        <v>0.980524910074337</v>
+        <v>0.980707074141306</v>
       </c>
       <c r="AD13" s="0" t="n">
-        <v>0.0110138786782069</v>
+        <v>0.0111578413416647</v>
       </c>
       <c r="AE13" s="0" t="n">
-        <v>0.000572728331612156</v>
+        <v>0.000604780119741901</v>
       </c>
       <c r="AF13" s="0" t="n">
-        <v>0.000385303064517594</v>
+        <v>0.000391452679899662</v>
       </c>
       <c r="AG13" s="0" t="n">
-        <v>0.988028089925663</v>
+        <v>0.987845925858694</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18377,27 +18377,27 @@
       </c>
       <c r="O14" s="24" t="n">
         <f aca="false">(L14/$F$2)^(1/$F$3)</f>
-        <v>0.268901196962656</v>
+        <v>0.272388240506614</v>
       </c>
       <c r="P14" s="47" t="n">
         <f aca="false">(M14/$G$2)^(1/$G$3)</f>
-        <v>0.0139468480340133</v>
+        <v>0.014730859469837</v>
       </c>
       <c r="Q14" s="26" t="n">
         <f aca="false">(N14/$H$2)^(1/$H$3)</f>
-        <v>0.00934769601066005</v>
+        <v>0.00949727012884177</v>
       </c>
       <c r="R14" s="25" t="n">
         <f aca="false">O14*$K14/$I14</f>
-        <v>1.06542803221594</v>
+        <v>1.07924423676711</v>
       </c>
       <c r="S14" s="47" t="n">
         <f aca="false">P14*$K14/$I14</f>
-        <v>0.0552595638261777</v>
+        <v>0.0583659381031968</v>
       </c>
       <c r="T14" s="26" t="n">
         <f aca="false">Q14*$K14/$I14</f>
-        <v>0.0370370138879427</v>
+        <v>0.0376296496225724</v>
       </c>
       <c r="U14" s="27" t="n">
         <v>99.0665</v>
@@ -18456,27 +18456,27 @@
       </c>
       <c r="O15" s="52" t="n">
         <f aca="false">(L15/$F$2)^(1/$F$3)</f>
-        <v>8.81132881440553</v>
+        <v>9.06558265401841</v>
       </c>
       <c r="P15" s="53" t="n">
         <f aca="false">(M15/$G$2)^(1/$G$3)</f>
-        <v>4.88225346109191</v>
+        <v>4.88284116674251</v>
       </c>
       <c r="Q15" s="54" t="n">
         <f aca="false">(N15/$H$2)^(1/$H$3)</f>
-        <v>5.05154844580341</v>
+        <v>5.08846694730775</v>
       </c>
       <c r="R15" s="55" t="n">
         <f aca="false">O15*$K15/$I15</f>
-        <v>37.0615279316118</v>
+        <v>38.1309507141468</v>
       </c>
       <c r="S15" s="53" t="n">
         <f aca="false">P15*$K15/$I15</f>
-        <v>20.535355884307</v>
+        <v>20.5378278462374</v>
       </c>
       <c r="T15" s="54" t="n">
         <f aca="false">Q15*$K15/$I15</f>
-        <v>21.2474313200017</v>
+        <v>21.4027150579617</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>5.1862</v>
@@ -18484,15 +18484,15 @@
       <c r="V15" s="2"/>
       <c r="W15" s="51" t="n">
         <f aca="false">AVERAGE(R15:R16)/100</f>
-        <v>0.368438652501512</v>
+        <v>0.379060398775977</v>
       </c>
       <c r="X15" s="0" t="n">
         <f aca="false">AVERAGE(S15:S16)/100</f>
-        <v>0.204461266524891</v>
+        <v>0.204493869050424</v>
       </c>
       <c r="Y15" s="1" t="n">
         <f aca="false">AVERAGE(T15:T16)/100</f>
-        <v>0.210860587483743</v>
+        <v>0.212403790522799</v>
       </c>
       <c r="Z15" s="33" t="n">
         <f aca="false">AVERAGE(U15:V16)/100</f>
@@ -18500,16 +18500,16 @@
       </c>
       <c r="AA15" s="2" t="n">
         <f aca="false">SUM(W15:Z15)</f>
-        <v>0.831605506510146</v>
+        <v>0.8438030583492</v>
       </c>
       <c r="AD15" s="0" t="n">
-        <v>0.447599365186993</v>
+        <v>0.453446321964613</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>0.248390695385833</v>
+        <v>0.244623266066972</v>
       </c>
       <c r="AF15" s="0" t="n">
-        <v>0.256164939427175</v>
+        <v>0.254085411968415</v>
       </c>
       <c r="AG15" s="0" t="n">
         <v>0.047845</v>
@@ -18562,27 +18562,27 @@
       </c>
       <c r="O16" s="52" t="n">
         <f aca="false">(L16/$F$2)^(1/$F$3)</f>
-        <v>8.7104651586848</v>
+        <v>8.96134839631268</v>
       </c>
       <c r="P16" s="53" t="n">
         <f aca="false">(M16/$G$2)^(1/$G$3)</f>
-        <v>4.84128938535535</v>
+        <v>4.8422522122882</v>
       </c>
       <c r="Q16" s="54" t="n">
         <f aca="false">(N16/$H$2)^(1/$H$3)</f>
-        <v>4.97632124316303</v>
+        <v>5.01279266465912</v>
       </c>
       <c r="R16" s="55" t="n">
         <f aca="false">O16*$K16/$I16</f>
-        <v>36.6262025686906</v>
+        <v>37.6811290410485</v>
       </c>
       <c r="S16" s="53" t="n">
         <f aca="false">P16*$K16/$I16</f>
-        <v>20.3568974206712</v>
+        <v>20.3609459638475</v>
       </c>
       <c r="T16" s="54" t="n">
         <f aca="false">Q16*$K16/$I16</f>
-        <v>20.9246861767469</v>
+        <v>21.0780430465981</v>
       </c>
       <c r="U16" s="2" t="n">
         <v>4.5975</v>
@@ -18643,27 +18643,27 @@
       </c>
       <c r="O17" s="24" t="n">
         <f aca="false">(L17/$F$2)^(1/$F$3)</f>
-        <v>0.405837843251855</v>
+        <v>0.411856007050728</v>
       </c>
       <c r="P17" s="47" t="n">
         <f aca="false">(M17/$G$2)^(1/$G$3)</f>
-        <v>0.0085397963045257</v>
+        <v>0.00906116371848025</v>
       </c>
       <c r="Q17" s="26" t="n">
         <f aca="false">(N17/$H$2)^(1/$H$3)</f>
-        <v>0.00593544519810214</v>
+        <v>0.00603416072770653</v>
       </c>
       <c r="R17" s="25" t="n">
         <f aca="false">O17*$K17/$I17</f>
-        <v>1.57385895309866</v>
+        <v>1.59719768587965</v>
       </c>
       <c r="S17" s="47" t="n">
         <f aca="false">P17*$K17/$I17</f>
-        <v>0.0331177466443802</v>
+        <v>0.0351396349082527</v>
       </c>
       <c r="T17" s="26" t="n">
         <f aca="false">Q17*$K17/$I17</f>
-        <v>0.0230179460121522</v>
+        <v>0.0234007696513497</v>
       </c>
       <c r="U17" s="27" t="n">
         <v>97.0684</v>
@@ -18671,15 +18671,15 @@
       <c r="V17" s="27"/>
       <c r="W17" s="56" t="n">
         <f aca="false">AVERAGE(R17:R18)/100</f>
-        <v>0.0128676895854389</v>
+        <v>0.0130570241673517</v>
       </c>
       <c r="X17" s="57" t="n">
         <f aca="false">AVERAGE(S17:S18)/100</f>
-        <v>0.000271929315948812</v>
+        <v>0.000288588254156595</v>
       </c>
       <c r="Y17" s="57" t="n">
         <f aca="false">AVERAGE(T17:T18)/100</f>
-        <v>0.000187847542885098</v>
+        <v>0.000190978822347075</v>
       </c>
       <c r="Z17" s="29" t="n">
         <f aca="false">AVERAGE(U17:V18)/100</f>
@@ -18687,19 +18687,19 @@
       </c>
       <c r="AA17" s="2" t="n">
         <f aca="false">SUM(W17:Z17)</f>
-        <v>1.00218346644427</v>
+        <v>1.00239259124386</v>
       </c>
       <c r="AD17" s="0" t="n">
-        <v>0.0128676895854389</v>
+        <v>0.0130570241673518</v>
       </c>
       <c r="AE17" s="0" t="n">
-        <v>0.000271929315948812</v>
+        <v>0.000288588254156595</v>
       </c>
       <c r="AF17" s="0" t="n">
-        <v>0.000187847542885098</v>
+        <v>0.000190978822347075</v>
       </c>
       <c r="AG17" s="0" t="n">
-        <v>0.986672533555727</v>
+        <v>0.986463408756145</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18749,27 +18749,27 @@
       </c>
       <c r="O18" s="24" t="n">
         <f aca="false">(L18/$F$2)^(1/$F$3)</f>
-        <v>0.3801302348416</v>
+        <v>0.385654610209316</v>
       </c>
       <c r="P18" s="47" t="n">
         <f aca="false">(M18/$G$2)^(1/$G$3)</f>
-        <v>0.00808725043565346</v>
+        <v>0.00858534269926474</v>
       </c>
       <c r="Q18" s="26" t="n">
         <f aca="false">(N18/$H$2)^(1/$H$3)</f>
-        <v>0.00553326527250548</v>
+        <v>0.00562583094899714</v>
       </c>
       <c r="R18" s="25" t="n">
         <f aca="false">O18*$K18/$I18</f>
-        <v>0.99967896398913</v>
+        <v>1.0142071475907</v>
       </c>
       <c r="S18" s="47" t="n">
         <f aca="false">P18*$K18/$I18</f>
-        <v>0.0212681165453823</v>
+        <v>0.0225780159230664</v>
       </c>
       <c r="T18" s="26" t="n">
         <f aca="false">Q18*$K18/$I18</f>
-        <v>0.0145515625648675</v>
+        <v>0.0147949948180654</v>
       </c>
       <c r="U18" s="27" t="n">
         <v>100.5119</v>
@@ -18828,27 +18828,27 @@
       </c>
       <c r="O19" s="52" t="n">
         <f aca="false">(L19/$F$2)^(1/$F$3)</f>
-        <v>14.1351316479187</v>
+        <v>14.5736923061734</v>
       </c>
       <c r="P19" s="53" t="n">
         <f aca="false">(M19/$G$2)^(1/$G$3)</f>
-        <v>3.01504166268551</v>
+        <v>3.02897409890509</v>
       </c>
       <c r="Q19" s="54" t="n">
         <f aca="false">(N19/$H$2)^(1/$H$3)</f>
-        <v>3.08390342929745</v>
+        <v>3.10853587434022</v>
       </c>
       <c r="R19" s="55" t="n">
         <f aca="false">O19*$K19/$I19</f>
-        <v>50.9219340378523</v>
+        <v>52.5018526029922</v>
       </c>
       <c r="S19" s="53" t="n">
         <f aca="false">P19*$K19/$I19</f>
-        <v>10.8617136714998</v>
+        <v>10.9119053935037</v>
       </c>
       <c r="T19" s="54" t="n">
         <f aca="false">Q19*$K19/$I19</f>
-        <v>11.1097887814094</v>
+        <v>11.1985273777594</v>
       </c>
       <c r="U19" s="2" t="n">
         <v>6.2745</v>
@@ -18856,15 +18856,15 @@
       <c r="V19" s="2"/>
       <c r="W19" s="51" t="n">
         <f aca="false">AVERAGE(R19:R20)/100</f>
-        <v>0.525398543509081</v>
+        <v>0.541729384334884</v>
       </c>
       <c r="X19" s="0" t="n">
         <f aca="false">AVERAGE(S19:S20)/100</f>
-        <v>0.112039110512796</v>
+        <v>0.112544238902586</v>
       </c>
       <c r="Y19" s="1" t="n">
         <f aca="false">AVERAGE(T19:T20)/100</f>
-        <v>0.114582921844376</v>
+        <v>0.115496269472424</v>
       </c>
       <c r="Z19" s="33" t="n">
         <f aca="false">AVERAGE(U19:V20)/100</f>
@@ -18872,16 +18872,16 @@
       </c>
       <c r="AA19" s="2" t="n">
         <f aca="false">SUM(W19:Z19)</f>
-        <v>0.816469575866254</v>
+        <v>0.834218892709893</v>
       </c>
       <c r="AD19" s="0" t="n">
-        <v>0.653621920134648</v>
+        <v>0.658398661786699</v>
       </c>
       <c r="AE19" s="0" t="n">
-        <v>0.139382226023027</v>
+        <v>0.136782272529376</v>
       </c>
       <c r="AF19" s="0" t="n">
-        <v>0.142546853842325</v>
+        <v>0.140370065683925</v>
       </c>
       <c r="AG19" s="0" t="n">
         <v>0.064449</v>
@@ -18934,27 +18934,27 @@
       </c>
       <c r="O20" s="52" t="n">
         <f aca="false">(L20/$F$2)^(1/$F$3)</f>
-        <v>14.4760293619802</v>
+        <v>14.9267531753751</v>
       </c>
       <c r="P20" s="53" t="n">
         <f aca="false">(M20/$G$2)^(1/$G$3)</f>
-        <v>3.08620148633689</v>
+        <v>3.09978908005805</v>
       </c>
       <c r="Q20" s="54" t="n">
         <f aca="false">(N20/$H$2)^(1/$H$3)</f>
-        <v>3.15588150834381</v>
+        <v>3.18098864944027</v>
       </c>
       <c r="R20" s="55" t="n">
         <f aca="false">O20*$K20/$I20</f>
-        <v>54.1577746639639</v>
+        <v>55.8440242639845</v>
       </c>
       <c r="S20" s="53" t="n">
         <f aca="false">P20*$K20/$I20</f>
-        <v>11.5461084310594</v>
+        <v>11.5969423870135</v>
       </c>
       <c r="T20" s="54" t="n">
         <f aca="false">Q20*$K20/$I20</f>
-        <v>11.8067955874659</v>
+        <v>11.9007265167254</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>6.6153</v>
@@ -19013,27 +19013,27 @@
       </c>
       <c r="O21" s="24" t="n">
         <f aca="false">(L21/$F$2)^(1/$F$3)</f>
-        <v>0.240403718078178</v>
+        <v>0.243399577379964</v>
       </c>
       <c r="P21" s="47" t="n">
         <f aca="false">(M21/$G$2)^(1/$G$3)</f>
-        <v>0.0169670201049863</v>
+        <v>0.0178881149070863</v>
       </c>
       <c r="Q21" s="26" t="n">
         <f aca="false">(N21/$H$2)^(1/$H$3)</f>
-        <v>0.010785478686861</v>
+        <v>0.0109559182845499</v>
       </c>
       <c r="R21" s="25" t="n">
         <f aca="false">O21*$K21/$I21</f>
-        <v>0.965062799030945</v>
+        <v>0.977089203557453</v>
       </c>
       <c r="S21" s="47" t="n">
         <f aca="false">P21*$K21/$I21</f>
-        <v>0.0681114254165053</v>
+        <v>0.0718090151833926</v>
       </c>
       <c r="T21" s="26" t="n">
         <f aca="false">Q21*$K21/$I21</f>
-        <v>0.0432966026217858</v>
+        <v>0.0439808054973748</v>
       </c>
       <c r="U21" s="27" t="n">
         <v>99.6909</v>
@@ -19041,15 +19041,15 @@
       <c r="V21" s="27"/>
       <c r="W21" s="56" t="n">
         <f aca="false">AVERAGE(R21:R22)/100</f>
-        <v>0.00937947850914304</v>
+        <v>0.00949522559982443</v>
       </c>
       <c r="X21" s="57" t="n">
         <f aca="false">AVERAGE(S21:S22)/100</f>
-        <v>0.000650870516148259</v>
+        <v>0.000686480517819178</v>
       </c>
       <c r="Y21" s="57" t="n">
         <f aca="false">AVERAGE(T21:T22)/100</f>
-        <v>0.00041998545422514</v>
+        <v>0.000426639108022695</v>
       </c>
       <c r="Z21" s="29" t="n">
         <f aca="false">AVERAGE(U21:V22)/100</f>
@@ -19057,19 +19057,19 @@
       </c>
       <c r="AA21" s="2" t="n">
         <f aca="false">SUM(W21:Z21)</f>
-        <v>1.00693683447952</v>
+        <v>1.00709484522567</v>
       </c>
       <c r="AD21" s="0" t="n">
-        <v>0.00937947850914304</v>
+        <v>0.00949522559982443</v>
       </c>
       <c r="AE21" s="0" t="n">
-        <v>0.00065087051614826</v>
+        <v>0.000686480517819178</v>
       </c>
       <c r="AF21" s="0" t="n">
-        <v>0.00041998545422514</v>
+        <v>0.000426639108022695</v>
       </c>
       <c r="AG21" s="0" t="n">
-        <v>0.989549665520484</v>
+        <v>0.989391654774334</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19119,27 +19119,27 @@
       </c>
       <c r="O22" s="24" t="n">
         <f aca="false">(L22/$F$2)^(1/$F$3)</f>
-        <v>0.227460387504798</v>
+        <v>0.230238114328377</v>
       </c>
       <c r="P22" s="47" t="n">
         <f aca="false">(M22/$G$2)^(1/$G$3)</f>
-        <v>0.0154987821603758</v>
+        <v>0.0163539530179725</v>
       </c>
       <c r="Q22" s="26" t="n">
         <f aca="false">(N22/$H$2)^(1/$H$3)</f>
-        <v>0.0101640474278625</v>
+        <v>0.0103255034782071</v>
       </c>
       <c r="R22" s="25" t="n">
         <f aca="false">O22*$K22/$I22</f>
-        <v>0.910832902797663</v>
+        <v>0.921955916407434</v>
       </c>
       <c r="S22" s="47" t="n">
         <f aca="false">P22*$K22/$I22</f>
-        <v>0.0620626778131466</v>
+        <v>0.065487088380443</v>
       </c>
       <c r="T22" s="26" t="n">
         <f aca="false">Q22*$K22/$I22</f>
-        <v>0.0407004882232422</v>
+        <v>0.0413470161071643</v>
       </c>
       <c r="U22" s="27" t="n">
         <v>99.6064</v>
@@ -19196,27 +19196,27 @@
       </c>
       <c r="O23" s="52" t="n">
         <f aca="false">(L23/$F$2)^(1/$F$3)</f>
-        <v>6.9965673935464</v>
+        <v>7.19105568162104</v>
       </c>
       <c r="P23" s="53" t="n">
         <f aca="false">(M23/$G$2)^(1/$G$3)</f>
-        <v>5.37552043114375</v>
+        <v>5.37134943434382</v>
       </c>
       <c r="Q23" s="54" t="n">
         <f aca="false">(N23/$H$2)^(1/$H$3)</f>
-        <v>5.52789278657069</v>
+        <v>5.56760741201139</v>
       </c>
       <c r="R23" s="55" t="n">
         <f aca="false">O23*$K23/$I23</f>
-        <v>29.2874377929641</v>
+        <v>30.1015603930981</v>
       </c>
       <c r="S23" s="53" t="n">
         <f aca="false">P23*$K23/$I23</f>
-        <v>22.5017799981671</v>
+        <v>22.484320320808</v>
       </c>
       <c r="T23" s="54" t="n">
         <f aca="false">Q23*$K23/$I23</f>
-        <v>23.1396064679085</v>
+        <v>23.305850792681</v>
       </c>
       <c r="U23" s="2" t="n">
         <v>4.3433</v>
@@ -19224,15 +19224,15 @@
       <c r="V23" s="2"/>
       <c r="W23" s="51" t="n">
         <f aca="false">AVERAGE(R23:R24)/100</f>
-        <v>0.306001613350373</v>
+        <v>0.314627239883138</v>
       </c>
       <c r="X23" s="0" t="n">
         <f aca="false">AVERAGE(S23:S24)/100</f>
-        <v>0.234057965105495</v>
+        <v>0.233701397841368</v>
       </c>
       <c r="Y23" s="1" t="n">
         <f aca="false">AVERAGE(T23:T24)/100</f>
-        <v>0.243803902579953</v>
+        <v>0.245523894212824</v>
       </c>
       <c r="Z23" s="33" t="n">
         <f aca="false">AVERAGE(U23:V24)/100</f>
@@ -19240,16 +19240,16 @@
       </c>
       <c r="AA23" s="2" t="n">
         <f aca="false">SUM(W23:Z23)</f>
-        <v>0.826491981035821</v>
+        <v>0.83648103193733</v>
       </c>
       <c r="AD23" s="0" t="n">
-        <v>0.37373500700472</v>
+        <v>0.379434643677069</v>
       </c>
       <c r="AE23" s="0" t="n">
-        <v>0.285866647141016</v>
+        <v>0.281839571963663</v>
       </c>
       <c r="AF23" s="0" t="n">
-        <v>0.297769845854264</v>
+        <v>0.296097284359268</v>
       </c>
       <c r="AG23" s="0" t="n">
         <v>0.0426285</v>
@@ -19302,27 +19302,27 @@
       </c>
       <c r="O24" s="58" t="n">
         <f aca="false">(L24/$F$2)^(1/$F$3)</f>
-        <v>8.23779970870867</v>
+        <v>8.47296045517424</v>
       </c>
       <c r="P24" s="59" t="n">
         <f aca="false">(M24/$G$2)^(1/$G$3)</f>
-        <v>6.27518857697214</v>
+        <v>6.26128708804196</v>
       </c>
       <c r="Q24" s="60" t="n">
         <f aca="false">(N24/$H$2)^(1/$H$3)</f>
-        <v>6.6136954061915</v>
+        <v>6.65957975258961</v>
       </c>
       <c r="R24" s="55" t="n">
         <f aca="false">O24*$K24/$I24</f>
-        <v>31.9128848771106</v>
+        <v>32.8238875835295</v>
       </c>
       <c r="S24" s="53" t="n">
         <f aca="false">P24*$K24/$I24</f>
-        <v>24.309813022932</v>
+        <v>24.2559592474656</v>
       </c>
       <c r="T24" s="54" t="n">
         <f aca="false">Q24*$K24/$I24</f>
-        <v>25.621174048082</v>
+        <v>25.7989280498838</v>
       </c>
       <c r="U24" s="42" t="n">
         <v>4.1824</v>
@@ -19377,27 +19377,27 @@
       </c>
       <c r="P25" s="1" t="n">
         <f aca="false">(M25/$G$2)^(1/$G$3)</f>
-        <v>0.0371869331792908</v>
+        <v>0.0389201777921435</v>
       </c>
       <c r="Q25" s="1" t="n">
         <f aca="false">(N25/$H$2)^(1/$H$3)</f>
-        <v>0.023803237734811</v>
+        <v>0.0241532684544262</v>
       </c>
       <c r="S25" s="1" t="n">
         <f aca="false">P25*$K25/$I25</f>
-        <v>0.0942797430779975</v>
+        <v>0.0986740246930806</v>
       </c>
       <c r="T25" s="1" t="n">
         <f aca="false">Q25*$K25/$I25</f>
-        <v>0.0603481638897892</v>
+        <v>0.0612355940566067</v>
       </c>
       <c r="X25" s="1" t="n">
         <f aca="false">AVERAGE(S25:S26)/100</f>
-        <v>0.000935095174796336</v>
+        <v>0.000978839379828612</v>
       </c>
       <c r="Y25" s="1" t="n">
         <f aca="false">AVERAGE(T25:T26)/100</f>
-        <v>0.000603769690895068</v>
+        <v>0.000612655779384382</v>
       </c>
       <c r="Z25" s="1" t="e">
         <f aca="false">AVERAGE(U25:V26)/100</f>
@@ -19461,19 +19461,19 @@
       </c>
       <c r="P26" s="1" t="n">
         <f aca="false">(M26/$G$2)^(1/$G$3)</f>
-        <v>0.0358910151667953</v>
+        <v>0.0375762723430151</v>
       </c>
       <c r="Q26" s="1" t="n">
         <f aca="false">(N26/$H$2)^(1/$H$3)</f>
-        <v>0.0233776268634033</v>
+        <v>0.023721983361325</v>
       </c>
       <c r="S26" s="1" t="n">
         <f aca="false">P26*$K26/$I26</f>
-        <v>0.0927392918812698</v>
+        <v>0.0970938512726418</v>
       </c>
       <c r="T26" s="1" t="n">
         <f aca="false">Q26*$K26/$I26</f>
-        <v>0.0604057742892244</v>
+        <v>0.0612955618202697</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19517,30 +19517,30 @@
       </c>
       <c r="P27" s="1" t="n">
         <f aca="false">(M27/$G$2)^(1/$G$3)</f>
-        <v>16.7099743539892</v>
+        <v>16.5215321399056</v>
       </c>
       <c r="Q27" s="1" t="n">
         <f aca="false">(N27/$H$2)^(1/$H$3)</f>
-        <v>17.4227089320943</v>
+        <v>17.5203933050834</v>
       </c>
       <c r="S27" s="1" t="n">
         <f aca="false">P27*$K27/$I27</f>
-        <v>45.1609816547708</v>
+        <v>44.6516909046517</v>
       </c>
       <c r="T27" s="1" t="n">
         <f aca="false">Q27*$K27/$I27</f>
-        <v>47.087243929305</v>
+        <v>47.3512492522974</v>
       </c>
       <c r="U27" s="1" t="n">
         <v>1.6475</v>
       </c>
       <c r="X27" s="1" t="n">
         <f aca="false">AVERAGE(S27:S28)/100</f>
-        <v>0.453538841373625</v>
+        <v>0.448337149454742</v>
       </c>
       <c r="Y27" s="1" t="n">
         <f aca="false">AVERAGE(T27:T28)/100</f>
-        <v>0.473581845113444</v>
+        <v>0.476222557679019</v>
       </c>
       <c r="Z27" s="1" t="n">
         <f aca="false">AVERAGE(U27:V28)/100</f>
@@ -19548,19 +19548,19 @@
       </c>
       <c r="AA27" s="1" t="n">
         <f aca="false">SUM(W27:Z27)</f>
-        <v>0.943600186487069</v>
+        <v>0.941039207133761</v>
       </c>
       <c r="AE27" s="1" t="n">
         <f aca="false">IFERROR(X27/$AA27,"")</f>
-        <v>0.480647257035955</v>
+        <v>0.476427704665247</v>
       </c>
       <c r="AF27" s="1" t="n">
         <f aca="false">IFERROR(Y27/$AA27,"")</f>
-        <v>0.501888248747112</v>
+        <v>0.50606027258897</v>
       </c>
       <c r="AG27" s="1" t="n">
         <f aca="false">IFERROR(Z27/$AA27,"")</f>
-        <v>0.0174644942169327</v>
+        <v>0.017512022745783</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19604,19 +19604,19 @@
       </c>
       <c r="P28" s="1" t="n">
         <f aca="false">(M28/$G$2)^(1/$G$3)</f>
-        <v>17.4180329077589</v>
+        <v>17.214949312953</v>
       </c>
       <c r="Q28" s="1" t="n">
         <f aca="false">(N28/$H$2)^(1/$H$3)</f>
-        <v>18.2143621934652</v>
+        <v>18.3153737161464</v>
       </c>
       <c r="S28" s="1" t="n">
         <f aca="false">P28*$K28/$I28</f>
-        <v>45.5467866199543</v>
+        <v>45.0157389862967</v>
       </c>
       <c r="T28" s="1" t="n">
         <f aca="false">Q28*$K28/$I28</f>
-        <v>47.6291250933837</v>
+        <v>47.8932622835064</v>
       </c>
       <c r="U28" s="1" t="n">
         <v>1.6484</v>

--- a/Sistemas ternarios_MF_filled.xlsx
+++ b/Sistemas ternarios_MF_filled.xlsx
@@ -1520,16 +1520,16 @@
         <v>2</v>
       </c>
       <c r="AD7" s="31" t="n">
-        <v>0.0012452928365592</v>
+        <v>0.00133391210031924</v>
       </c>
       <c r="AE7" s="31" t="n">
-        <v>0.000640343911906584</v>
+        <v>0.000685912957483989</v>
       </c>
       <c r="AF7" s="31" t="n">
-        <v>0.000748305407068313</v>
+        <v>0.000801557358974884</v>
       </c>
       <c r="AG7" s="31" t="n">
-        <v>0.997366057844466</v>
+        <v>0.997178617583222</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1729,16 +1729,16 @@
         <v>3</v>
       </c>
       <c r="AD9" s="31" t="n">
-        <v>0.022429496434778</v>
+        <v>0.0240256555085348</v>
       </c>
       <c r="AE9" s="31" t="n">
-        <v>2.41651253614074E-005</v>
+        <v>2.58847976788953E-005</v>
       </c>
       <c r="AF9" s="31" t="n">
-        <v>4.63156550236011E-005</v>
+        <v>4.96116341927225E-005</v>
       </c>
       <c r="AG9" s="31" t="n">
-        <v>0.977500022784837</v>
+        <v>0.975898848059594</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2351,16 +2351,16 @@
       </c>
       <c r="AB15" s="2"/>
       <c r="AD15" s="0" t="n">
-        <v>0.0132888185355668</v>
+        <v>0.0142344959539936</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>0.000143558200184956</v>
+        <v>0.000153774288829822</v>
       </c>
       <c r="AF15" s="0" t="n">
-        <v>0.00027499423116433</v>
+        <v>0.000294563753760617</v>
       </c>
       <c r="AG15" s="0" t="n">
-        <v>0.986292629033084</v>
+        <v>0.985317166003416</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2729,16 +2729,16 @@
       </c>
       <c r="AB19" s="2"/>
       <c r="AD19" s="0" t="n">
-        <v>0.00783372736021942</v>
+        <v>0.0083912019804683</v>
       </c>
       <c r="AE19" s="0" t="n">
-        <v>0.000722277624523893</v>
+        <v>0.000773677351107489</v>
       </c>
       <c r="AF19" s="0" t="n">
-        <v>0.000883124523321954</v>
+        <v>0.000945970661007499</v>
       </c>
       <c r="AG19" s="0" t="n">
-        <v>0.990560870491935</v>
+        <v>0.989889150007417</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2920,16 +2920,16 @@
       </c>
       <c r="AB21" s="2"/>
       <c r="AD21" s="0" t="n">
-        <v>0.0211783260595737</v>
+        <v>0.0226854476039769</v>
       </c>
       <c r="AE21" s="0" t="n">
-        <v>0.000425202945023175</v>
+        <v>0.000455461829383794</v>
       </c>
       <c r="AF21" s="0" t="n">
-        <v>0.000534700459504692</v>
+        <v>0.000572751558541273</v>
       </c>
       <c r="AG21" s="0" t="n">
-        <v>0.977861770535899</v>
+        <v>0.976286339008098</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3772,16 +3772,16 @@
         <v>0.962892579742591</v>
       </c>
       <c r="AD5" s="0" t="n">
-        <v>0.0249246213698665</v>
+        <v>0.0269449351828853</v>
       </c>
       <c r="AE5" s="0" t="n">
-        <v>5.65969280179736E-005</v>
+        <v>6.11845024389588E-005</v>
       </c>
       <c r="AF5" s="0" t="n">
-        <v>6.58614447060957E-005</v>
+        <v>7.11999726022893E-005</v>
       </c>
       <c r="AG5" s="0" t="n">
-        <v>0.974952920257409</v>
+        <v>0.972922680342074</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4329,16 +4329,16 @@
         <v>0.983901670260377</v>
       </c>
       <c r="AD11" s="0" t="n">
-        <v>0.00127757433988938</v>
+        <v>0.00138113062055398</v>
       </c>
       <c r="AE11" s="0" t="n">
-        <v>0.000482642843348461</v>
+        <v>0.00052176440065125</v>
       </c>
       <c r="AF11" s="0" t="n">
-        <v>0.000242453077139349</v>
+        <v>0.000262105584332325</v>
       </c>
       <c r="AG11" s="0" t="n">
-        <v>0.997997329739623</v>
+        <v>0.997834999394462</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4701,16 +4701,16 @@
         <v>1.00786714430956</v>
       </c>
       <c r="AD15" s="0" t="n">
-        <v>0.0135775328502213</v>
+        <v>0.0146780862651342</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>0.000186181812273992</v>
+        <v>0.000201273142308187</v>
       </c>
       <c r="AF15" s="0" t="n">
-        <v>0.000166929647062546</v>
+        <v>0.000180460455284594</v>
       </c>
       <c r="AG15" s="0" t="n">
-        <v>0.986069355690442</v>
+        <v>0.984940180137273</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5073,16 +5073,16 @@
         <v>0.998103391430224</v>
       </c>
       <c r="AD19" s="0" t="n">
-        <v>0.00835405281883261</v>
+        <v>0.00903120686880268</v>
       </c>
       <c r="AE19" s="0" t="n">
-        <v>0.000813964789591377</v>
+        <v>0.000879942293655311</v>
       </c>
       <c r="AF19" s="0" t="n">
-        <v>0.00074287382179994</v>
+        <v>0.000803088908771208</v>
       </c>
       <c r="AG19" s="0" t="n">
-        <v>0.990089108569776</v>
+        <v>0.989285761928771</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5445,16 +5445,16 @@
         <v>0.998622949499804</v>
       </c>
       <c r="AD23" s="0" t="n">
-        <v>0.0193409846827522</v>
+        <v>0.0209087059304334</v>
       </c>
       <c r="AE23" s="0" t="n">
-        <v>0.000279756625784368</v>
+        <v>0.000302432844891912</v>
       </c>
       <c r="AF23" s="0" t="n">
-        <v>0.000292708191267029</v>
+        <v>0.000316434224783248</v>
       </c>
       <c r="AG23" s="0" t="n">
-        <v>0.980086550500196</v>
+        <v>0.978472426999892</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6101,16 +6101,16 @@
         <v>0.996793022322558</v>
       </c>
       <c r="AD5" s="0" t="n">
-        <v>0.0217205401206323</v>
+        <v>0.0235153495087636</v>
       </c>
       <c r="AE5" s="0" t="n">
-        <v>2.11310192269882E-005</v>
+        <v>2.28771153866024E-005</v>
       </c>
       <c r="AF5" s="0" t="n">
-        <v>1.63511826991334E-005</v>
+        <v>1.77023119092022E-005</v>
       </c>
       <c r="AG5" s="0" t="n">
-        <v>0.978241977677442</v>
+        <v>0.976444071063941</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6654,16 +6654,16 @@
         <v>0.846458155919536</v>
       </c>
       <c r="AD11" s="0" t="n">
-        <v>0.000476326035390113</v>
+        <v>0.000515685758278287</v>
       </c>
       <c r="AE11" s="0" t="n">
-        <v>0.000624690978018088</v>
+        <v>0.000676310377250375</v>
       </c>
       <c r="AF11" s="0" t="n">
-        <v>0.000500138906128114</v>
+        <v>0.000541466331648062</v>
       </c>
       <c r="AG11" s="0" t="n">
-        <v>0.998398844080464</v>
+        <v>0.998266537532823</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7024,16 +7024,16 @@
         <v>1.0018061446917</v>
       </c>
       <c r="AD15" s="0" t="n">
-        <v>0.009994325907786</v>
+        <v>0.010820175995662</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>0.000314170963805408</v>
+        <v>0.000340131505863043</v>
       </c>
       <c r="AF15" s="0" t="n">
-        <v>0.00014879251180822</v>
+        <v>0.000161087519003891</v>
       </c>
       <c r="AG15" s="0" t="n">
-        <v>0.9895427106166</v>
+        <v>0.988678604979471</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8319,16 +8319,16 @@
         <v>0.979275168342005</v>
       </c>
       <c r="AD5" s="0" t="n">
-        <v>0.00752789377984754</v>
+        <v>0.00816941356095746</v>
       </c>
       <c r="AE5" s="0" t="n">
-        <v>5.3731402517012E-006</v>
+        <v>5.83103403433824E-006</v>
       </c>
       <c r="AF5" s="0" t="n">
-        <v>1.19014219052806E-005</v>
+        <v>1.29156494965375E-005</v>
       </c>
       <c r="AG5" s="0" t="n">
-        <v>0.992454831657996</v>
+        <v>0.991811839755512</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8687,16 +8687,16 @@
         <v>0.986814490385097</v>
       </c>
       <c r="AD9" s="0" t="n">
-        <v>0.000830963275791131</v>
+        <v>0.000901777157387466</v>
       </c>
       <c r="AE9" s="0" t="n">
-        <v>0.00119328633472228</v>
+        <v>0.00129497703475605</v>
       </c>
       <c r="AF9" s="0" t="n">
-        <v>0.00149354706525587</v>
+        <v>0.00162082569250554</v>
       </c>
       <c r="AG9" s="0" t="n">
-        <v>0.996482203324231</v>
+        <v>0.996182420115351</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9055,16 +9055,16 @@
         <v>0.998513169671521</v>
       </c>
       <c r="AD13" s="0" t="n">
-        <v>0.0177055813738214</v>
+        <v>0.0192144337858686</v>
       </c>
       <c r="AE13" s="0" t="n">
-        <v>0.00368221093439793</v>
+        <v>0.00399600536637561</v>
       </c>
       <c r="AF13" s="0" t="n">
-        <v>0.00425987736330177</v>
+        <v>0.00462289996611482</v>
       </c>
       <c r="AG13" s="0" t="n">
-        <v>0.974352330328479</v>
+        <v>0.972166660881641</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9423,16 +9423,16 @@
         <v>1.0009793159734</v>
       </c>
       <c r="AD17" s="0" t="n">
-        <v>0.015748546470514</v>
+        <v>0.0170906222728599</v>
       </c>
       <c r="AE17" s="0" t="n">
-        <v>0.000116599609525434</v>
+        <v>0.000126536114764191</v>
       </c>
       <c r="AF17" s="0" t="n">
-        <v>0.000293669893355705</v>
+        <v>0.000318696155842095</v>
       </c>
       <c r="AG17" s="0" t="n">
-        <v>0.983841184026605</v>
+        <v>0.982464145456534</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9791,16 +9791,16 @@
         <v>1.00823753359508</v>
       </c>
       <c r="AD21" s="0" t="n">
-        <v>0.00744754305251486</v>
+        <v>0.00808221542284589</v>
       </c>
       <c r="AE21" s="0" t="n">
-        <v>0.00362206061128188</v>
+        <v>0.00393072909126719</v>
       </c>
       <c r="AF21" s="0" t="n">
-        <v>0.00415842993128495</v>
+        <v>0.0045128072826791</v>
       </c>
       <c r="AG21" s="0" t="n">
-        <v>0.984771966404918</v>
+        <v>0.983474248203208</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10815,16 +10815,16 @@
         <v>0.986784337965768</v>
       </c>
       <c r="AD7" s="0" t="n">
-        <v>0.00163139153517796</v>
+        <v>0.00164237103978913</v>
       </c>
       <c r="AE7" s="0" t="n">
-        <v>0.000258487986468277</v>
+        <v>0.000260227648577686</v>
       </c>
       <c r="AF7" s="0" t="n">
-        <v>0.000607458444121444</v>
+        <v>0.000611546728659218</v>
       </c>
       <c r="AG7" s="0" t="n">
-        <v>0.997502662034232</v>
+        <v>0.997485854582974</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11004,16 +11004,16 @@
         <v>1.84807683984028</v>
       </c>
       <c r="AD9" s="0" t="n">
-        <v>0.0206431586579825</v>
+        <v>0.0207820901473196</v>
       </c>
       <c r="AE9" s="0" t="n">
-        <v>1.74071987726536E-005</v>
+        <v>1.75243517767428E-005</v>
       </c>
       <c r="AF9" s="0" t="n">
-        <v>5.74697532249489E-005</v>
+        <v>5.78565331039233E-005</v>
       </c>
       <c r="AG9" s="0" t="n">
-        <v>0.97928196439002</v>
+        <v>0.9791425289678</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11557,16 +11557,16 @@
         <v>0.988757794253589</v>
       </c>
       <c r="AD15" s="0" t="n">
-        <v>0.0125515292950584</v>
+        <v>0.0126360029304799</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>0.000146268243121633</v>
+        <v>0.000147252649878191</v>
       </c>
       <c r="AF15" s="0" t="n">
-        <v>0.000450496715408967</v>
+        <v>0.000453528624461755</v>
       </c>
       <c r="AG15" s="0" t="n">
-        <v>0.986851705746411</v>
+        <v>0.98676321579518</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11925,16 +11925,16 @@
         <v>1.00616972680853</v>
       </c>
       <c r="AD19" s="0" t="n">
-        <v>0.00712153851695347</v>
+        <v>0.00716946751701228</v>
       </c>
       <c r="AE19" s="0" t="n">
-        <v>0.000210679215893882</v>
+        <v>0.000212097117956327</v>
       </c>
       <c r="AF19" s="0" t="n">
-        <v>0.000536509075681631</v>
+        <v>0.000540119860550474</v>
       </c>
       <c r="AG19" s="0" t="n">
-        <v>0.992131273191471</v>
+        <v>0.992078315504481</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12112,16 +12112,16 @@
         <v>0.993381331115203</v>
       </c>
       <c r="AD21" s="0" t="n">
-        <v>0.0160589950353215</v>
+        <v>0.0161670744302668</v>
       </c>
       <c r="AE21" s="0" t="n">
-        <v>7.12162537083959E-005</v>
+        <v>7.16955495543781E-005</v>
       </c>
       <c r="AF21" s="0" t="n">
-        <v>0.000258119826172836</v>
+        <v>0.00025985701050939</v>
       </c>
       <c r="AG21" s="0" t="n">
-        <v>0.983611668884797</v>
+        <v>0.983501373009669</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13135,16 +13135,16 @@
         <v>0.991981746494854</v>
       </c>
       <c r="AD7" s="0" t="n">
-        <v>0.00142524039504853</v>
+        <v>0.0013261570063198</v>
       </c>
       <c r="AE7" s="0" t="n">
-        <v>0.00127326753543119</v>
+        <v>0.00118474937203427</v>
       </c>
       <c r="AF7" s="0" t="n">
-        <v>0.000668738564374399</v>
+        <v>0.000622247541974248</v>
       </c>
       <c r="AG7" s="0" t="n">
-        <v>0.996632753505146</v>
+        <v>0.996866846079672</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13322,16 +13322,16 @@
         <v>1.02076098936013</v>
       </c>
       <c r="AD9" s="0" t="n">
-        <v>0.0345139852641209</v>
+        <v>0.0321145566271111</v>
       </c>
       <c r="AE9" s="0" t="n">
-        <v>9.83853241807006E-005</v>
+        <v>9.15455297468173E-005</v>
       </c>
       <c r="AF9" s="0" t="n">
-        <v>5.46187718239917E-005</v>
+        <v>5.0821648882961E-005</v>
       </c>
       <c r="AG9" s="0" t="n">
-        <v>0.965333010639874</v>
+        <v>0.967743076194259</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13873,16 +13873,16 @@
         <v>1.00097074204372</v>
       </c>
       <c r="AD15" s="0" t="n">
-        <v>0.0122748370913457</v>
+        <v>0.0114214845907227</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>0.000756831559461948</v>
+        <v>0.00070421627023154</v>
       </c>
       <c r="AF15" s="0" t="n">
-        <v>0.000417073392914513</v>
+        <v>0.000388078252682642</v>
       </c>
       <c r="AG15" s="0" t="n">
-        <v>0.986551257956278</v>
+        <v>0.987486220886363</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14241,16 +14241,16 @@
         <v>1.00237865154989</v>
       </c>
       <c r="AD19" s="0" t="n">
-        <v>0.0175578550060032</v>
+        <v>0.0163372245924629</v>
       </c>
       <c r="AE19" s="0" t="n">
-        <v>0.00052815289434853</v>
+        <v>0.00049143545445506</v>
       </c>
       <c r="AF19" s="0" t="n">
-        <v>0.000341643649535169</v>
+        <v>0.000317892420864414</v>
       </c>
       <c r="AG19" s="0" t="n">
-        <v>0.981572348450113</v>
+        <v>0.982853447532218</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14611,16 +14611,16 @@
         <v>1.00009283969192</v>
       </c>
       <c r="AD23" s="0" t="n">
-        <v>0.00769281793172293</v>
+        <v>0.0071580095778506</v>
       </c>
       <c r="AE23" s="0" t="n">
-        <v>0.00341684273974584</v>
+        <v>0.00317930221073518</v>
       </c>
       <c r="AF23" s="0" t="n">
-        <v>0.00312917902045536</v>
+        <v>0.00291163700974424</v>
       </c>
       <c r="AG23" s="0" t="n">
-        <v>0.985761160308076</v>
+        <v>0.98675105120167</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15450,16 +15450,16 @@
         <v>0.99633399656016</v>
       </c>
       <c r="AD7" s="0" t="n">
-        <v>0.00172118263994998</v>
+        <v>0.00212151000799315</v>
       </c>
       <c r="AE7" s="0" t="n">
-        <v>0.00121915997361151</v>
+        <v>0.00150272261951042</v>
       </c>
       <c r="AF7" s="0" t="n">
-        <v>0.000653909273414378</v>
+        <v>0.000806001080692081</v>
       </c>
       <c r="AG7" s="0" t="n">
-        <v>0.996405748113024</v>
+        <v>0.995569766291804</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15635,16 +15635,16 @@
         <v>0.993981804136749</v>
       </c>
       <c r="AD9" s="0" t="n">
-        <v>0.020307085950242</v>
+        <v>0.025030281549823</v>
       </c>
       <c r="AE9" s="0" t="n">
-        <v>9.78145453972403E-005</v>
+        <v>0.00012056508831252</v>
       </c>
       <c r="AF9" s="0" t="n">
-        <v>4.82369744427494E-005</v>
+        <v>5.94563422035077E-005</v>
       </c>
       <c r="AG9" s="0" t="n">
-        <v>0.979546862529918</v>
+        <v>0.974789697019661</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16190,16 +16190,16 @@
         <v>0.9724361525717</v>
       </c>
       <c r="AD15" s="0" t="n">
-        <v>0.0106713401134174</v>
+        <v>0.0131533715968525</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>0.00044107640298022</v>
+        <v>0.000543665722331101</v>
       </c>
       <c r="AF15" s="0" t="n">
-        <v>0.000104069388635398</v>
+        <v>0.000128274736446413</v>
       </c>
       <c r="AG15" s="0" t="n">
-        <v>0.988783514094967</v>
+        <v>0.98617468794437</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16377,16 +16377,16 @@
         <v>0.996406952339411</v>
       </c>
       <c r="AD17" s="0" t="n">
-        <v>0.0118897227611479</v>
+        <v>0.0146551360933853</v>
       </c>
       <c r="AE17" s="0" t="n">
-        <v>0.000231516305497412</v>
+        <v>0.000285364346424406</v>
       </c>
       <c r="AF17" s="0" t="n">
-        <v>5.12132727659047E-005</v>
+        <v>6.31248934268285E-005</v>
       </c>
       <c r="AG17" s="0" t="n">
-        <v>0.987827547660589</v>
+        <v>0.984996374666763</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16928,16 +16928,16 @@
         <v>0.989566450519272</v>
       </c>
       <c r="AD23" s="0" t="n">
-        <v>0.00600981612283326</v>
+        <v>0.00740763051802561</v>
       </c>
       <c r="AE23" s="0" t="n">
-        <v>0.000493677333551138</v>
+        <v>0.000608501026874493</v>
       </c>
       <c r="AF23" s="0" t="n">
-        <v>0.000138957062887524</v>
+        <v>0.000171276884134611</v>
       </c>
       <c r="AG23" s="0" t="n">
-        <v>0.993357549480728</v>
+        <v>0.991812591570965</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17584,16 +17584,16 @@
         <v>0.973628146734699</v>
       </c>
       <c r="AD5" s="0" t="n">
-        <v>0.00174207999767895</v>
+        <v>0.00210091632060141</v>
       </c>
       <c r="AE5" s="0" t="n">
-        <v>8.36005031851114E-006</v>
+        <v>1.00820663681404E-005</v>
       </c>
       <c r="AF5" s="0" t="n">
-        <v>4.20668670118973E-006</v>
+        <v>5.07318651150438E-006</v>
       </c>
       <c r="AG5" s="0" t="n">
-        <v>0.998245353265301</v>
+        <v>0.997883928426519</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17952,16 +17952,16 @@
         <v>0.996734939323061</v>
       </c>
       <c r="AD9" s="0" t="n">
-        <v>0.000918926138104065</v>
+        <v>0.00110820796033607</v>
       </c>
       <c r="AE9" s="0" t="n">
-        <v>0.00121462650126326</v>
+        <v>0.00146481714005033</v>
       </c>
       <c r="AF9" s="0" t="n">
-        <v>0.000942288932322795</v>
+        <v>0.00113638305891615</v>
       </c>
       <c r="AG9" s="0" t="n">
-        <v>0.99692415842831</v>
+        <v>0.996290591840698</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18318,16 +18318,16 @@
         <v>0.980707074141306</v>
       </c>
       <c r="AD13" s="0" t="n">
-        <v>0.0111578413416647</v>
+        <v>0.0134561506983703</v>
       </c>
       <c r="AE13" s="0" t="n">
-        <v>0.000604780119741901</v>
+        <v>0.000729353660930557</v>
       </c>
       <c r="AF13" s="0" t="n">
-        <v>0.000391452679899662</v>
+        <v>0.000472084706236278</v>
       </c>
       <c r="AG13" s="0" t="n">
-        <v>0.987845925858694</v>
+        <v>0.985342410934463</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18690,16 +18690,16 @@
         <v>1.00239259124386</v>
       </c>
       <c r="AD17" s="0" t="n">
-        <v>0.0130570241673518</v>
+        <v>0.0157465301296295</v>
       </c>
       <c r="AE17" s="0" t="n">
-        <v>0.000288588254156595</v>
+        <v>0.000348032107537691</v>
       </c>
       <c r="AF17" s="0" t="n">
-        <v>0.000190978822347075</v>
+        <v>0.000230316934522402</v>
       </c>
       <c r="AG17" s="0" t="n">
-        <v>0.986463408756145</v>
+        <v>0.98367512082831</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19060,16 +19060,16 @@
         <v>1.00709484522567</v>
       </c>
       <c r="AD21" s="0" t="n">
-        <v>0.00949522559982443</v>
+        <v>0.0114510668035004</v>
       </c>
       <c r="AE21" s="0" t="n">
-        <v>0.000686480517819178</v>
+        <v>0.000827882832925456</v>
       </c>
       <c r="AF21" s="0" t="n">
-        <v>0.000426639108022695</v>
+        <v>0.000514518889055574</v>
       </c>
       <c r="AG21" s="0" t="n">
-        <v>0.989391654774334</v>
+        <v>0.987206531474519</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Sistemas ternarios_MF_filled.xlsx
+++ b/Sistemas ternarios_MF_filled.xlsx
@@ -1520,16 +1520,16 @@
         <v>2</v>
       </c>
       <c r="AD7" s="31" t="n">
-        <v>0.00133391210031924</v>
+        <v>0.00131439593254686</v>
       </c>
       <c r="AE7" s="31" t="n">
-        <v>0.000685912957483989</v>
+        <v>0.000331876406245623</v>
       </c>
       <c r="AF7" s="31" t="n">
-        <v>0.000801557358974884</v>
+        <v>0.000429268908006592</v>
       </c>
       <c r="AG7" s="31" t="n">
-        <v>0.997178617583222</v>
+        <v>0.997924458753201</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1729,16 +1729,16 @@
         <v>3</v>
       </c>
       <c r="AD9" s="31" t="n">
-        <v>0.0240256555085348</v>
+        <v>0.0242128859067119</v>
       </c>
       <c r="AE9" s="31" t="n">
-        <v>2.58847976788953E-005</v>
+        <v>2.1224264005602E-005</v>
       </c>
       <c r="AF9" s="31" t="n">
-        <v>4.96116341927225E-005</v>
+        <v>4.38811348964189E-005</v>
       </c>
       <c r="AG9" s="31" t="n">
-        <v>0.975898848059594</v>
+        <v>0.975722008694386</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2729,16 +2729,16 @@
       </c>
       <c r="AB19" s="2"/>
       <c r="AD19" s="0" t="n">
-        <v>0.0083912019804683</v>
+        <v>0.00786374369982345</v>
       </c>
       <c r="AE19" s="0" t="n">
-        <v>0.000773677351107489</v>
+        <v>0.000335604906130558</v>
       </c>
       <c r="AF19" s="0" t="n">
-        <v>0.000945970661007499</v>
+        <v>0.000486851403368356</v>
       </c>
       <c r="AG19" s="0" t="n">
-        <v>0.989889150007417</v>
+        <v>0.991313799990678</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3772,16 +3772,16 @@
         <v>0.962892579742591</v>
       </c>
       <c r="AD5" s="0" t="n">
-        <v>0.0269449351828853</v>
+        <v>0.0249102993464579</v>
       </c>
       <c r="AE5" s="0" t="n">
-        <v>6.11845024389588E-005</v>
+        <v>2.33107578428212E-005</v>
       </c>
       <c r="AF5" s="0" t="n">
-        <v>7.11999726022893E-005</v>
+        <v>3.11945685660548E-005</v>
       </c>
       <c r="AG5" s="0" t="n">
-        <v>0.972922680342074</v>
+        <v>0.975035195327133</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5073,16 +5073,16 @@
         <v>0.998103391430224</v>
       </c>
       <c r="AD19" s="0" t="n">
-        <v>0.00903120686880268</v>
+        <v>0.008776458612092</v>
       </c>
       <c r="AE19" s="0" t="n">
-        <v>0.000879942293655311</v>
+        <v>0.000389405566648141</v>
       </c>
       <c r="AF19" s="0" t="n">
-        <v>0.000803088908771208</v>
+        <v>0.000286059240735268</v>
       </c>
       <c r="AG19" s="0" t="n">
-        <v>0.989285761928771</v>
+        <v>0.990548076580525</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5445,16 +5445,16 @@
         <v>0.998622949499804</v>
       </c>
       <c r="AD23" s="0" t="n">
-        <v>0.0209087059304334</v>
+        <v>0.0203487415232242</v>
       </c>
       <c r="AE23" s="0" t="n">
-        <v>0.000302432844891912</v>
+        <v>0.000205702317551325</v>
       </c>
       <c r="AF23" s="0" t="n">
-        <v>0.000316434224783248</v>
+        <v>0.000216708489771156</v>
       </c>
       <c r="AG23" s="0" t="n">
-        <v>0.978472426999892</v>
+        <v>0.979228847669453</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9791,16 +9791,16 @@
         <v>1.00823753359508</v>
       </c>
       <c r="AD21" s="0" t="n">
-        <v>0.00808221542284589</v>
+        <v>0.00726214373206045</v>
       </c>
       <c r="AE21" s="0" t="n">
-        <v>0.00393072909126719</v>
+        <v>0.00289929210117323</v>
       </c>
       <c r="AF21" s="0" t="n">
-        <v>0.0045128072826791</v>
+        <v>0.00343251162688846</v>
       </c>
       <c r="AG21" s="0" t="n">
-        <v>0.983474248203208</v>
+        <v>0.986406052539878</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15635,16 +15635,16 @@
         <v>0.993981804136749</v>
       </c>
       <c r="AD9" s="0" t="n">
-        <v>0.025030281549823</v>
+        <v>0.0252102595450379</v>
       </c>
       <c r="AE9" s="0" t="n">
-        <v>0.00012056508831252</v>
+        <v>8.04924118460484E-005</v>
       </c>
       <c r="AF9" s="0" t="n">
-        <v>5.94563422035077E-005</v>
+        <v>1.94615075386359E-005</v>
       </c>
       <c r="AG9" s="0" t="n">
-        <v>0.974789697019661</v>
+        <v>0.974689786535578</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
